--- a/research/traditional_assets/database/data/sweden/sweden_telecom_wireless.xlsx
+++ b/research/traditional_assets/database/data/sweden/sweden_telecom_wireless.xlsx
@@ -650,10 +650,10 @@
         <v>0.1867898429008991</v>
       </c>
       <c r="X2">
-        <v>0.08300313275511723</v>
+        <v>0.08297921444850598</v>
       </c>
       <c r="Y2">
-        <v>0.1037867101457819</v>
+        <v>0.1038106284523931</v>
       </c>
       <c r="Z2">
         <v>1.499381060449763</v>
@@ -662,10 +662,10 @@
         <v>0.2476366554609589</v>
       </c>
       <c r="AB2">
-        <v>0.07165964827800408</v>
+        <v>0.07164304113904044</v>
       </c>
       <c r="AC2">
-        <v>0.1759770071829549</v>
+        <v>0.1759936143219185</v>
       </c>
       <c r="AD2">
         <v>3006.9</v>
@@ -787,10 +787,10 @@
         <v>0.1867898429008991</v>
       </c>
       <c r="X3">
-        <v>0.08300313275511723</v>
+        <v>0.08297921444850598</v>
       </c>
       <c r="Y3">
-        <v>0.1037867101457819</v>
+        <v>0.1038106284523931</v>
       </c>
       <c r="Z3">
         <v>1.499381060449763</v>
@@ -799,10 +799,10 @@
         <v>0.2476366554609589</v>
       </c>
       <c r="AB3">
-        <v>0.07165964827800408</v>
+        <v>0.07164304113904044</v>
       </c>
       <c r="AC3">
-        <v>0.1759770071829549</v>
+        <v>0.1759936143219185</v>
       </c>
       <c r="AD3">
         <v>3006.9</v>
@@ -1139,49 +1139,49 @@
         <v>5.04510638297872</v>
       </c>
       <c r="F2">
-        <v>3.06117418896002</v>
+        <v>3.02703812958946</v>
       </c>
       <c r="G2">
         <v>2.87356651376147</v>
       </c>
       <c r="H2">
-        <v>3.19627293577982</v>
+        <v>3.38428899082569</v>
       </c>
       <c r="I2">
         <v>0.305672461116194</v>
       </c>
       <c r="J2">
-        <v>0.34</v>
+        <v>0.36</v>
       </c>
       <c r="K2">
         <v>6830.1</v>
       </c>
       <c r="L2">
-        <v>6554.30745060234</v>
+        <v>6691.44071835918</v>
       </c>
       <c r="M2">
         <v>9652.5</v>
       </c>
       <c r="N2">
-        <v>9714.38745060234</v>
+        <v>10048.2607183592</v>
       </c>
       <c r="O2">
         <v>3006.9</v>
       </c>
       <c r="P2">
-        <v>3344.58</v>
+        <v>3541.32</v>
       </c>
       <c r="Q2">
-        <v>0.0716596482780041</v>
+        <v>0.07164304113904039</v>
       </c>
       <c r="R2">
-        <v>0.07149490421014219</v>
+        <v>0.0706251873221022</v>
       </c>
       <c r="S2">
         <v>0.0458932</v>
       </c>
       <c r="T2">
-        <v>0.0459726</v>
+        <v>0.0439082</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1194,16 +1194,16 @@
         </is>
       </c>
       <c r="W2">
-        <v>0.0830031327551172</v>
+        <v>0.08297921444850601</v>
       </c>
       <c r="X2">
-        <v>0.0846427578941548</v>
+        <v>0.08565349269078459</v>
       </c>
       <c r="Y2">
         <v>0.8586423660163049</v>
       </c>
       <c r="Z2">
-        <v>0.896484652525615</v>
+        <v>0.9204039882398301</v>
       </c>
       <c r="AA2">
         <v>3006.9</v>
@@ -1236,7 +1236,7 @@
         <v>6830.1</v>
       </c>
       <c r="AK2">
-        <v>0.043327855959079</v>
+        <v>0.04329999999999999</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1424,13 +1424,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.07336701386096411</v>
+        <v>0.07334929072204935</v>
       </c>
       <c r="C2">
-        <v>9239.171509303063</v>
+        <v>9239.177926605858</v>
       </c>
       <c r="D2">
-        <v>9054.671509303063</v>
+        <v>9054.677926605858</v>
       </c>
       <c r="E2">
         <v>-3006.9</v>
@@ -1475,19 +1475,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.07336701386096411</v>
+        <v>0.07334929072204935</v>
       </c>
       <c r="T2">
         <v>0.6362422799549505</v>
       </c>
       <c r="U2">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V2">
         <v>0.206</v>
       </c>
       <c r="W2">
-        <v>0.04104980000000001</v>
+        <v>0.03993820000000001</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1506,13 +1506,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.07326272381241052</v>
+        <v>0.07323392118316192</v>
       </c>
       <c r="C3">
-        <v>9175.186741364982</v>
+        <v>9178.886114925792</v>
       </c>
       <c r="D3">
-        <v>9089.056741364982</v>
+        <v>9092.756114925793</v>
       </c>
       <c r="E3">
         <v>-2908.53</v>
@@ -1539,37 +1539,37 @@
         <v>592.8</v>
       </c>
       <c r="M3">
-        <v>5.085729000000001</v>
+        <v>4.948011000000001</v>
       </c>
       <c r="N3">
-        <v>587.7142709999999</v>
+        <v>587.851989</v>
       </c>
       <c r="O3">
-        <v>121.069139826</v>
+        <v>121.097509734</v>
       </c>
       <c r="P3">
-        <v>466.645131174</v>
+        <v>466.754479266</v>
       </c>
       <c r="Q3">
-        <v>920.2451311740001</v>
+        <v>920.3544792660001</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.07358810688122275</v>
+        <v>0.07357024159915346</v>
       </c>
       <c r="T3">
         <v>0.6413450715739831</v>
       </c>
       <c r="U3">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V3">
         <v>0.206</v>
       </c>
       <c r="W3">
-        <v>0.04104980000000001</v>
+        <v>0.03993820000000001</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>116.5614605103811</v>
+        <v>119.8057158724991</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1588,13 +1588,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.07315843376385694</v>
+        <v>0.0731185516442745</v>
       </c>
       <c r="C4">
-        <v>9111.464125679628</v>
+        <v>9118.915920810621</v>
       </c>
       <c r="D4">
-        <v>9123.704125679627</v>
+        <v>9131.155920810621</v>
       </c>
       <c r="E4">
         <v>-2810.16</v>
@@ -1621,37 +1621,37 @@
         <v>592.8</v>
       </c>
       <c r="M4">
-        <v>10.171458</v>
+        <v>9.896022000000002</v>
       </c>
       <c r="N4">
-        <v>582.6285419999999</v>
+        <v>582.9039779999999</v>
       </c>
       <c r="O4">
-        <v>120.021479652</v>
+        <v>120.078219468</v>
       </c>
       <c r="P4">
-        <v>462.6070623479999</v>
+        <v>462.825758532</v>
       </c>
       <c r="Q4">
-        <v>916.2070623480001</v>
+        <v>916.4257585320001</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.07381371200393566</v>
+        <v>0.07379570167783113</v>
       </c>
       <c r="T4">
         <v>0.6465520017974858</v>
       </c>
       <c r="U4">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V4">
         <v>0.206</v>
       </c>
       <c r="W4">
-        <v>0.04104980000000001</v>
+        <v>0.03993820000000001</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>58.28073025519053</v>
+        <v>59.90285793624952</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1670,13 +1670,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.07305414371530336</v>
+        <v>0.07300318210538709</v>
       </c>
       <c r="C5">
-        <v>9048.006671683463</v>
+        <v>9059.271436230538</v>
       </c>
       <c r="D5">
-        <v>9158.616671683463</v>
+        <v>9169.881436230538</v>
       </c>
       <c r="E5">
         <v>-2711.79</v>
@@ -1703,37 +1703,37 @@
         <v>592.8</v>
       </c>
       <c r="M5">
-        <v>15.257187</v>
+        <v>14.844033</v>
       </c>
       <c r="N5">
-        <v>577.5428129999999</v>
+        <v>577.955967</v>
       </c>
       <c r="O5">
-        <v>118.973819478</v>
+        <v>119.058929202</v>
       </c>
       <c r="P5">
-        <v>458.5689935219999</v>
+        <v>458.897037798</v>
       </c>
       <c r="Q5">
-        <v>912.1689935220001</v>
+        <v>912.4970377980001</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.07404396877866326</v>
+        <v>0.07402581041792483</v>
       </c>
       <c r="T5">
         <v>0.6518662914070401</v>
       </c>
       <c r="U5">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V5">
         <v>0.206</v>
       </c>
       <c r="W5">
-        <v>0.04104980000000001</v>
+        <v>0.03993820000000001</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>38.85382017012702</v>
+        <v>39.93523862416635</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1752,13 +1752,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.07294985366674976</v>
+        <v>0.07288781256649966</v>
       </c>
       <c r="C6">
-        <v>8984.817435053228</v>
+        <v>8999.956822868093</v>
       </c>
       <c r="D6">
-        <v>9193.797435053228</v>
+        <v>9208.936822868092</v>
       </c>
       <c r="E6">
         <v>-2613.42</v>
@@ -1785,37 +1785,37 @@
         <v>592.8</v>
       </c>
       <c r="M6">
-        <v>20.34291600000001</v>
+        <v>19.792044</v>
       </c>
       <c r="N6">
-        <v>572.4570839999999</v>
+        <v>573.0079559999999</v>
       </c>
       <c r="O6">
-        <v>117.926159304</v>
+        <v>118.039638936</v>
       </c>
       <c r="P6">
-        <v>454.5309246959999</v>
+        <v>454.968317064</v>
       </c>
       <c r="Q6">
-        <v>908.1309246960001</v>
+        <v>908.5683170640001</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.07427902256953101</v>
+        <v>0.07426071309010382</v>
       </c>
       <c r="T6">
         <v>0.6572912953834602</v>
       </c>
       <c r="U6">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V6">
         <v>0.206</v>
       </c>
       <c r="W6">
-        <v>0.04104980000000001</v>
+        <v>0.03993820000000001</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>29.14036512759526</v>
+        <v>29.95142896812476</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1834,13 +1834,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.07284556361819618</v>
+        <v>0.07277244302761225</v>
       </c>
       <c r="C7">
-        <v>8921.899518597475</v>
+        <v>8940.976313609068</v>
       </c>
       <c r="D7">
-        <v>9229.249518597475</v>
+        <v>9248.326313609068</v>
       </c>
       <c r="E7">
         <v>-2515.05</v>
@@ -1867,37 +1867,37 @@
         <v>592.8</v>
       </c>
       <c r="M7">
-        <v>25.42864500000001</v>
+        <v>24.740055</v>
       </c>
       <c r="N7">
-        <v>567.371355</v>
+        <v>568.059945</v>
       </c>
       <c r="O7">
-        <v>116.87849913</v>
+        <v>117.02034867</v>
       </c>
       <c r="P7">
-        <v>450.49285587</v>
+        <v>451.03959633</v>
       </c>
       <c r="Q7">
-        <v>904.0928558700001</v>
+        <v>904.6395963300001</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.07451902486125914</v>
+        <v>0.0745005610816971</v>
       </c>
       <c r="T7">
         <v>0.6628305099699101</v>
       </c>
       <c r="U7">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V7">
         <v>0.206</v>
       </c>
       <c r="W7">
-        <v>0.04104980000000001</v>
+        <v>0.03993820000000001</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>23.31229210207622</v>
+        <v>23.96114317449981</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1916,13 +1916,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.07274127356964259</v>
+        <v>0.07265707348872481</v>
       </c>
       <c r="C8">
-        <v>8859.256073168832</v>
+        <v>8882.334214071849</v>
       </c>
       <c r="D8">
-        <v>9264.976073168831</v>
+        <v>9288.054214071848</v>
       </c>
       <c r="E8">
         <v>-2416.68</v>
@@ -1949,37 +1949,37 @@
         <v>592.8</v>
       </c>
       <c r="M8">
-        <v>30.51437400000001</v>
+        <v>29.688066</v>
       </c>
       <c r="N8">
-        <v>562.285626</v>
+        <v>563.1119339999999</v>
       </c>
       <c r="O8">
-        <v>115.830838956</v>
+        <v>116.001058404</v>
       </c>
       <c r="P8">
-        <v>446.454787044</v>
+        <v>447.1108755959999</v>
       </c>
       <c r="Q8">
-        <v>900.0547870440001</v>
+        <v>900.7108755960001</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.07476413358472617</v>
+        <v>0.07474551222204769</v>
       </c>
       <c r="T8">
         <v>0.6684875801858589</v>
       </c>
       <c r="U8">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V8">
         <v>0.206</v>
       </c>
       <c r="W8">
-        <v>0.04104980000000001</v>
+        <v>0.03993820000000001</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>19.42691008506351</v>
+        <v>19.96761931208317</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1998,13 +1998,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.07263698352108901</v>
+        <v>0.07254170394983739</v>
       </c>
       <c r="C9">
-        <v>8796.890298597493</v>
+        <v>8824.034904176298</v>
       </c>
       <c r="D9">
-        <v>9300.980298597493</v>
+        <v>9328.124904176299</v>
       </c>
       <c r="E9">
         <v>-2318.31</v>
@@ -2031,37 +2031,37 @@
         <v>592.8</v>
       </c>
       <c r="M9">
-        <v>35.60010300000001</v>
+        <v>34.63607700000001</v>
       </c>
       <c r="N9">
-        <v>557.199897</v>
+        <v>558.163923</v>
       </c>
       <c r="O9">
-        <v>114.783178782</v>
+        <v>114.981768138</v>
       </c>
       <c r="P9">
-        <v>442.416718218</v>
+        <v>443.1821548619999</v>
       </c>
       <c r="Q9">
-        <v>896.0167182180001</v>
+        <v>896.7821548620001</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.07501451346353658</v>
+        <v>0.07499573112885742</v>
       </c>
       <c r="T9">
         <v>0.6742663078258065</v>
       </c>
       <c r="U9">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V9">
         <v>0.206</v>
       </c>
       <c r="W9">
-        <v>0.04104980000000001</v>
+        <v>0.03993820000000001</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>16.65163721576872</v>
+        <v>17.11510226749986</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2080,13 +2080,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.07253269347253544</v>
+        <v>0.07242633441094999</v>
       </c>
       <c r="C10">
-        <v>8734.805444646583</v>
+        <v>8766.082839753501</v>
       </c>
       <c r="D10">
-        <v>9337.265444646584</v>
+        <v>9368.542839753502</v>
       </c>
       <c r="E10">
         <v>-2219.94</v>
@@ -2113,37 +2113,37 @@
         <v>592.8</v>
       </c>
       <c r="M10">
-        <v>40.68583200000001</v>
+        <v>39.58408800000001</v>
       </c>
       <c r="N10">
-        <v>552.1141679999999</v>
+        <v>553.2159119999999</v>
       </c>
       <c r="O10">
-        <v>113.735518608</v>
+        <v>113.962477872</v>
       </c>
       <c r="P10">
-        <v>438.3786493919999</v>
+        <v>439.2534341279999</v>
       </c>
       <c r="Q10">
-        <v>891.9786493920001</v>
+        <v>892.8534341280001</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.07527033638319068</v>
+        <v>0.07525138957711955</v>
       </c>
       <c r="T10">
         <v>0.6801706599796662</v>
       </c>
       <c r="U10">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V10">
         <v>0.206</v>
       </c>
       <c r="W10">
-        <v>0.04104980000000001</v>
+        <v>0.03993820000000001</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>14.57018256379763</v>
+        <v>14.97571448406238</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2162,13 +2162,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.07242840342398185</v>
+        <v>0.07231096487206257</v>
       </c>
       <c r="C11">
-        <v>8673.004811989986</v>
+        <v>8708.482554197522</v>
       </c>
       <c r="D11">
-        <v>9373.834811989986</v>
+        <v>9409.312554197522</v>
       </c>
       <c r="E11">
         <v>-2121.57</v>
@@ -2195,37 +2195,37 @@
         <v>592.8</v>
       </c>
       <c r="M11">
-        <v>45.77156100000001</v>
+        <v>44.532099</v>
       </c>
       <c r="N11">
-        <v>547.0284389999999</v>
+        <v>548.2679009999999</v>
       </c>
       <c r="O11">
-        <v>112.687858434</v>
+        <v>112.943187606</v>
       </c>
       <c r="P11">
-        <v>434.340580566</v>
+        <v>435.324713394</v>
       </c>
       <c r="Q11">
-        <v>887.9405805660001</v>
+        <v>888.924713394</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.07553178178459544</v>
+        <v>0.07551266689237644</v>
       </c>
       <c r="T11">
         <v>0.6862047781149294</v>
       </c>
       <c r="U11">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V11">
         <v>0.206</v>
       </c>
       <c r="W11">
-        <v>0.04104980000000001</v>
+        <v>0.03993820000000001</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>12.95127339004234</v>
+        <v>13.31174620805545</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2244,13 +2244,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.07232411337542827</v>
+        <v>0.07219559533317513</v>
       </c>
       <c r="C12">
-        <v>8611.491753213188</v>
+        <v>8651.238660160405</v>
       </c>
       <c r="D12">
-        <v>9410.691753213188</v>
+        <v>9450.438660160406</v>
       </c>
       <c r="E12">
         <v>-2023.2</v>
@@ -2277,37 +2277,37 @@
         <v>592.8</v>
       </c>
       <c r="M12">
-        <v>50.85729000000001</v>
+        <v>49.48011</v>
       </c>
       <c r="N12">
-        <v>541.9427099999999</v>
+        <v>543.31989</v>
       </c>
       <c r="O12">
-        <v>111.64019826</v>
+        <v>111.92389734</v>
       </c>
       <c r="P12">
-        <v>430.3025117399999</v>
+        <v>431.39599266</v>
       </c>
       <c r="Q12">
-        <v>883.9025117400001</v>
+        <v>884.9959926600002</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.07579903708380917</v>
+        <v>0.07577975037019459</v>
       </c>
       <c r="T12">
         <v>0.6923729877643094</v>
       </c>
       <c r="U12">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V12">
         <v>0.206</v>
       </c>
       <c r="W12">
-        <v>0.04104980000000001</v>
+        <v>0.03993820000000001</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>11.65614605103811</v>
+        <v>11.98057158724991</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2326,13 +2326,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.07221982332687467</v>
+        <v>0.07208022579428772</v>
       </c>
       <c r="C13">
-        <v>8550.269673837898</v>
+        <v>8594.355851291901</v>
       </c>
       <c r="D13">
-        <v>9447.839673837898</v>
+        <v>9491.9258512919</v>
       </c>
       <c r="E13">
         <v>-1924.83</v>
@@ -2359,37 +2359,37 @@
         <v>592.8</v>
       </c>
       <c r="M13">
-        <v>55.94301900000001</v>
+        <v>54.428121</v>
       </c>
       <c r="N13">
-        <v>536.8569809999999</v>
+        <v>538.3718789999999</v>
       </c>
       <c r="O13">
-        <v>110.592538086</v>
+        <v>110.904607074</v>
       </c>
       <c r="P13">
-        <v>426.2644429139999</v>
+        <v>427.4672719259999</v>
       </c>
       <c r="Q13">
-        <v>879.8644429140001</v>
+        <v>881.0672719260001</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.0760722981200839</v>
+        <v>0.07605283572391879</v>
       </c>
       <c r="T13">
         <v>0.6986798088664847</v>
       </c>
       <c r="U13">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V13">
         <v>0.206</v>
       </c>
       <c r="W13">
-        <v>0.04104980000000001</v>
+        <v>0.03993820000000001</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>10.59649641003464</v>
+        <v>10.89142871568173</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2408,13 +2408,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.07211553327832108</v>
+        <v>0.07196485625540029</v>
       </c>
       <c r="C14">
-        <v>8489.342033370953</v>
+        <v>8537.838904025228</v>
       </c>
       <c r="D14">
-        <v>9485.282033370953</v>
+        <v>9533.778904025228</v>
       </c>
       <c r="E14">
         <v>-1826.46</v>
@@ -2441,37 +2441,37 @@
         <v>592.8</v>
       </c>
       <c r="M14">
-        <v>61.02874800000001</v>
+        <v>59.37613200000001</v>
       </c>
       <c r="N14">
-        <v>531.7712519999999</v>
+        <v>533.423868</v>
       </c>
       <c r="O14">
-        <v>109.544877912</v>
+        <v>109.885316808</v>
       </c>
       <c r="P14">
-        <v>422.2263740879999</v>
+        <v>423.538551192</v>
       </c>
       <c r="Q14">
-        <v>875.826374088</v>
+        <v>877.1385511920001</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.07635176963445578</v>
+        <v>0.07633212756295488</v>
       </c>
       <c r="T14">
         <v>0.7051299668118911</v>
       </c>
       <c r="U14">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V14">
         <v>0.206</v>
       </c>
       <c r="W14">
-        <v>0.04104980000000001</v>
+        <v>0.03993820000000001</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>9.713455042531756</v>
+        <v>9.983809656041588</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2490,13 +2490,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.0720112432297675</v>
+        <v>0.07184948671651288</v>
       </c>
       <c r="C15">
-        <v>8428.712346378361</v>
+        <v>8481.692679410202</v>
       </c>
       <c r="D15">
-        <v>9523.02234637836</v>
+        <v>9576.002679410201</v>
       </c>
       <c r="E15">
         <v>-1728.09</v>
@@ -2523,37 +2523,37 @@
         <v>592.8</v>
       </c>
       <c r="M15">
-        <v>66.11447700000001</v>
+        <v>64.32414300000001</v>
       </c>
       <c r="N15">
-        <v>526.685523</v>
+        <v>528.4758569999999</v>
       </c>
       <c r="O15">
-        <v>108.497217738</v>
+        <v>108.866026542</v>
       </c>
       <c r="P15">
-        <v>418.188305262</v>
+        <v>419.6098304579999</v>
       </c>
       <c r="Q15">
-        <v>871.7883052620001</v>
+        <v>873.2098304580001</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.07663766578134194</v>
+        <v>0.07661783990403778</v>
       </c>
       <c r="T15">
         <v>0.7117284042502953</v>
       </c>
       <c r="U15">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V15">
         <v>0.206</v>
       </c>
       <c r="W15">
-        <v>0.04104980000000001</v>
+        <v>0.03993820000000001</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>8.966266193106238</v>
+        <v>9.215824297884541</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2572,13 +2572,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.07202922918121392</v>
+        <v>0.07190085717762545</v>
       </c>
       <c r="C16">
-        <v>8323.812203370277</v>
+        <v>8364.475648069092</v>
       </c>
       <c r="D16">
-        <v>9516.492203370277</v>
+        <v>9557.155648069092</v>
       </c>
       <c r="E16">
         <v>-1629.72</v>
@@ -2605,37 +2605,37 @@
         <v>592.8</v>
       </c>
       <c r="M16">
-        <v>72.71510400000001</v>
+        <v>71.33792400000002</v>
       </c>
       <c r="N16">
-        <v>520.084896</v>
+        <v>521.4620759999999</v>
       </c>
       <c r="O16">
-        <v>107.137488576</v>
+        <v>107.421187656</v>
       </c>
       <c r="P16">
-        <v>412.9474074239999</v>
+        <v>414.0408883439999</v>
       </c>
       <c r="Q16">
-        <v>866.5474074240001</v>
+        <v>867.6408883440001</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.07693021067583013</v>
+        <v>0.07691019671816912</v>
       </c>
       <c r="T16">
         <v>0.7184802937221508</v>
       </c>
       <c r="U16">
-        <v>0.05280000000000001</v>
+        <v>0.05180000000000001</v>
       </c>
       <c r="V16">
         <v>0.206</v>
       </c>
       <c r="W16">
-        <v>0.04192320000000001</v>
+        <v>0.0411292</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>8.152364053553438</v>
+        <v>8.309745598988833</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2654,13 +2654,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.07193367313266032</v>
+        <v>0.07179739763873803</v>
       </c>
       <c r="C17">
-        <v>8260.238628137249</v>
+        <v>8304.139413223771</v>
       </c>
       <c r="D17">
-        <v>9551.288628137248</v>
+        <v>9595.18941322377</v>
       </c>
       <c r="E17">
         <v>-1531.35</v>
@@ -2687,37 +2687,37 @@
         <v>592.8</v>
       </c>
       <c r="M17">
-        <v>77.90904</v>
+        <v>76.43349000000001</v>
       </c>
       <c r="N17">
-        <v>514.89096</v>
+        <v>516.3665099999999</v>
       </c>
       <c r="O17">
-        <v>106.06753776</v>
+        <v>106.37150106</v>
       </c>
       <c r="P17">
-        <v>408.82342224</v>
+        <v>409.9950089399999</v>
       </c>
       <c r="Q17">
-        <v>862.42342224</v>
+        <v>863.5950089400001</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.07722963897960038</v>
+        <v>0.07720943251616239</v>
       </c>
       <c r="T17">
         <v>0.7253910511815794</v>
       </c>
       <c r="U17">
-        <v>0.05280000000000001</v>
+        <v>0.05180000000000001</v>
       </c>
       <c r="V17">
         <v>0.206</v>
       </c>
       <c r="W17">
-        <v>0.04192320000000001</v>
+        <v>0.0411292</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>7.608873116649876</v>
+        <v>7.755762559056245</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2736,13 +2736,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.07183811708410674</v>
+        <v>0.0716939380998506</v>
       </c>
       <c r="C18">
-        <v>8196.920448395656</v>
+        <v>8244.107107104155</v>
       </c>
       <c r="D18">
-        <v>9586.340448395656</v>
+        <v>9633.527107104155</v>
       </c>
       <c r="E18">
         <v>-1432.98</v>
@@ -2769,37 +2769,37 @@
         <v>592.8</v>
       </c>
       <c r="M18">
-        <v>83.10297600000001</v>
+        <v>81.52905600000001</v>
       </c>
       <c r="N18">
-        <v>509.6970239999999</v>
+        <v>511.2709439999999</v>
       </c>
       <c r="O18">
-        <v>104.997586944</v>
+        <v>105.321814464</v>
       </c>
       <c r="P18">
-        <v>404.699437056</v>
+        <v>405.9491295359999</v>
       </c>
       <c r="Q18">
-        <v>858.2994370560001</v>
+        <v>859.549129536</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.0775361965286985</v>
+        <v>0.07751579297601263</v>
       </c>
       <c r="T18">
         <v>0.7324663504852802</v>
       </c>
       <c r="U18">
-        <v>0.05280000000000001</v>
+        <v>0.05180000000000001</v>
       </c>
       <c r="V18">
         <v>0.206</v>
       </c>
       <c r="W18">
-        <v>0.04192320000000001</v>
+        <v>0.0411292</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>7.133318546859259</v>
+        <v>7.271027399115229</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2818,13 +2818,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.07203951703555315</v>
+        <v>0.07159047856096318</v>
       </c>
       <c r="C19">
-        <v>8024.971026250055</v>
+        <v>8184.38238737705</v>
       </c>
       <c r="D19">
-        <v>9512.761026250055</v>
+        <v>9672.17238737705</v>
       </c>
       <c r="E19">
         <v>-1334.61</v>
@@ -2851,45 +2851,45 @@
         <v>592.8</v>
       </c>
       <c r="M19">
-        <v>91.97595000000003</v>
+        <v>86.62462200000002</v>
       </c>
       <c r="N19">
-        <v>500.8240499999999</v>
+        <v>506.1753779999999</v>
       </c>
       <c r="O19">
-        <v>103.1697543</v>
+        <v>104.272127868</v>
       </c>
       <c r="P19">
-        <v>397.6542956999999</v>
+        <v>401.9032501319999</v>
       </c>
       <c r="Q19">
-        <v>851.2542957000001</v>
+        <v>855.5032501320001</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.07785014100669055</v>
+        <v>0.07782953561561828</v>
       </c>
       <c r="T19">
         <v>0.739712138928829</v>
       </c>
       <c r="U19">
-        <v>0.05500000000000001</v>
+        <v>0.05180000000000001</v>
       </c>
       <c r="V19">
         <v>0.206</v>
       </c>
       <c r="W19">
-        <v>0.04367000000000001</v>
+        <v>0.0411292</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y19">
-        <v>6.445163110574012</v>
+        <v>6.843319905049627</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2900,13 +2900,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.07196142898699956</v>
+        <v>0.07172998302207577</v>
       </c>
       <c r="C20">
-        <v>7954.995229994265</v>
+        <v>8033.975670054851</v>
       </c>
       <c r="D20">
-        <v>9541.155229994265</v>
+        <v>9620.135670054851</v>
       </c>
       <c r="E20">
         <v>-1236.24</v>
@@ -2933,37 +2933,37 @@
         <v>592.8</v>
       </c>
       <c r="M20">
-        <v>97.38630000000001</v>
+        <v>94.73031</v>
       </c>
       <c r="N20">
-        <v>495.4136999999999</v>
+        <v>498.0696899999999</v>
       </c>
       <c r="O20">
-        <v>102.0552222</v>
+        <v>102.60235614</v>
       </c>
       <c r="P20">
-        <v>393.3584777999999</v>
+        <v>395.4673338599999</v>
       </c>
       <c r="Q20">
-        <v>846.9584778000001</v>
+        <v>849.0673338600001</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.07817174266707264</v>
+        <v>0.07815093051472655</v>
       </c>
       <c r="T20">
         <v>0.7471346539197816</v>
       </c>
       <c r="U20">
-        <v>0.05500000000000001</v>
+        <v>0.05350000000000001</v>
       </c>
       <c r="V20">
         <v>0.206</v>
       </c>
       <c r="W20">
-        <v>0.04367000000000001</v>
+        <v>0.04247900000000001</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>6.087098493319901</v>
+        <v>6.257764806216721</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2982,13 +2982,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.07188334093844599</v>
+        <v>0.07164002148318835</v>
       </c>
       <c r="C21">
-        <v>7885.189446312074</v>
+        <v>7969.097987766235</v>
       </c>
       <c r="D21">
-        <v>9569.719446312074</v>
+        <v>9653.627987766235</v>
       </c>
       <c r="E21">
         <v>-1137.87</v>
@@ -3015,37 +3015,37 @@
         <v>592.8</v>
       </c>
       <c r="M21">
-        <v>102.79665</v>
+        <v>99.99310500000001</v>
       </c>
       <c r="N21">
-        <v>490.00335</v>
+        <v>492.8068949999999</v>
       </c>
       <c r="O21">
-        <v>100.9406901</v>
+        <v>101.51822037</v>
       </c>
       <c r="P21">
-        <v>389.0626599</v>
+        <v>391.2886746299999</v>
       </c>
       <c r="Q21">
-        <v>842.6626599000001</v>
+        <v>844.8886746300001</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.07850128510919258</v>
+        <v>0.07848026109035597</v>
       </c>
       <c r="T21">
         <v>0.7547404408858195</v>
       </c>
       <c r="U21">
-        <v>0.05500000000000001</v>
+        <v>0.05350000000000001</v>
       </c>
       <c r="V21">
         <v>0.206</v>
       </c>
       <c r="W21">
-        <v>0.04367000000000001</v>
+        <v>0.04247900000000001</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>5.766724888408327</v>
+        <v>5.928408763784262</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3064,13 +3064,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.07204345288989239</v>
+        <v>0.07155005994430091</v>
       </c>
       <c r="C22">
-        <v>7728.434352636626</v>
+        <v>7904.454325938059</v>
       </c>
       <c r="D22">
-        <v>9511.334352636626</v>
+        <v>9687.354325938059</v>
       </c>
       <c r="E22">
         <v>-1039.5</v>
@@ -3097,45 +3097,45 @@
         <v>592.8</v>
       </c>
       <c r="M22">
-        <v>111.1581</v>
+        <v>105.2559</v>
       </c>
       <c r="N22">
-        <v>481.6419</v>
+        <v>487.5441</v>
       </c>
       <c r="O22">
-        <v>99.21823140000001</v>
+        <v>100.4340846</v>
       </c>
       <c r="P22">
-        <v>382.4236685999999</v>
+        <v>387.1100154</v>
       </c>
       <c r="Q22">
-        <v>836.0236686000001</v>
+        <v>840.7100154000001</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.07883906611236549</v>
+        <v>0.07881782493037615</v>
       </c>
       <c r="T22">
         <v>0.7625363725260083</v>
       </c>
       <c r="U22">
-        <v>0.05650000000000001</v>
+        <v>0.05350000000000001</v>
       </c>
       <c r="V22">
         <v>0.206</v>
       </c>
       <c r="W22">
-        <v>0.04486100000000001</v>
+        <v>0.04247900000000001</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y22">
-        <v>5.332944697687347</v>
+        <v>5.631988325595048</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3146,13 +3146,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.07197727484133881</v>
+        <v>0.0715934904054135</v>
       </c>
       <c r="C23">
-        <v>7654.109695416315</v>
+        <v>7789.772990840571</v>
       </c>
       <c r="D23">
-        <v>9535.379695416315</v>
+        <v>9671.042990840571</v>
       </c>
       <c r="E23">
         <v>-941.1300000000001</v>
@@ -3179,37 +3179,37 @@
         <v>592.8</v>
       </c>
       <c r="M23">
-        <v>116.716005</v>
+        <v>112.171311</v>
       </c>
       <c r="N23">
-        <v>476.083995</v>
+        <v>480.628689</v>
       </c>
       <c r="O23">
-        <v>98.07330297</v>
+        <v>99.00950993399999</v>
       </c>
       <c r="P23">
-        <v>378.01069203</v>
+        <v>381.619179066</v>
       </c>
       <c r="Q23">
-        <v>831.6106920300001</v>
+        <v>835.2191790660002</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.07918539853334026</v>
+        <v>0.07916393469039684</v>
       </c>
       <c r="T23">
         <v>0.7705296695241765</v>
       </c>
       <c r="U23">
-        <v>0.05650000000000001</v>
+        <v>0.05430000000000001</v>
       </c>
       <c r="V23">
         <v>0.206</v>
       </c>
       <c r="W23">
-        <v>0.04486100000000001</v>
+        <v>0.04311420000000001</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>5.078994950178426</v>
+        <v>5.284773751106465</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3228,13 +3228,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.07191109679278523</v>
+        <v>0.07150988086652607</v>
       </c>
       <c r="C24">
-        <v>7579.906923069288</v>
+        <v>7722.853601180721</v>
       </c>
       <c r="D24">
-        <v>9559.546923069287</v>
+        <v>9702.49360118072</v>
       </c>
       <c r="E24">
         <v>-842.7600000000002</v>
@@ -3261,37 +3261,37 @@
         <v>592.8</v>
       </c>
       <c r="M24">
-        <v>122.27391</v>
+        <v>117.512802</v>
       </c>
       <c r="N24">
-        <v>470.52609</v>
+        <v>475.2871979999999</v>
       </c>
       <c r="O24">
-        <v>96.92837453999999</v>
+        <v>97.90916278799999</v>
       </c>
       <c r="P24">
-        <v>373.59771546</v>
+        <v>377.3780352119999</v>
       </c>
       <c r="Q24">
-        <v>827.1977154600002</v>
+        <v>830.9780352120001</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.07954061127280157</v>
+        <v>0.07951891905964881</v>
       </c>
       <c r="T24">
         <v>0.778727922855631</v>
       </c>
       <c r="U24">
-        <v>0.05650000000000001</v>
+        <v>0.05430000000000001</v>
       </c>
       <c r="V24">
         <v>0.206</v>
       </c>
       <c r="W24">
-        <v>0.04486100000000001</v>
+        <v>0.04311420000000001</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>4.848131543352133</v>
+        <v>5.044556762419807</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3310,13 +3310,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.07184491874423164</v>
+        <v>0.07142627132763865</v>
       </c>
       <c r="C25">
-        <v>7505.826964694597</v>
+        <v>7656.139436151057</v>
       </c>
       <c r="D25">
-        <v>9583.836964694598</v>
+        <v>9734.149436151058</v>
       </c>
       <c r="E25">
         <v>-744.3899999999999</v>
@@ -3343,37 +3343,37 @@
         <v>592.8</v>
       </c>
       <c r="M25">
-        <v>127.831815</v>
+        <v>122.854293</v>
       </c>
       <c r="N25">
-        <v>464.9681849999999</v>
+        <v>469.9457069999999</v>
       </c>
       <c r="O25">
-        <v>95.78344611</v>
+        <v>96.80881564199998</v>
       </c>
       <c r="P25">
-        <v>369.1847388899999</v>
+        <v>373.136891358</v>
       </c>
       <c r="Q25">
-        <v>822.7847388900001</v>
+        <v>826.7368913580001</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.07990505031718394</v>
+        <v>0.07988312380212811</v>
       </c>
       <c r="T25">
         <v>0.7871391178320584</v>
       </c>
       <c r="U25">
-        <v>0.05650000000000001</v>
+        <v>0.05430000000000001</v>
       </c>
       <c r="V25">
         <v>0.206</v>
       </c>
       <c r="W25">
-        <v>0.04486100000000001</v>
+        <v>0.04311420000000001</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>4.637343215380302</v>
+        <v>4.825228207531989</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3392,13 +3392,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.07177874069567805</v>
+        <v>0.07134266178875123</v>
       </c>
       <c r="C26">
-        <v>7431.870758858407</v>
+        <v>7589.632511054874</v>
       </c>
       <c r="D26">
-        <v>9608.250758858407</v>
+        <v>9766.012511054874</v>
       </c>
       <c r="E26">
         <v>-646.02</v>
@@ -3425,37 +3425,37 @@
         <v>592.8</v>
       </c>
       <c r="M26">
-        <v>133.38972</v>
+        <v>128.195784</v>
       </c>
       <c r="N26">
-        <v>459.4102799999999</v>
+        <v>464.604216</v>
       </c>
       <c r="O26">
-        <v>94.63851767999999</v>
+        <v>95.70846849599999</v>
       </c>
       <c r="P26">
-        <v>364.7717623199999</v>
+        <v>368.8957475039999</v>
       </c>
       <c r="Q26">
-        <v>818.37176232</v>
+        <v>822.4957475040001</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.08027907986273428</v>
+        <v>0.08025691287993583</v>
       </c>
       <c r="T26">
         <v>0.7957716600447076</v>
       </c>
       <c r="U26">
-        <v>0.05650000000000001</v>
+        <v>0.05430000000000001</v>
       </c>
       <c r="V26">
         <v>0.206</v>
       </c>
       <c r="W26">
-        <v>0.04486100000000001</v>
+        <v>0.04311420000000001</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>4.444120581406121</v>
+        <v>4.624177032218157</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3474,13 +3474,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.07171256264712446</v>
+        <v>0.07125905224986381</v>
       </c>
       <c r="C27">
-        <v>7358.039253714893</v>
+        <v>7523.334867669109</v>
       </c>
       <c r="D27">
-        <v>9632.789253714893</v>
+        <v>9798.084867669109</v>
       </c>
       <c r="E27">
         <v>-547.6500000000001</v>
@@ -3507,37 +3507,37 @@
         <v>592.8</v>
       </c>
       <c r="M27">
-        <v>138.947625</v>
+        <v>133.537275</v>
       </c>
       <c r="N27">
-        <v>453.8523749999999</v>
+        <v>459.2627249999999</v>
       </c>
       <c r="O27">
-        <v>93.49358925</v>
+        <v>94.60812134999999</v>
       </c>
       <c r="P27">
-        <v>360.3587857499999</v>
+        <v>364.65460365</v>
       </c>
       <c r="Q27">
-        <v>813.9587857500001</v>
+        <v>818.25460365</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.08066308352949927</v>
+        <v>0.08064066966648509</v>
       </c>
       <c r="T27">
         <v>0.8046344033830274</v>
       </c>
       <c r="U27">
-        <v>0.05650000000000001</v>
+        <v>0.05430000000000001</v>
       </c>
       <c r="V27">
         <v>0.206</v>
       </c>
       <c r="W27">
-        <v>0.04486100000000001</v>
+        <v>0.04311420000000001</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>4.266355758149878</v>
+        <v>4.43920995092943</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3556,13 +3556,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.07193540059857088</v>
+        <v>0.07117544271097639</v>
       </c>
       <c r="C28">
-        <v>7177.537318682286</v>
+        <v>7457.248574680504</v>
       </c>
       <c r="D28">
-        <v>9550.657318682286</v>
+        <v>9830.368574680504</v>
       </c>
       <c r="E28">
         <v>-449.2800000000002</v>
@@ -3589,45 +3589,45 @@
         <v>592.8</v>
       </c>
       <c r="M28">
-        <v>148.086198</v>
+        <v>138.878766</v>
       </c>
       <c r="N28">
-        <v>444.7138019999999</v>
+        <v>453.9212339999999</v>
       </c>
       <c r="O28">
-        <v>91.611043212</v>
+        <v>93.50777420399999</v>
       </c>
       <c r="P28">
-        <v>353.102758788</v>
+        <v>360.4134597959999</v>
       </c>
       <c r="Q28">
-        <v>806.7027587880001</v>
+        <v>814.013459796</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.08105746567374443</v>
+        <v>0.0810347982580762</v>
       </c>
       <c r="T28">
         <v>0.8137366803250857</v>
       </c>
       <c r="U28">
-        <v>0.05790000000000001</v>
+        <v>0.05430000000000001</v>
       </c>
       <c r="V28">
         <v>0.206</v>
       </c>
       <c r="W28">
-        <v>0.04597260000000001</v>
+        <v>0.04311420000000001</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y28">
-        <v>4.003073939409261</v>
+        <v>4.268471106662914</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3638,13 +3638,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.07188033855001728</v>
+        <v>0.07130621317208896</v>
       </c>
       <c r="C29">
-        <v>7099.331119700113</v>
+        <v>7308.478234075488</v>
       </c>
       <c r="D29">
-        <v>9570.821119700113</v>
+        <v>9779.968234075488</v>
       </c>
       <c r="E29">
         <v>-350.9099999999999</v>
@@ -3671,37 +3671,37 @@
         <v>592.8</v>
       </c>
       <c r="M29">
-        <v>153.781821</v>
+        <v>146.876247</v>
       </c>
       <c r="N29">
-        <v>439.0181789999999</v>
+        <v>445.9237529999999</v>
       </c>
       <c r="O29">
-        <v>90.43774487399999</v>
+        <v>91.86029311799999</v>
       </c>
       <c r="P29">
-        <v>348.5804341259999</v>
+        <v>354.063459882</v>
       </c>
       <c r="Q29">
-        <v>802.1804341260001</v>
+        <v>807.6634598820001</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.08146265280824286</v>
+        <v>0.08143972489327256</v>
       </c>
       <c r="T29">
         <v>0.8230883347176112</v>
       </c>
       <c r="U29">
-        <v>0.05790000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V29">
         <v>0.206</v>
       </c>
       <c r="W29">
-        <v>0.04597260000000001</v>
+        <v>0.04390820000000001</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>3.854811941653362</v>
+        <v>4.036050839452616</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3720,13 +3720,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.07182527650146371</v>
+        <v>0.07123054363320155</v>
       </c>
       <c r="C30">
-        <v>7021.210242400532</v>
+        <v>7239.208897328308</v>
       </c>
       <c r="D30">
-        <v>9591.070242400532</v>
+        <v>9809.068897328309</v>
       </c>
       <c r="E30">
         <v>-252.54</v>
@@ -3753,37 +3753,37 @@
         <v>592.8</v>
       </c>
       <c r="M30">
-        <v>159.477444</v>
+        <v>152.316108</v>
       </c>
       <c r="N30">
-        <v>433.322556</v>
+        <v>440.4838919999999</v>
       </c>
       <c r="O30">
-        <v>89.26444653599999</v>
+        <v>90.739681752</v>
       </c>
       <c r="P30">
-        <v>344.058109464</v>
+        <v>349.7442102479999</v>
       </c>
       <c r="Q30">
-        <v>797.6581094640001</v>
+        <v>803.3442102480001</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.08187909514092181</v>
+        <v>0.0818558994905577</v>
       </c>
       <c r="T30">
         <v>0.832699757287707</v>
       </c>
       <c r="U30">
-        <v>0.05790000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V30">
         <v>0.206</v>
       </c>
       <c r="W30">
-        <v>0.04597260000000001</v>
+        <v>0.04390820000000001</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>3.717140086594314</v>
+        <v>3.891906166615023</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3802,13 +3802,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.07177021445291011</v>
+        <v>0.07115487409431412</v>
       </c>
       <c r="C31">
-        <v>6943.175229480659</v>
+        <v>7170.113257658988</v>
       </c>
       <c r="D31">
-        <v>9611.405229480659</v>
+        <v>9838.343257658988</v>
       </c>
       <c r="E31">
         <v>-154.1700000000001</v>
@@ -3835,37 +3835,37 @@
         <v>592.8</v>
       </c>
       <c r="M31">
-        <v>165.173067</v>
+        <v>157.755969</v>
       </c>
       <c r="N31">
-        <v>427.6269329999999</v>
+        <v>435.0440309999999</v>
       </c>
       <c r="O31">
-        <v>88.09114819799998</v>
+        <v>89.61907038599999</v>
       </c>
       <c r="P31">
-        <v>339.5357848019999</v>
+        <v>345.4249606139999</v>
       </c>
       <c r="Q31">
-        <v>793.135784802</v>
+        <v>799.0249606140001</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.08230726824353538</v>
+        <v>0.08228379731593538</v>
       </c>
       <c r="T31">
         <v>0.8425819241555518</v>
       </c>
       <c r="U31">
-        <v>0.05790000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V31">
         <v>0.206</v>
       </c>
       <c r="W31">
-        <v>0.04597260000000001</v>
+        <v>0.04390820000000001</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>3.588962842228992</v>
+        <v>3.757702505697264</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3884,13 +3884,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.07171515240435654</v>
+        <v>0.0710792045554267</v>
       </c>
       <c r="C32">
-        <v>6865.226628249849</v>
+        <v>7101.192874876606</v>
       </c>
       <c r="D32">
-        <v>9631.82662824985</v>
+        <v>9867.792874876606</v>
       </c>
       <c r="E32">
         <v>-55.80000000000018</v>
@@ -3917,37 +3917,37 @@
         <v>592.8</v>
       </c>
       <c r="M32">
-        <v>170.86869</v>
+        <v>163.19583</v>
       </c>
       <c r="N32">
-        <v>421.9313099999999</v>
+        <v>429.60417</v>
       </c>
       <c r="O32">
-        <v>86.91784985999999</v>
+        <v>88.49845902</v>
       </c>
       <c r="P32">
-        <v>335.0134601399999</v>
+        <v>341.10571098</v>
       </c>
       <c r="Q32">
-        <v>788.6134601400001</v>
+        <v>794.70571098</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.08274767486336648</v>
+        <v>0.08272392079346672</v>
       </c>
       <c r="T32">
         <v>0.8527464386481923</v>
       </c>
       <c r="U32">
-        <v>0.05790000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V32">
         <v>0.206</v>
       </c>
       <c r="W32">
-        <v>0.04597260000000001</v>
+        <v>0.04390820000000001</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>3.469330747488027</v>
+        <v>3.632445755507355</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3966,13 +3966,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.07166009035580294</v>
+        <v>0.07100353501653928</v>
       </c>
       <c r="C33">
-        <v>6787.364990678891</v>
+        <v>7032.449327522576</v>
       </c>
       <c r="D33">
-        <v>9652.33499067889</v>
+        <v>9897.419327522575</v>
       </c>
       <c r="E33">
         <v>42.56999999999971</v>
@@ -3999,37 +3999,37 @@
         <v>592.8</v>
       </c>
       <c r="M33">
-        <v>176.564313</v>
+        <v>168.635691</v>
       </c>
       <c r="N33">
-        <v>416.235687</v>
+        <v>424.1643089999999</v>
       </c>
       <c r="O33">
-        <v>85.74455152200001</v>
+        <v>87.37784765399999</v>
       </c>
       <c r="P33">
-        <v>330.491135478</v>
+        <v>336.786461346</v>
       </c>
       <c r="Q33">
-        <v>784.0911354780001</v>
+        <v>790.386461346</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.08320084689246804</v>
+        <v>0.08317680147324533</v>
       </c>
       <c r="T33">
         <v>0.8632055767493151</v>
       </c>
       <c r="U33">
-        <v>0.05790000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V33">
         <v>0.206</v>
       </c>
       <c r="W33">
-        <v>0.04597260000000001</v>
+        <v>0.04390820000000001</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>3.357416852407768</v>
+        <v>3.51527008597486</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4048,13 +4048,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.07160502830724935</v>
+        <v>0.07092786547765186</v>
       </c>
       <c r="C34">
-        <v>6709.590873449652</v>
+        <v>6963.88421315264</v>
       </c>
       <c r="D34">
-        <v>9672.930873449652</v>
+        <v>9927.22421315264</v>
       </c>
       <c r="E34">
         <v>140.9400000000001</v>
@@ -4081,37 +4081,37 @@
         <v>592.8</v>
       </c>
       <c r="M34">
-        <v>182.259936</v>
+        <v>174.075552</v>
       </c>
       <c r="N34">
-        <v>410.5400639999999</v>
+        <v>418.7244479999999</v>
       </c>
       <c r="O34">
-        <v>84.57125318399999</v>
+        <v>86.25723628799999</v>
       </c>
       <c r="P34">
-        <v>325.9688108159999</v>
+        <v>332.4672117119999</v>
       </c>
       <c r="Q34">
-        <v>779.568810816</v>
+        <v>786.067211712</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.08366734751066082</v>
+        <v>0.08364300217301744</v>
       </c>
       <c r="T34">
         <v>0.8739723365592944</v>
       </c>
       <c r="U34">
-        <v>0.05790000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V34">
         <v>0.206</v>
       </c>
       <c r="W34">
-        <v>0.04597260000000001</v>
+        <v>0.04390820000000001</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>3.252497575770025</v>
+        <v>3.405417895788145</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4130,13 +4130,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.07154996625869577</v>
+        <v>0.07085219593876443</v>
       </c>
       <c r="C35">
-        <v>6631.904838005507</v>
+        <v>6895.499148624062</v>
       </c>
       <c r="D35">
-        <v>9693.614838005507</v>
+        <v>9957.209148624062</v>
       </c>
       <c r="E35">
         <v>239.3099999999999</v>
@@ -4163,37 +4163,37 @@
         <v>592.8</v>
       </c>
       <c r="M35">
-        <v>187.955559</v>
+        <v>179.515413</v>
       </c>
       <c r="N35">
-        <v>404.844441</v>
+        <v>413.2845869999999</v>
       </c>
       <c r="O35">
-        <v>83.397954846</v>
+        <v>85.136624922</v>
       </c>
       <c r="P35">
-        <v>321.446486154</v>
+        <v>328.1479620779999</v>
       </c>
       <c r="Q35">
-        <v>775.0464861540001</v>
+        <v>781.747962078</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.08414777352044145</v>
+        <v>0.08412311931158872</v>
       </c>
       <c r="T35">
         <v>0.8850604921844971</v>
       </c>
       <c r="U35">
-        <v>0.05790000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V35">
         <v>0.206</v>
       </c>
       <c r="W35">
-        <v>0.04597260000000001</v>
+        <v>0.04390820000000001</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.153937043170933</v>
+        <v>3.302223414097595</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4212,13 +4212,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.07149490421014218</v>
+        <v>0.070776526399877</v>
       </c>
       <c r="C36">
-        <v>6554.30745060234</v>
+        <v>6827.295770388002</v>
       </c>
       <c r="D36">
-        <v>9714.38745060234</v>
+        <v>9987.375770388002</v>
       </c>
       <c r="E36">
         <v>337.6800000000003</v>
@@ -4245,37 +4245,37 @@
         <v>592.8</v>
       </c>
       <c r="M36">
-        <v>193.651182</v>
+        <v>184.9552740000001</v>
       </c>
       <c r="N36">
-        <v>399.1488179999999</v>
+        <v>407.8447259999999</v>
       </c>
       <c r="O36">
-        <v>82.22465650799998</v>
+        <v>84.01601355599999</v>
       </c>
       <c r="P36">
-        <v>316.9241614919999</v>
+        <v>323.828712444</v>
       </c>
       <c r="Q36">
-        <v>770.5241614920001</v>
+        <v>777.4287124440001</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.08464275789415483</v>
+        <v>0.08461778545435911</v>
       </c>
       <c r="T36">
         <v>0.8964846525256148</v>
       </c>
       <c r="U36">
-        <v>0.05790000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V36">
         <v>0.206</v>
       </c>
       <c r="W36">
-        <v>0.04597260000000001</v>
+        <v>0.04390820000000001</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>3.061174188960023</v>
+        <v>3.205099196035901</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4294,13 +4294,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.0721623821615886</v>
+        <v>0.07070085686098959</v>
       </c>
       <c r="C37">
-        <v>6209.975632913018</v>
+        <v>6759.275734787198</v>
       </c>
       <c r="D37">
-        <v>9468.425632913018</v>
+        <v>10017.7257347872</v>
       </c>
       <c r="E37">
         <v>436.0500000000002</v>
@@ -4327,45 +4327,45 @@
         <v>592.8</v>
       </c>
       <c r="M37">
-        <v>208.298475</v>
+        <v>190.395135</v>
       </c>
       <c r="N37">
-        <v>384.5015249999999</v>
+        <v>402.4048649999999</v>
       </c>
       <c r="O37">
-        <v>79.20731414999999</v>
+        <v>82.89540218999998</v>
       </c>
       <c r="P37">
-        <v>305.2942108499999</v>
+        <v>319.5094628099999</v>
       </c>
       <c r="Q37">
-        <v>758.89421085</v>
+        <v>773.1094628100001</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.08515297255629016</v>
+        <v>0.08512767209383015</v>
       </c>
       <c r="T37">
         <v>0.9082603254926133</v>
       </c>
       <c r="U37">
-        <v>0.06050000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V37">
         <v>0.206</v>
       </c>
       <c r="W37">
-        <v>0.048037</v>
+        <v>0.04390820000000001</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y37">
-        <v>2.845916178695019</v>
+        <v>3.113524933292018</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4376,13 +4376,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.07212796411303501</v>
+        <v>0.07062518732210218</v>
       </c>
       <c r="C38">
-        <v>6123.98352631034</v>
+        <v>6691.440718359185</v>
       </c>
       <c r="D38">
-        <v>9480.803526310339</v>
+        <v>10048.26071835918</v>
       </c>
       <c r="E38">
         <v>534.4199999999996</v>
@@ -4409,45 +4409,45 @@
         <v>592.8</v>
       </c>
       <c r="M38">
-        <v>214.24986</v>
+        <v>195.834996</v>
       </c>
       <c r="N38">
-        <v>378.5501399999999</v>
+        <v>396.9650039999999</v>
       </c>
       <c r="O38">
-        <v>77.98132883999999</v>
+        <v>81.77479082399999</v>
       </c>
       <c r="P38">
-        <v>300.5688111599999</v>
+        <v>315.1902131759999</v>
       </c>
       <c r="Q38">
-        <v>754.1688111600001</v>
+        <v>768.7902131760001</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.08567913142661721</v>
+        <v>0.08565349269078465</v>
       </c>
       <c r="T38">
         <v>0.9204039882398304</v>
       </c>
       <c r="U38">
-        <v>0.06050000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V38">
         <v>0.206</v>
       </c>
       <c r="W38">
-        <v>0.048037</v>
+        <v>0.04390820000000001</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y38">
-        <v>2.766862951509046</v>
+        <v>3.027038129589462</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4458,13 +4458,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.07209354606448143</v>
+        <v>0.07128396778321475</v>
       </c>
       <c r="C39">
-        <v>6038.023824841215</v>
+        <v>6333.31533467125</v>
       </c>
       <c r="D39">
-        <v>9493.213824841216</v>
+        <v>9788.50533467125</v>
       </c>
       <c r="E39">
         <v>632.79</v>
@@ -4491,37 +4491,37 @@
         <v>592.8</v>
       </c>
       <c r="M39">
-        <v>220.201245</v>
+        <v>210.374082</v>
       </c>
       <c r="N39">
-        <v>372.5987549999999</v>
+        <v>382.4259179999999</v>
       </c>
       <c r="O39">
-        <v>76.75534352999999</v>
+        <v>78.77973910799999</v>
       </c>
       <c r="P39">
-        <v>295.8434114699999</v>
+        <v>303.6461788919999</v>
       </c>
       <c r="Q39">
-        <v>749.44341147</v>
+        <v>757.246178892</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.08622199375314513</v>
+        <v>0.08619600600510277</v>
       </c>
       <c r="T39">
         <v>0.9329331640901336</v>
       </c>
       <c r="U39">
-        <v>0.06050000000000001</v>
+        <v>0.0578</v>
       </c>
       <c r="V39">
         <v>0.206</v>
       </c>
       <c r="W39">
-        <v>0.048037</v>
+        <v>0.04589320000000001</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>2.692082871738531</v>
+        <v>2.817837607961612</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4540,13 +4540,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.07205912801592784</v>
+        <v>0.07122814824432734</v>
       </c>
       <c r="C40">
-        <v>5952.096655926649</v>
+        <v>6256.432933725979</v>
       </c>
       <c r="D40">
-        <v>9505.656655926648</v>
+        <v>9809.992933725978</v>
       </c>
       <c r="E40">
         <v>731.1599999999999</v>
@@ -4573,37 +4573,37 @@
         <v>592.8</v>
       </c>
       <c r="M40">
-        <v>226.15263</v>
+        <v>216.059868</v>
       </c>
       <c r="N40">
-        <v>366.6473699999999</v>
+        <v>376.7401319999999</v>
       </c>
       <c r="O40">
-        <v>75.52935821999999</v>
+        <v>77.60846719199999</v>
       </c>
       <c r="P40">
-        <v>291.1180117799999</v>
+        <v>299.1316648079999</v>
       </c>
       <c r="Q40">
-        <v>744.7180117800001</v>
+        <v>752.731664808</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.08678236776762556</v>
+        <v>0.08675601974891506</v>
       </c>
       <c r="T40">
         <v>0.9458665069033501</v>
       </c>
       <c r="U40">
-        <v>0.06050000000000001</v>
+        <v>0.0578</v>
       </c>
       <c r="V40">
         <v>0.206</v>
       </c>
       <c r="W40">
-        <v>0.048037</v>
+        <v>0.04589320000000001</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>2.621238585640149</v>
+        <v>2.743683986699463</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4622,13 +4622,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.07202470996737426</v>
+        <v>0.07117232870543992</v>
       </c>
       <c r="C41">
-        <v>5866.202147656564</v>
+        <v>6179.645078920716</v>
       </c>
       <c r="D41">
-        <v>9518.132147656564</v>
+        <v>9831.575078920716</v>
       </c>
       <c r="E41">
         <v>829.5300000000002</v>
@@ -4655,37 +4655,37 @@
         <v>592.8</v>
       </c>
       <c r="M41">
-        <v>232.104015</v>
+        <v>221.745654</v>
       </c>
       <c r="N41">
-        <v>360.695985</v>
+        <v>371.0543459999999</v>
       </c>
       <c r="O41">
-        <v>74.30337290999999</v>
+        <v>76.43719527599998</v>
       </c>
       <c r="P41">
-        <v>286.3926120899999</v>
+        <v>294.6171507239999</v>
       </c>
       <c r="Q41">
-        <v>739.9926120900001</v>
+        <v>748.217150724</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.08736111470061354</v>
+        <v>0.08733439459908182</v>
       </c>
       <c r="T41">
         <v>0.9592238937432294</v>
       </c>
       <c r="U41">
-        <v>0.06050000000000001</v>
+        <v>0.0578</v>
       </c>
       <c r="V41">
         <v>0.206</v>
       </c>
       <c r="W41">
-        <v>0.048037</v>
+        <v>0.04589320000000001</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>2.554027339854504</v>
+        <v>2.673333115245631</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4704,13 +4704,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.07284781191882067</v>
+        <v>0.07111650916655249</v>
       </c>
       <c r="C42">
-        <v>5478.182353862724</v>
+        <v>6102.952395640493</v>
       </c>
       <c r="D42">
-        <v>9228.482353862724</v>
+        <v>9853.252395640493</v>
       </c>
       <c r="E42">
         <v>927.9000000000001</v>
@@ -4737,45 +4737,45 @@
         <v>592.8</v>
       </c>
       <c r="M42">
-        <v>248.67936</v>
+        <v>227.43144</v>
       </c>
       <c r="N42">
-        <v>344.1206399999999</v>
+        <v>365.3685599999999</v>
       </c>
       <c r="O42">
-        <v>70.88885183999999</v>
+        <v>75.26592335999999</v>
       </c>
       <c r="P42">
-        <v>273.23178816</v>
+        <v>290.1026366399999</v>
       </c>
       <c r="Q42">
-        <v>726.8317881600001</v>
+        <v>743.70263664</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.08795915319803446</v>
+        <v>0.08793204861092081</v>
       </c>
       <c r="T42">
         <v>0.9730265268111044</v>
       </c>
       <c r="U42">
-        <v>0.06320000000000001</v>
+        <v>0.0578</v>
       </c>
       <c r="V42">
         <v>0.206</v>
       </c>
       <c r="W42">
-        <v>0.0501808</v>
+        <v>0.04589320000000001</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y42">
-        <v>2.383792527051702</v>
+        <v>2.60649978736449</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4786,13 +4786,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.0728348318702671</v>
+        <v>0.07106068962766507</v>
       </c>
       <c r="C43">
-        <v>5384.243161851608</v>
+        <v>6026.355514798081</v>
       </c>
       <c r="D43">
-        <v>9232.913161851608</v>
+        <v>9875.025514798081</v>
       </c>
       <c r="E43">
         <v>1026.27</v>
@@ -4819,45 +4819,45 @@
         <v>592.8</v>
       </c>
       <c r="M43">
-        <v>254.8963440000001</v>
+        <v>233.117226</v>
       </c>
       <c r="N43">
-        <v>337.9036559999999</v>
+        <v>359.6827739999999</v>
       </c>
       <c r="O43">
-        <v>69.60815313599998</v>
+        <v>74.09465144399998</v>
       </c>
       <c r="P43">
-        <v>268.2955028639999</v>
+        <v>285.5881225559999</v>
       </c>
       <c r="Q43">
-        <v>721.895502864</v>
+        <v>739.1881225560001</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.08857746418689337</v>
+        <v>0.08854996208078825</v>
       </c>
       <c r="T43">
         <v>0.9872970457456872</v>
       </c>
       <c r="U43">
-        <v>0.06320000000000001</v>
+        <v>0.0578</v>
       </c>
       <c r="V43">
         <v>0.206</v>
       </c>
       <c r="W43">
-        <v>0.0501808</v>
+        <v>0.04589320000000001</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y43">
-        <v>2.325651245904099</v>
+        <v>2.542926621819015</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4868,13 +4868,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.07282185182171351</v>
+        <v>0.07217205008877765</v>
       </c>
       <c r="C44">
-        <v>5290.308226551194</v>
+        <v>5511.836111445677</v>
       </c>
       <c r="D44">
-        <v>9237.348226551194</v>
+        <v>9458.876111445677</v>
       </c>
       <c r="E44">
         <v>1124.64</v>
@@ -4901,37 +4901,37 @@
         <v>592.8</v>
       </c>
       <c r="M44">
-        <v>261.113328</v>
+        <v>253.263402</v>
       </c>
       <c r="N44">
-        <v>331.6866719999999</v>
+        <v>339.5365979999999</v>
       </c>
       <c r="O44">
-        <v>68.327454432</v>
+        <v>69.94453918799999</v>
       </c>
       <c r="P44">
-        <v>263.359217568</v>
+        <v>269.5920588119999</v>
       </c>
       <c r="Q44">
-        <v>716.9592175680001</v>
+        <v>723.192058812</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.08921709624433362</v>
+        <v>0.08918918291168559</v>
       </c>
       <c r="T44">
         <v>1.002059651540083</v>
       </c>
       <c r="U44">
-        <v>0.06320000000000001</v>
+        <v>0.06130000000000001</v>
       </c>
       <c r="V44">
         <v>0.206</v>
       </c>
       <c r="W44">
-        <v>0.0501808</v>
+        <v>0.04867220000000001</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>2.270278597192097</v>
+        <v>2.340646123043075</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4950,13 +4950,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.07441354577315992</v>
+        <v>0.07214402054989022</v>
       </c>
       <c r="C45">
-        <v>4678.089596389547</v>
+        <v>5423.530176469279</v>
       </c>
       <c r="D45">
-        <v>8723.499596389547</v>
+        <v>9468.940176469279</v>
       </c>
       <c r="E45">
         <v>1223.01</v>
@@ -4983,45 +4983,45 @@
         <v>592.8</v>
       </c>
       <c r="M45">
-        <v>287.2108890000001</v>
+        <v>259.293483</v>
       </c>
       <c r="N45">
-        <v>305.5891109999999</v>
+        <v>333.5065169999999</v>
       </c>
       <c r="O45">
-        <v>62.95135686599998</v>
+        <v>68.70234250199999</v>
       </c>
       <c r="P45">
-        <v>242.6377541339999</v>
+        <v>264.804174498</v>
       </c>
       <c r="Q45">
-        <v>696.2377541340001</v>
+        <v>718.4041744980001</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.08987917153185949</v>
+        <v>0.08985083254366705</v>
       </c>
       <c r="T45">
         <v>1.017340243502703</v>
       </c>
       <c r="U45">
-        <v>0.06790000000000002</v>
+        <v>0.06130000000000001</v>
       </c>
       <c r="V45">
         <v>0.206</v>
       </c>
       <c r="W45">
-        <v>0.05391260000000001</v>
+        <v>0.04867220000000001</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y45">
-        <v>2.063988597591089</v>
+        <v>2.286212492274632</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5032,13 +5032,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.07443788372460633</v>
+        <v>0.07309419901100281</v>
       </c>
       <c r="C46">
-        <v>4572.305916256569</v>
+        <v>4995.522988669124</v>
       </c>
       <c r="D46">
-        <v>8716.085916256568</v>
+        <v>9139.302988669124</v>
       </c>
       <c r="E46">
         <v>1321.38</v>
@@ -5065,37 +5065,37 @@
         <v>592.8</v>
       </c>
       <c r="M46">
-        <v>293.8902120000001</v>
+        <v>277.442748</v>
       </c>
       <c r="N46">
-        <v>298.9097879999999</v>
+        <v>315.357252</v>
       </c>
       <c r="O46">
-        <v>61.57541632799998</v>
+        <v>64.96359391199999</v>
       </c>
       <c r="P46">
-        <v>237.3343716719999</v>
+        <v>250.393658088</v>
       </c>
       <c r="Q46">
-        <v>690.934371672</v>
+        <v>703.9936580880001</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.09056489236536844</v>
+        <v>0.09053611251964785</v>
       </c>
       <c r="T46">
         <v>1.03316657089256</v>
       </c>
       <c r="U46">
-        <v>0.06790000000000002</v>
+        <v>0.0641</v>
       </c>
       <c r="V46">
         <v>0.206</v>
       </c>
       <c r="W46">
-        <v>0.05391260000000001</v>
+        <v>0.05089540000000001</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.017079765827654</v>
+        <v>2.136657037436783</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5114,13 +5114,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.07946442167605275</v>
+        <v>0.07308840147211539</v>
       </c>
       <c r="C47">
-        <v>3172.510421182733</v>
+        <v>4899.094673107286</v>
       </c>
       <c r="D47">
-        <v>7414.660421182733</v>
+        <v>9141.244673107287</v>
       </c>
       <c r="E47">
         <v>1419.75</v>
@@ -5147,45 +5147,45 @@
         <v>592.8</v>
       </c>
       <c r="M47">
-        <v>362.5426350000001</v>
+        <v>283.7482650000001</v>
       </c>
       <c r="N47">
-        <v>230.2573649999999</v>
+        <v>309.0517349999999</v>
       </c>
       <c r="O47">
-        <v>47.43301718999998</v>
+        <v>63.66465740999998</v>
       </c>
       <c r="P47">
-        <v>182.8243478099999</v>
+        <v>245.3870775899999</v>
       </c>
       <c r="Q47">
-        <v>636.42434781</v>
+        <v>698.98707759</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.09127554850191408</v>
+        <v>0.0912463117674825</v>
       </c>
       <c r="T47">
         <v>1.049568401096594</v>
       </c>
       <c r="U47">
-        <v>0.0819</v>
+        <v>0.0641</v>
       </c>
       <c r="V47">
         <v>0.206</v>
       </c>
       <c r="W47">
-        <v>0.06502860000000001</v>
+        <v>0.05089540000000001</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y47">
-        <v>1.635118032393624</v>
+        <v>2.089175769938187</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5196,13 +5196,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.07959991962749915</v>
+        <v>0.07308260393322796</v>
       </c>
       <c r="C48">
-        <v>3044.41634761057</v>
+        <v>4802.667182759278</v>
       </c>
       <c r="D48">
-        <v>7384.936347610571</v>
+        <v>9143.187182759279</v>
       </c>
       <c r="E48">
         <v>1518.12</v>
@@ -5229,45 +5229,45 @@
         <v>592.8</v>
       </c>
       <c r="M48">
-        <v>370.599138</v>
+        <v>290.0537820000001</v>
       </c>
       <c r="N48">
-        <v>222.2008619999999</v>
+        <v>302.7462179999999</v>
       </c>
       <c r="O48">
-        <v>45.77337757199999</v>
+        <v>62.36572090799998</v>
       </c>
       <c r="P48">
-        <v>176.4274844279999</v>
+        <v>240.3804970919999</v>
       </c>
       <c r="Q48">
-        <v>630.0274844280001</v>
+        <v>693.9804970920001</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.09201252523610955</v>
+        <v>0.09198281469116287</v>
       </c>
       <c r="T48">
         <v>1.066577706493369</v>
       </c>
       <c r="U48">
-        <v>0.0819</v>
+        <v>0.0641</v>
       </c>
       <c r="V48">
         <v>0.206</v>
       </c>
       <c r="W48">
-        <v>0.06502860000000001</v>
+        <v>0.05089540000000001</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y48">
-        <v>1.599571988211154</v>
+        <v>2.043758905374314</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5278,13 +5278,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.07973541757894557</v>
+        <v>0.07307680639434054</v>
       </c>
       <c r="C49">
-        <v>2916.559639679671</v>
+        <v>4706.240518151285</v>
       </c>
       <c r="D49">
-        <v>7355.449639679671</v>
+        <v>9145.130518151285</v>
       </c>
       <c r="E49">
         <v>1616.49</v>
@@ -5311,45 +5311,45 @@
         <v>592.8</v>
       </c>
       <c r="M49">
-        <v>378.655641</v>
+        <v>296.359299</v>
       </c>
       <c r="N49">
-        <v>214.144359</v>
+        <v>296.4407009999999</v>
       </c>
       <c r="O49">
-        <v>44.11373795399999</v>
+        <v>61.06678440599999</v>
       </c>
       <c r="P49">
-        <v>170.030621046</v>
+        <v>235.373916594</v>
       </c>
       <c r="Q49">
-        <v>623.6306210460001</v>
+        <v>688.9739165940001</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.09277731241310484</v>
+        <v>0.092747110178001</v>
       </c>
       <c r="T49">
         <v>1.084228872471155</v>
       </c>
       <c r="U49">
-        <v>0.0819</v>
+        <v>0.0641</v>
       </c>
       <c r="V49">
         <v>0.206</v>
       </c>
       <c r="W49">
-        <v>0.06502860000000001</v>
+        <v>0.05089540000000001</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y49">
-        <v>1.56553854165347</v>
+        <v>2.000274673345073</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5360,13 +5360,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.07987091553039199</v>
+        <v>0.07753011285545311</v>
       </c>
       <c r="C50">
-        <v>2788.93746542404</v>
+        <v>3324.355738051734</v>
       </c>
       <c r="D50">
-        <v>7326.19746542404</v>
+        <v>7861.615738051734</v>
       </c>
       <c r="E50">
         <v>1714.86</v>
@@ -5393,37 +5393,37 @@
         <v>592.8</v>
       </c>
       <c r="M50">
-        <v>386.712144</v>
+        <v>357.909408</v>
       </c>
       <c r="N50">
-        <v>206.0878559999999</v>
+        <v>234.8905919999999</v>
       </c>
       <c r="O50">
-        <v>42.45409833599999</v>
+        <v>48.38746195199999</v>
       </c>
       <c r="P50">
-        <v>163.6337576639999</v>
+        <v>186.5031300479999</v>
       </c>
       <c r="Q50">
-        <v>617.2337576640001</v>
+        <v>640.103130048</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.09357151448152304</v>
+        <v>0.09354080164510213</v>
       </c>
       <c r="T50">
         <v>1.102558929448086</v>
       </c>
       <c r="U50">
-        <v>0.0819</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V50">
         <v>0.206</v>
       </c>
       <c r="W50">
-        <v>0.06502860000000001</v>
+        <v>0.06018520000000001</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>1.532923155369023</v>
+        <v>1.656285045181042</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5442,13 +5442,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.0800064134818384</v>
+        <v>0.07761721331656571</v>
       </c>
       <c r="C51">
-        <v>2661.547037749451</v>
+        <v>3204.464357500225</v>
       </c>
       <c r="D51">
-        <v>7297.177037749451</v>
+        <v>7840.094357500225</v>
       </c>
       <c r="E51">
         <v>1813.23</v>
@@ -5475,37 +5475,37 @@
         <v>592.8</v>
       </c>
       <c r="M51">
-        <v>394.768647</v>
+        <v>365.365854</v>
       </c>
       <c r="N51">
-        <v>198.031353</v>
+        <v>227.4341459999999</v>
       </c>
       <c r="O51">
-        <v>40.79445871799999</v>
+        <v>46.85143407599999</v>
       </c>
       <c r="P51">
-        <v>157.236894282</v>
+        <v>180.582711924</v>
       </c>
       <c r="Q51">
-        <v>610.8368942820001</v>
+        <v>634.1827119240002</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.09439686172909489</v>
+        <v>0.09436561826777587</v>
       </c>
       <c r="T51">
         <v>1.121607812188819</v>
       </c>
       <c r="U51">
-        <v>0.0819</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V51">
         <v>0.206</v>
       </c>
       <c r="W51">
-        <v>0.06502860000000001</v>
+        <v>0.06018520000000001</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>1.501639009341084</v>
+        <v>1.622483309565102</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5524,13 +5524,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.1008886406532657</v>
+        <v>0.07770431377767828</v>
       </c>
       <c r="C52">
-        <v>-202.9342114191832</v>
+        <v>3084.690485959125</v>
       </c>
       <c r="D52">
-        <v>4531.065788580817</v>
+        <v>7818.690485959125</v>
       </c>
       <c r="E52">
         <v>1911.6</v>
@@ -5557,45 +5557,45 @@
         <v>592.8</v>
       </c>
       <c r="M52">
-        <v>643.8316500000001</v>
+        <v>372.8223</v>
       </c>
       <c r="N52">
-        <v>-51.03165000000013</v>
+        <v>219.9776999999999</v>
       </c>
       <c r="O52">
-        <v>-10.51251990000003</v>
+        <v>45.31540619999998</v>
       </c>
       <c r="P52">
-        <v>-40.5191301000001</v>
+        <v>174.6622937999999</v>
       </c>
       <c r="Q52">
-        <v>413.0808699</v>
+        <v>628.2622938000001</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.09570533864108452</v>
+        <v>0.09522342755535654</v>
       </c>
       <c r="T52">
-        <v>1.151807250472251</v>
+        <v>1.141418650239181</v>
       </c>
       <c r="U52">
-        <v>0.1309</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V52">
-        <v>0.189671942968321</v>
+        <v>0.206</v>
       </c>
       <c r="W52">
-        <v>0.1060719426654468</v>
+        <v>0.06018520000000001</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y52">
-        <v>0.920737587224859</v>
+        <v>1.5900336433738</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5606,13 +5606,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.1017396406532657</v>
+        <v>0.07779141423879085</v>
       </c>
       <c r="C53">
-        <v>-370.2345252548193</v>
+        <v>2965.033163631319</v>
       </c>
       <c r="D53">
-        <v>4462.135474745181</v>
+        <v>7797.403163631319</v>
       </c>
       <c r="E53">
         <v>2009.97</v>
@@ -5639,45 +5639,45 @@
         <v>592.8</v>
       </c>
       <c r="M53">
-        <v>656.7082830000001</v>
+        <v>380.278746</v>
       </c>
       <c r="N53">
-        <v>-63.9082830000001</v>
+        <v>212.5212539999999</v>
       </c>
       <c r="O53">
-        <v>-13.16510629800002</v>
+        <v>43.77937832399999</v>
       </c>
       <c r="P53">
-        <v>-50.74317670200008</v>
+        <v>168.7418756759999</v>
       </c>
       <c r="Q53">
-        <v>402.8568232980001</v>
+        <v>622.3418756760001</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.09672381493988218</v>
+        <v>0.0961162494669201</v>
       </c>
       <c r="T53">
-        <v>1.175313520890052</v>
+        <v>1.162038093924252</v>
       </c>
       <c r="U53">
-        <v>0.1309</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V53">
-        <v>0.1859528852630598</v>
+        <v>0.206</v>
       </c>
       <c r="W53">
-        <v>0.1065587673190655</v>
+        <v>0.06018520000000001</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y53">
-        <v>0.9026839090439794</v>
+        <v>1.558856513111569</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5688,13 +5688,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.1025906406532657</v>
+        <v>0.07787851469990342</v>
       </c>
       <c r="C54">
-        <v>-535.4690163985697</v>
+        <v>2845.491441143964</v>
       </c>
       <c r="D54">
-        <v>4395.27098360143</v>
+        <v>7776.231441143964</v>
       </c>
       <c r="E54">
         <v>2108.34</v>
@@ -5721,45 +5721,45 @@
         <v>592.8</v>
       </c>
       <c r="M54">
-        <v>669.584916</v>
+        <v>387.735192</v>
       </c>
       <c r="N54">
-        <v>-76.78491600000007</v>
+        <v>205.0648079999999</v>
       </c>
       <c r="O54">
-        <v>-15.81769269600001</v>
+        <v>42.24335044799999</v>
       </c>
       <c r="P54">
-        <v>-60.96722330400005</v>
+        <v>162.8214575519999</v>
       </c>
       <c r="Q54">
-        <v>392.6327766960001</v>
+        <v>616.421457552</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.09778472775112973</v>
+        <v>0.09704627229146548</v>
       </c>
       <c r="T54">
-        <v>1.199799219241928</v>
+        <v>1.183516681096201</v>
       </c>
       <c r="U54">
-        <v>0.1309</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V54">
-        <v>0.1823768682387702</v>
+        <v>0.206</v>
       </c>
       <c r="W54">
-        <v>0.107026867947545</v>
+        <v>0.06018520000000001</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y54">
-        <v>0.8853246031008261</v>
+        <v>1.528878503244039</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5770,13 +5770,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.1034416406532657</v>
+        <v>0.07796561516101601</v>
       </c>
       <c r="C55">
-        <v>-698.7291819916072</v>
+        <v>2726.064379407345</v>
       </c>
       <c r="D55">
-        <v>4330.380818008393</v>
+        <v>7755.174379407345</v>
       </c>
       <c r="E55">
         <v>2206.71</v>
@@ -5803,45 +5803,45 @@
         <v>592.8</v>
       </c>
       <c r="M55">
-        <v>682.4615490000001</v>
+        <v>395.1916380000001</v>
       </c>
       <c r="N55">
-        <v>-89.66154900000015</v>
+        <v>197.6083619999999</v>
       </c>
       <c r="O55">
-        <v>-18.47027909400003</v>
+        <v>40.70732257199998</v>
       </c>
       <c r="P55">
-        <v>-71.19126990600012</v>
+        <v>156.9010394279999</v>
       </c>
       <c r="Q55">
-        <v>382.408730094</v>
+        <v>610.501039428</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.09889078578838781</v>
+        <v>0.09801587055535321</v>
       </c>
       <c r="T55">
-        <v>1.225326862204523</v>
+        <v>1.205909250700998</v>
       </c>
       <c r="U55">
-        <v>0.1309</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V55">
-        <v>0.178935795253133</v>
+        <v>0.206</v>
       </c>
       <c r="W55">
-        <v>0.1074773044013649</v>
+        <v>0.06018520000000001</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y55">
-        <v>0.8686203653064707</v>
+        <v>1.500031739031887</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5852,13 +5852,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.1042926406532657</v>
+        <v>0.09736363908018036</v>
       </c>
       <c r="C56">
-        <v>-860.101194466476</v>
+        <v>-289.7695698517628</v>
       </c>
       <c r="D56">
-        <v>4267.378805533524</v>
+        <v>4837.710430148238</v>
       </c>
       <c r="E56">
         <v>2305.08</v>
@@ -5885,37 +5885,37 @@
         <v>592.8</v>
       </c>
       <c r="M56">
-        <v>695.3381820000002</v>
+        <v>630.0008280000001</v>
       </c>
       <c r="N56">
-        <v>-102.5381820000002</v>
+        <v>-37.20082800000012</v>
       </c>
       <c r="O56">
-        <v>-21.12286549200005</v>
+        <v>-7.663370568000024</v>
       </c>
       <c r="P56">
-        <v>-81.41531650800019</v>
+        <v>-29.53745743200009</v>
       </c>
       <c r="Q56">
-        <v>372.184683492</v>
+        <v>424.062542568</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.1000449333055267</v>
+        <v>0.09942101684229773</v>
       </c>
       <c r="T56">
-        <v>1.25196440268723</v>
+        <v>1.238360666103874</v>
       </c>
       <c r="U56">
-        <v>0.1309</v>
+        <v>0.1186</v>
       </c>
       <c r="V56">
-        <v>0.175622169415112</v>
+        <v>0.1938359357203892</v>
       </c>
       <c r="W56">
-        <v>0.1079110580235619</v>
+        <v>0.09561105802356185</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.8525348029859804</v>
+        <v>0.9409511442737341</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5934,13 +5934,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.1051436406532657</v>
+        <v>0.09809163908018036</v>
       </c>
       <c r="C57">
-        <v>-1019.666283334171</v>
+        <v>-455.489785968487</v>
       </c>
       <c r="D57">
-        <v>4206.18371666583</v>
+        <v>4770.360214031513</v>
       </c>
       <c r="E57">
         <v>2403.45</v>
@@ -5967,37 +5967,37 @@
         <v>592.8</v>
       </c>
       <c r="M57">
-        <v>708.2148150000002</v>
+        <v>641.6675100000001</v>
       </c>
       <c r="N57">
-        <v>-115.4148150000002</v>
+        <v>-48.86751000000015</v>
       </c>
       <c r="O57">
-        <v>-23.77545189000005</v>
+        <v>-10.06670706000003</v>
       </c>
       <c r="P57">
-        <v>-91.63936311000016</v>
+        <v>-38.80080294000012</v>
       </c>
       <c r="Q57">
-        <v>361.96063689</v>
+        <v>414.79919706</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.1012503762678717</v>
+        <v>0.1006125949943488</v>
       </c>
       <c r="T57">
-        <v>1.279785833858057</v>
+        <v>1.265879792017294</v>
       </c>
       <c r="U57">
-        <v>0.1309</v>
+        <v>0.1186</v>
       </c>
       <c r="V57">
-        <v>0.17242903906211</v>
+        <v>0.1903116459800185</v>
       </c>
       <c r="W57">
-        <v>0.1083290387867698</v>
+        <v>0.09602903878676981</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.8370341702044172</v>
+        <v>0.9238429416505751</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6016,13 +6016,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1059946406532657</v>
+        <v>0.09881963908018035</v>
       </c>
       <c r="C58">
-        <v>-1177.50108458618</v>
+        <v>-619.3604626246033</v>
       </c>
       <c r="D58">
-        <v>4146.71891541382</v>
+        <v>4704.859537375397</v>
       </c>
       <c r="E58">
         <v>2501.82</v>
@@ -6049,37 +6049,37 @@
         <v>592.8</v>
       </c>
       <c r="M58">
-        <v>721.0914480000001</v>
+        <v>653.3341920000001</v>
       </c>
       <c r="N58">
-        <v>-128.2914480000002</v>
+        <v>-60.53419200000019</v>
       </c>
       <c r="O58">
-        <v>-26.42803828800004</v>
+        <v>-12.47004355200004</v>
       </c>
       <c r="P58">
-        <v>-101.8634097120001</v>
+        <v>-48.06414844800015</v>
       </c>
       <c r="Q58">
-        <v>351.736590288</v>
+        <v>405.535851552</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.1025106120921415</v>
+        <v>0.1018583357896749</v>
       </c>
       <c r="T58">
-        <v>1.308871875536649</v>
+        <v>1.294649787290414</v>
       </c>
       <c r="U58">
-        <v>0.1309</v>
+        <v>0.1186</v>
       </c>
       <c r="V58">
-        <v>0.169349949078858</v>
+        <v>0.1869132237303753</v>
       </c>
       <c r="W58">
-        <v>0.1087320916655775</v>
+        <v>0.09643209166557749</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.822087131450767</v>
+        <v>0.9073457462639577</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6098,13 +6098,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1068456406532657</v>
+        <v>0.09954763908018036</v>
       </c>
       <c r="C59">
-        <v>-1333.67796087176</v>
+        <v>-781.4567546408871</v>
       </c>
       <c r="D59">
-        <v>4088.912039128242</v>
+        <v>4641.133245359114</v>
       </c>
       <c r="E59">
         <v>2600.190000000001</v>
@@ -6131,37 +6131,37 @@
         <v>592.8</v>
       </c>
       <c r="M59">
-        <v>733.9680810000002</v>
+        <v>665.0008740000002</v>
       </c>
       <c r="N59">
-        <v>-141.1680810000003</v>
+        <v>-72.20087400000023</v>
       </c>
       <c r="O59">
-        <v>-29.08062468600005</v>
+        <v>-14.87338004400005</v>
       </c>
       <c r="P59">
-        <v>-112.0874563140002</v>
+        <v>-57.32749395600018</v>
       </c>
       <c r="Q59">
-        <v>341.512543686</v>
+        <v>396.272506044</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.1038294635361448</v>
+        <v>0.1031620180173418</v>
       </c>
       <c r="T59">
-        <v>1.339310756363083</v>
+        <v>1.324757921878563</v>
       </c>
       <c r="U59">
-        <v>0.1309</v>
+        <v>0.1186</v>
       </c>
       <c r="V59">
-        <v>0.1663788973406324</v>
+        <v>0.1836340443666845</v>
       </c>
       <c r="W59">
-        <v>0.1091210023381112</v>
+        <v>0.09682100233811122</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.8076645501972446</v>
+        <v>0.8914273998382742</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6180,13 +6180,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.1579671756462305</v>
+        <v>0.1002756390801804</v>
       </c>
       <c r="C60">
-        <v>-3295.618641751913</v>
+        <v>-941.8497994306581</v>
       </c>
       <c r="D60">
-        <v>2225.341358248087</v>
+        <v>4579.110200569342</v>
       </c>
       <c r="E60">
         <v>2698.56</v>
@@ -6213,45 +6213,45 @@
         <v>592.8</v>
       </c>
       <c r="M60">
-        <v>1231.238268</v>
+        <v>676.6675560000001</v>
       </c>
       <c r="N60">
-        <v>-638.4382680000001</v>
+        <v>-83.86755600000015</v>
       </c>
       <c r="O60">
-        <v>-131.518283208</v>
+        <v>-17.27671653600003</v>
       </c>
       <c r="P60">
-        <v>-506.919984792</v>
+        <v>-66.59083946400011</v>
       </c>
       <c r="Q60">
-        <v>-53.3199847919999</v>
+        <v>387.009160536</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.107660010270255</v>
+        <v>0.104527780351088</v>
       </c>
       <c r="T60">
-        <v>1.427719163594864</v>
+        <v>1.356299777161386</v>
       </c>
       <c r="U60">
-        <v>0.2158</v>
+        <v>0.1186</v>
       </c>
       <c r="V60">
-        <v>0.09918210241983803</v>
+        <v>0.1804679401534658</v>
       </c>
       <c r="W60">
-        <v>0.194396502297799</v>
+        <v>0.09719650229779897</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y60">
-        <v>0.4814665166011555</v>
+        <v>0.8760579619100282</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6262,13 +6262,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.1596671756462305</v>
+        <v>0.1010036390801803</v>
       </c>
       <c r="C61">
-        <v>-3427.212266449299</v>
+        <v>-1100.606981898331</v>
       </c>
       <c r="D61">
-        <v>2192.117733550701</v>
+        <v>4518.723018101669</v>
       </c>
       <c r="E61">
         <v>2796.93</v>
@@ -6295,45 +6295,45 @@
         <v>592.8</v>
       </c>
       <c r="M61">
-        <v>1252.466514</v>
+        <v>688.334238</v>
       </c>
       <c r="N61">
-        <v>-659.6665140000002</v>
+        <v>-95.53423800000007</v>
       </c>
       <c r="O61">
-        <v>-135.8913018840001</v>
+        <v>-19.68005302800002</v>
       </c>
       <c r="P61">
-        <v>-523.7752121160001</v>
+        <v>-75.85418497200006</v>
       </c>
       <c r="Q61">
-        <v>-70.17521211600001</v>
+        <v>377.7458150280001</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.1091687910085539</v>
+        <v>0.1059601652376999</v>
       </c>
       <c r="T61">
-        <v>1.462541582219129</v>
+        <v>1.389380259531175</v>
       </c>
       <c r="U61">
-        <v>0.2158</v>
+        <v>0.1186</v>
       </c>
       <c r="V61">
-        <v>0.09750104983645094</v>
+        <v>0.1774091615067969</v>
       </c>
       <c r="W61">
-        <v>0.1947592734452939</v>
+        <v>0.09755927344529389</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y61">
-        <v>0.4733060671672376</v>
+        <v>0.861209521877655</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6344,13 +6344,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.1613671756462305</v>
+        <v>0.1017316390801803</v>
       </c>
       <c r="C62">
-        <v>-3557.828448171728</v>
+        <v>-1257.792178650605</v>
       </c>
       <c r="D62">
-        <v>2159.871551828272</v>
+        <v>4459.907821349395</v>
       </c>
       <c r="E62">
         <v>2895.3</v>
@@ -6377,45 +6377,45 @@
         <v>592.8</v>
       </c>
       <c r="M62">
-        <v>1273.69476</v>
+        <v>700.0009200000001</v>
       </c>
       <c r="N62">
-        <v>-680.8947600000001</v>
+        <v>-107.2009200000001</v>
       </c>
       <c r="O62">
-        <v>-140.26432056</v>
+        <v>-22.08338952000003</v>
       </c>
       <c r="P62">
-        <v>-540.6304394400001</v>
+        <v>-85.11753048000008</v>
       </c>
       <c r="Q62">
-        <v>-87.03043944000001</v>
+        <v>368.4824695200001</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.1107530107837678</v>
+        <v>0.1074641693686424</v>
       </c>
       <c r="T62">
-        <v>1.499105121774608</v>
+        <v>1.424114766019455</v>
       </c>
       <c r="U62">
-        <v>0.2158</v>
+        <v>0.1186</v>
       </c>
       <c r="V62">
-        <v>0.09587603233917677</v>
+        <v>0.1744523421483503</v>
       </c>
       <c r="W62">
-        <v>0.1951099522212057</v>
+        <v>0.09790995222120566</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y62">
-        <v>0.4654176327144502</v>
+        <v>0.8468560298463607</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6426,13 +6426,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.1630671756462305</v>
+        <v>0.1024596390801804</v>
       </c>
       <c r="C63">
-        <v>-3687.509696335365</v>
+        <v>-1413.465983380948</v>
       </c>
       <c r="D63">
-        <v>2128.560303664634</v>
+        <v>4402.604016619051</v>
       </c>
       <c r="E63">
         <v>2993.67</v>
@@ -6459,45 +6459,45 @@
         <v>592.8</v>
       </c>
       <c r="M63">
-        <v>1294.923006</v>
+        <v>711.667602</v>
       </c>
       <c r="N63">
-        <v>-702.123006</v>
+        <v>-118.867602</v>
       </c>
       <c r="O63">
-        <v>-144.637339236</v>
+        <v>-24.48672601200001</v>
       </c>
       <c r="P63">
-        <v>-557.485666764</v>
+        <v>-94.38087598800003</v>
       </c>
       <c r="Q63">
-        <v>-103.8856667639999</v>
+        <v>359.2191240120001</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.1124184725987362</v>
+        <v>0.1090453019165563</v>
       </c>
       <c r="T63">
-        <v>1.537543714640623</v>
+        <v>1.460630529250723</v>
       </c>
       <c r="U63">
-        <v>0.2158</v>
+        <v>0.1186</v>
       </c>
       <c r="V63">
-        <v>0.0943042941041083</v>
+        <v>0.171592467686902</v>
       </c>
       <c r="W63">
-        <v>0.1954491333323334</v>
+        <v>0.09824913333233344</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y63">
-        <v>0.4577878354568364</v>
+        <v>0.8329731441111745</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6508,13 +6508,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.1647671756462305</v>
+        <v>0.1031876390801804</v>
       </c>
       <c r="C64">
-        <v>-3816.296090576667</v>
+        <v>-1567.685915099181</v>
       </c>
       <c r="D64">
-        <v>2098.143909423333</v>
+        <v>4346.754084900818</v>
       </c>
       <c r="E64">
         <v>3092.04</v>
@@ -6541,45 +6541,45 @@
         <v>592.8</v>
       </c>
       <c r="M64">
-        <v>1316.151252</v>
+        <v>723.334284</v>
       </c>
       <c r="N64">
-        <v>-723.3512520000002</v>
+        <v>-130.5342840000001</v>
       </c>
       <c r="O64">
-        <v>-149.010357912</v>
+        <v>-26.89006250400002</v>
       </c>
       <c r="P64">
-        <v>-574.3408940880001</v>
+        <v>-103.6442214960001</v>
       </c>
       <c r="Q64">
-        <v>-120.740894088</v>
+        <v>349.9557785040001</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.1141715902987029</v>
+        <v>0.110709651966992</v>
       </c>
       <c r="T64">
-        <v>1.578005391341692</v>
+        <v>1.499068174757321</v>
       </c>
       <c r="U64">
-        <v>0.2158</v>
+        <v>0.1186</v>
       </c>
       <c r="V64">
-        <v>0.09278325710242913</v>
+        <v>0.168824847240339</v>
       </c>
       <c r="W64">
-        <v>0.1957773731172958</v>
+        <v>0.09857737311729581</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y64">
-        <v>0.4504041606914035</v>
+        <v>0.8195380933997038</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6590,13 +6590,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.1664671756462305</v>
+        <v>0.1039156390801804</v>
       </c>
       <c r="C65">
-        <v>-3944.225451910167</v>
+        <v>-1720.506610710426</v>
       </c>
       <c r="D65">
-        <v>2068.584548089833</v>
+        <v>4292.303389289575</v>
       </c>
       <c r="E65">
         <v>3190.41</v>
@@ -6623,45 +6623,45 @@
         <v>592.8</v>
       </c>
       <c r="M65">
-        <v>1337.379498</v>
+        <v>735.0009660000001</v>
       </c>
       <c r="N65">
-        <v>-744.5794980000003</v>
+        <v>-142.2009660000001</v>
       </c>
       <c r="O65">
-        <v>-153.3833765880001</v>
+        <v>-29.29339899600003</v>
       </c>
       <c r="P65">
-        <v>-591.1961214120003</v>
+        <v>-112.9075670040001</v>
       </c>
       <c r="Q65">
-        <v>-137.5961214120001</v>
+        <v>340.692432996</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.1160194711175868</v>
+        <v>0.1124639668850188</v>
       </c>
       <c r="T65">
-        <v>1.620654185702279</v>
+        <v>1.539583530831843</v>
       </c>
       <c r="U65">
-        <v>0.2158</v>
+        <v>0.1186</v>
       </c>
       <c r="V65">
-        <v>0.09131050698969215</v>
+        <v>0.1661450877603336</v>
       </c>
       <c r="W65">
-        <v>0.1960951925916244</v>
+        <v>0.09889519259162444</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y65">
-        <v>0.4432548882994765</v>
+        <v>0.8065295522346292</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6672,13 +6672,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.1681671756462305</v>
+        <v>0.1584320863337237</v>
       </c>
       <c r="C66">
-        <v>-4071.333499619296</v>
+        <v>-3896.447389476574</v>
       </c>
       <c r="D66">
-        <v>2039.846500380705</v>
+        <v>2214.732610523427</v>
       </c>
       <c r="E66">
         <v>3288.78</v>
@@ -6705,37 +6705,37 @@
         <v>592.8</v>
       </c>
       <c r="M66">
-        <v>1358.607744</v>
+        <v>1264.172544</v>
       </c>
       <c r="N66">
-        <v>-765.8077440000002</v>
+        <v>-671.3725440000001</v>
       </c>
       <c r="O66">
-        <v>-157.756395264</v>
+        <v>-138.302744064</v>
       </c>
       <c r="P66">
-        <v>-608.0513487360001</v>
+        <v>-533.069799936</v>
       </c>
       <c r="Q66">
-        <v>-154.451348736</v>
+        <v>-79.46979993599984</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.1179700119819642</v>
+        <v>0.1175947638916674</v>
       </c>
       <c r="T66">
-        <v>1.665672357527342</v>
+        <v>1.65807768802927</v>
       </c>
       <c r="U66">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V66">
-        <v>0.08988378031797821</v>
+        <v>0.09659820613854432</v>
       </c>
       <c r="W66">
-        <v>0.1964030802073803</v>
+        <v>0.1814030802073803</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.4363290306697971</v>
+        <v>0.4689233307696327</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6754,13 +6754,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.1698671756462305</v>
+        <v>0.1599820863337237</v>
       </c>
       <c r="C67">
-        <v>-4197.653995248656</v>
+        <v>-4024.881961394432</v>
       </c>
       <c r="D67">
-        <v>2011.896004751344</v>
+        <v>2184.668038605568</v>
       </c>
       <c r="E67">
         <v>3387.15</v>
@@ -6787,37 +6787,37 @@
         <v>592.8</v>
       </c>
       <c r="M67">
-        <v>1379.83599</v>
+        <v>1283.92524</v>
       </c>
       <c r="N67">
-        <v>-787.0359900000003</v>
+        <v>-691.1252400000001</v>
       </c>
       <c r="O67">
-        <v>-162.1294139400001</v>
+        <v>-142.37179944</v>
       </c>
       <c r="P67">
-        <v>-624.9065760600002</v>
+        <v>-548.7534405600001</v>
       </c>
       <c r="Q67">
-        <v>-171.3065760600001</v>
+        <v>-95.15344055999992</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.120032012324306</v>
+        <v>0.1196460428600007</v>
       </c>
       <c r="T67">
-        <v>1.713262996313838</v>
+        <v>1.705451336258678</v>
       </c>
       <c r="U67">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V67">
-        <v>0.08850095292847085</v>
+        <v>0.09511207989025902</v>
       </c>
       <c r="W67">
-        <v>0.196701494358036</v>
+        <v>0.181701494358036</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.4296162763518002</v>
+        <v>0.4617091256808691</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6836,13 +6836,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.1715671756462305</v>
+        <v>0.1615320863337237</v>
       </c>
       <c r="C68">
-        <v>-4323.218874918199</v>
+        <v>-4152.511223601751</v>
       </c>
       <c r="D68">
-        <v>1984.701125081802</v>
+        <v>2155.408776398249</v>
       </c>
       <c r="E68">
         <v>3485.52</v>
@@ -6869,37 +6869,37 @@
         <v>592.8</v>
       </c>
       <c r="M68">
-        <v>1401.064236</v>
+        <v>1303.677936</v>
       </c>
       <c r="N68">
-        <v>-808.2642360000002</v>
+        <v>-710.8779360000001</v>
       </c>
       <c r="O68">
-        <v>-166.502432616</v>
+        <v>-146.440854816</v>
       </c>
       <c r="P68">
-        <v>-641.7618033840001</v>
+        <v>-564.437081184</v>
       </c>
       <c r="Q68">
-        <v>-188.161803384</v>
+        <v>-110.8370811839999</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.1222153068044327</v>
+        <v>0.1218179852970596</v>
       </c>
       <c r="T68">
-        <v>1.763653084440715</v>
+        <v>1.755611669678051</v>
       </c>
       <c r="U68">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V68">
-        <v>0.0871600293992516</v>
+        <v>0.09367098777070965</v>
       </c>
       <c r="W68">
-        <v>0.1969908656556415</v>
+        <v>0.1819908656556415</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.4231069388313184</v>
+        <v>0.4547135328675226</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6918,13 +6918,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.1732671756462305</v>
+        <v>0.1630820863337237</v>
       </c>
       <c r="C69">
-        <v>-4448.058371049525</v>
+        <v>-4279.367105016845</v>
       </c>
       <c r="D69">
-        <v>1958.231628950476</v>
+        <v>2126.922894983154</v>
       </c>
       <c r="E69">
         <v>3583.89</v>
@@ -6951,37 +6951,37 @@
         <v>592.8</v>
       </c>
       <c r="M69">
-        <v>1422.292482</v>
+        <v>1323.430632</v>
       </c>
       <c r="N69">
-        <v>-829.4924820000001</v>
+        <v>-730.6306320000001</v>
       </c>
       <c r="O69">
-        <v>-170.875451292</v>
+        <v>-150.509910192</v>
       </c>
       <c r="P69">
-        <v>-658.6170307080001</v>
+        <v>-580.1207218080001</v>
       </c>
       <c r="Q69">
-        <v>-205.017030708</v>
+        <v>-126.520721808</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.1245309221621428</v>
+        <v>0.1241215606090917</v>
       </c>
       <c r="T69">
-        <v>1.817097117302555</v>
+        <v>1.808812023304659</v>
       </c>
       <c r="U69">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V69">
-        <v>0.08585913343806875</v>
+        <v>0.09227291332637071</v>
       </c>
       <c r="W69">
-        <v>0.1972715990040648</v>
+        <v>0.1822715990040648</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.4167919098935375</v>
+        <v>0.4479267637202461</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7000,13 +7000,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.1749671756462305</v>
+        <v>0.1646320863337237</v>
       </c>
       <c r="C70">
-        <v>-4572.201124479805</v>
+        <v>-4405.479868683939</v>
       </c>
       <c r="D70">
-        <v>1932.458875520196</v>
+        <v>2099.180131316063</v>
       </c>
       <c r="E70">
         <v>3682.260000000001</v>
@@ -7033,37 +7033,37 @@
         <v>592.8</v>
       </c>
       <c r="M70">
-        <v>1443.520728</v>
+        <v>1343.183328</v>
       </c>
       <c r="N70">
-        <v>-850.7207280000002</v>
+        <v>-750.3833280000003</v>
       </c>
       <c r="O70">
-        <v>-175.2484699680001</v>
+        <v>-154.5789655680001</v>
       </c>
       <c r="P70">
-        <v>-675.4722580320001</v>
+        <v>-595.8043624320003</v>
       </c>
       <c r="Q70">
-        <v>-221.872258032</v>
+        <v>-142.2043624320002</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.1269912634797097</v>
+        <v>0.1265691093781258</v>
       </c>
       <c r="T70">
-        <v>1.87388140221826</v>
+        <v>1.865337399032929</v>
       </c>
       <c r="U70">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V70">
-        <v>0.08459649912280302</v>
+        <v>0.09091595871862994</v>
       </c>
       <c r="W70">
-        <v>0.1975440754892991</v>
+        <v>0.1825440754892991</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.4106626171009855</v>
+        <v>0.4413396054302424</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7082,13 +7082,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1766671756462305</v>
+        <v>0.1661820863337237</v>
       </c>
       <c r="C71">
-        <v>-4695.674287837322</v>
+        <v>-4530.878219019384</v>
       </c>
       <c r="D71">
-        <v>1907.355712162678</v>
+        <v>2072.151780980616</v>
       </c>
       <c r="E71">
         <v>3780.630000000001</v>
@@ -7115,37 +7115,37 @@
         <v>592.8</v>
       </c>
       <c r="M71">
-        <v>1464.748974</v>
+        <v>1362.936024</v>
       </c>
       <c r="N71">
-        <v>-871.9489740000004</v>
+        <v>-770.1360240000001</v>
       </c>
       <c r="O71">
-        <v>-179.6214886440001</v>
+        <v>-158.6480209440001</v>
       </c>
       <c r="P71">
-        <v>-692.3274853560002</v>
+        <v>-611.488003056</v>
       </c>
       <c r="Q71">
-        <v>-238.7274853560001</v>
+        <v>-157.8880030559999</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.1296103364951843</v>
+        <v>0.1291745645193557</v>
       </c>
       <c r="T71">
-        <v>1.934329189386591</v>
+        <v>1.925509573195282</v>
       </c>
       <c r="U71">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V71">
-        <v>0.08337046290363195</v>
+        <v>0.08959833612850487</v>
       </c>
       <c r="W71">
-        <v>0.1978086541053962</v>
+        <v>0.1828086541053962</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.4047109849690872</v>
+        <v>0.4349433792645867</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7164,13 +7164,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1783671756462305</v>
+        <v>0.1677320863337237</v>
       </c>
       <c r="C72">
-        <v>-4818.503620963114</v>
+        <v>-4655.589400878024</v>
       </c>
       <c r="D72">
-        <v>1882.896379036886</v>
+        <v>2045.810599121976</v>
       </c>
       <c r="E72">
         <v>3879</v>
@@ -7197,37 +7197,37 @@
         <v>592.8</v>
       </c>
       <c r="M72">
-        <v>1485.97722</v>
+        <v>1382.68872</v>
       </c>
       <c r="N72">
-        <v>-893.1772200000003</v>
+        <v>-789.8887200000001</v>
       </c>
       <c r="O72">
-        <v>-183.9945073200001</v>
+        <v>-162.71707632</v>
       </c>
       <c r="P72">
-        <v>-709.1827126800001</v>
+        <v>-627.1716436800001</v>
       </c>
       <c r="Q72">
-        <v>-255.58271268</v>
+        <v>-173.57164368</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.1324040143783571</v>
+        <v>0.1319537166700009</v>
       </c>
       <c r="T72">
-        <v>1.998806829032811</v>
+        <v>1.989693225635125</v>
       </c>
       <c r="U72">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V72">
-        <v>0.08217945629072293</v>
+        <v>0.08831835989809766</v>
       </c>
       <c r="W72">
-        <v>0.198065673332462</v>
+        <v>0.183065673332462</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.3989293994695288</v>
+        <v>0.4287299024179498</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7246,13 +7246,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.1800671756462305</v>
+        <v>0.1692820863337237</v>
       </c>
       <c r="C73">
-        <v>-4940.713579083605</v>
+        <v>-4779.639291158375</v>
       </c>
       <c r="D73">
-        <v>1859.056420916395</v>
+        <v>2020.130708841624</v>
       </c>
       <c r="E73">
         <v>3977.369999999999</v>
@@ -7279,37 +7279,37 @@
         <v>592.8</v>
       </c>
       <c r="M73">
-        <v>1507.205466</v>
+        <v>1402.441416</v>
       </c>
       <c r="N73">
-        <v>-914.4054660000002</v>
+        <v>-809.6414159999999</v>
       </c>
       <c r="O73">
-        <v>-188.367525996</v>
+        <v>-166.786131696</v>
       </c>
       <c r="P73">
-        <v>-726.0379400040001</v>
+        <v>-642.855284304</v>
       </c>
       <c r="Q73">
-        <v>-272.437940004</v>
+        <v>-189.2552843039998</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.1353903597017487</v>
+        <v>0.1349245344862078</v>
       </c>
       <c r="T73">
-        <v>2.067731202447735</v>
+        <v>2.058303336863921</v>
       </c>
       <c r="U73">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.08102199915986769</v>
+        <v>0.08707443933615264</v>
       </c>
       <c r="W73">
-        <v>0.1983154525813006</v>
+        <v>0.1833154525813006</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.3933106755333383</v>
+        <v>0.4226914530881196</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7328,13 +7328,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.1817671756462305</v>
+        <v>0.1708320863337237</v>
       </c>
       <c r="C74">
-        <v>-5062.327394368705</v>
+        <v>-4903.052483594171</v>
       </c>
       <c r="D74">
-        <v>1835.812605631295</v>
+        <v>1995.087516405828</v>
       </c>
       <c r="E74">
         <v>4075.739999999999</v>
@@ -7361,37 +7361,37 @@
         <v>592.8</v>
       </c>
       <c r="M74">
-        <v>1528.433712</v>
+        <v>1422.194112</v>
       </c>
       <c r="N74">
-        <v>-935.6337120000001</v>
+        <v>-829.394112</v>
       </c>
       <c r="O74">
-        <v>-192.740544672</v>
+        <v>-170.855187072</v>
       </c>
       <c r="P74">
-        <v>-742.893167328</v>
+        <v>-658.5389249279999</v>
       </c>
       <c r="Q74">
-        <v>-289.2931673279999</v>
+        <v>-204.9389249279998</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.1385900154053826</v>
+        <v>0.1381075535750009</v>
       </c>
       <c r="T74">
-        <v>2.141578745392297</v>
+        <v>2.131814170323347</v>
       </c>
       <c r="U74">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.07989669361598065</v>
+        <v>0.08586507212315052</v>
       </c>
       <c r="W74">
-        <v>0.1985582935176714</v>
+        <v>0.1835582935176714</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.3878480272620419</v>
+        <v>0.4168207384618957</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7410,13 +7410,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.1834671756462306</v>
+        <v>0.1723820863337236</v>
       </c>
       <c r="C75">
-        <v>-5183.367151447133</v>
+        <v>-5025.852367316236</v>
       </c>
       <c r="D75">
-        <v>1813.142848552868</v>
+        <v>1970.657632683764</v>
       </c>
       <c r="E75">
         <v>4174.110000000001</v>
@@ -7443,37 +7443,37 @@
         <v>592.8</v>
       </c>
       <c r="M75">
-        <v>1549.661958</v>
+        <v>1441.946808</v>
       </c>
       <c r="N75">
-        <v>-956.8619580000002</v>
+        <v>-849.1468080000002</v>
       </c>
       <c r="O75">
-        <v>-197.113563348</v>
+        <v>-174.9242424480001</v>
       </c>
       <c r="P75">
-        <v>-759.7483946520001</v>
+        <v>-674.2225655520001</v>
       </c>
       <c r="Q75">
-        <v>-306.148394652</v>
+        <v>-220.622565552</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.1420266826426189</v>
+        <v>0.1415263518555565</v>
       </c>
       <c r="T75">
-        <v>2.220896476703123</v>
+        <v>2.210770250705693</v>
       </c>
       <c r="U75">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V75">
-        <v>0.07880221836096721</v>
+        <v>0.08468883825844982</v>
       </c>
       <c r="W75">
-        <v>0.1987944812777033</v>
+        <v>0.1837944812777033</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3825350405872194</v>
+        <v>0.4111108653322806</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7492,13 +7492,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.1851671756462305</v>
+        <v>0.1739320863337236</v>
       </c>
       <c r="C76">
-        <v>-5303.85385739491</v>
+        <v>-5148.061199712239</v>
       </c>
       <c r="D76">
-        <v>1791.02614260509</v>
+        <v>1946.818800287761</v>
       </c>
       <c r="E76">
         <v>4272.48</v>
@@ -7525,37 +7525,37 @@
         <v>592.8</v>
       </c>
       <c r="M76">
-        <v>1570.890204</v>
+        <v>1461.699504</v>
       </c>
       <c r="N76">
-        <v>-978.0902040000003</v>
+        <v>-868.8995040000002</v>
       </c>
       <c r="O76">
-        <v>-201.4865820240001</v>
+        <v>-178.9932978240001</v>
       </c>
       <c r="P76">
-        <v>-776.6036219760002</v>
+        <v>-689.9062061760002</v>
       </c>
       <c r="Q76">
-        <v>-323.0036219760001</v>
+        <v>-236.306206176</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.1457277088981043</v>
+        <v>0.1452081346192317</v>
       </c>
       <c r="T76">
-        <v>2.306315571960935</v>
+        <v>2.295799875732835</v>
       </c>
       <c r="U76">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V76">
-        <v>0.07773732351825142</v>
+        <v>0.08354439449820049</v>
       </c>
       <c r="W76">
-        <v>0.1990242855847613</v>
+        <v>0.1840242855847613</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.3773656481468516</v>
+        <v>0.4055553130980606</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7574,13 +7574,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.1868671756462305</v>
+        <v>0.1754820863337236</v>
       </c>
       <c r="C77">
-        <v>-5423.807506663285</v>
+        <v>-5269.700174061407</v>
       </c>
       <c r="D77">
-        <v>1769.442493336715</v>
+        <v>1923.549825938593</v>
       </c>
       <c r="E77">
         <v>4370.85</v>
@@ -7607,37 +7607,37 @@
         <v>592.8</v>
       </c>
       <c r="M77">
-        <v>1592.11845</v>
+        <v>1481.4522</v>
       </c>
       <c r="N77">
-        <v>-999.3184500000002</v>
+        <v>-888.6522</v>
       </c>
       <c r="O77">
-        <v>-205.8596007000001</v>
+        <v>-183.0623532</v>
       </c>
       <c r="P77">
-        <v>-793.4588493000001</v>
+        <v>-705.5898468</v>
       </c>
       <c r="Q77">
-        <v>-339.8588493</v>
+        <v>-251.9898467999999</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.1497248172540284</v>
+        <v>0.149184460004001</v>
       </c>
       <c r="T77">
-        <v>2.398568194839372</v>
+        <v>2.387631870762149</v>
       </c>
       <c r="U77">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V77">
-        <v>0.07670082587134142</v>
+        <v>0.08243046923822449</v>
       </c>
       <c r="W77">
-        <v>0.1992479617769645</v>
+        <v>0.1842479617769645</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3723341061715603</v>
+        <v>0.4001479089234199</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7656,13 +7656,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.1885671756462305</v>
+        <v>0.1770320863337236</v>
       </c>
       <c r="C78">
-        <v>-5543.247141367878</v>
+        <v>-5390.789482376164</v>
       </c>
       <c r="D78">
-        <v>1748.372858632122</v>
+        <v>1900.830517623836</v>
       </c>
       <c r="E78">
         <v>4469.219999999999</v>
@@ -7689,37 +7689,37 @@
         <v>592.8</v>
       </c>
       <c r="M78">
-        <v>1613.346696</v>
+        <v>1501.204896</v>
       </c>
       <c r="N78">
-        <v>-1020.546696</v>
+        <v>-908.404896</v>
       </c>
       <c r="O78">
-        <v>-210.232619376</v>
+        <v>-187.131408576</v>
       </c>
       <c r="P78">
-        <v>-810.3140766240001</v>
+        <v>-721.273487424</v>
       </c>
       <c r="Q78">
-        <v>-356.714076624</v>
+        <v>-267.6734874239999</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.1540550179729463</v>
+        <v>0.1534921458375011</v>
       </c>
       <c r="T78">
-        <v>2.498508536291013</v>
+        <v>2.487116532043905</v>
       </c>
       <c r="U78">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V78">
-        <v>0.07569160447829745</v>
+        <v>0.08134585780087944</v>
       </c>
       <c r="W78">
-        <v>0.1994657517535834</v>
+        <v>0.1844657517535834</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3674349731956187</v>
+        <v>0.394882804858638</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7738,13 +7738,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.1902671756462306</v>
+        <v>0.1785820863337237</v>
       </c>
       <c r="C79">
-        <v>-5662.190907321142</v>
+        <v>-5511.348373842383</v>
       </c>
       <c r="D79">
-        <v>1727.799092678858</v>
+        <v>1878.641626157617</v>
       </c>
       <c r="E79">
         <v>4567.59</v>
@@ -7771,37 +7771,37 @@
         <v>592.8</v>
       </c>
       <c r="M79">
-        <v>1634.574942</v>
+        <v>1520.957592</v>
       </c>
       <c r="N79">
-        <v>-1041.774942</v>
+        <v>-928.157592</v>
       </c>
       <c r="O79">
-        <v>-214.6056380520001</v>
+        <v>-191.200463952</v>
       </c>
       <c r="P79">
-        <v>-827.1693039480001</v>
+        <v>-736.957128048</v>
       </c>
       <c r="Q79">
-        <v>-373.569303948</v>
+        <v>-283.3571280479998</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.1587617578848136</v>
+        <v>0.1581744130478272</v>
       </c>
       <c r="T79">
-        <v>2.60713934221671</v>
+        <v>2.595252033437119</v>
       </c>
       <c r="U79">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V79">
-        <v>0.07470859662792995</v>
+        <v>0.08028941808917971</v>
       </c>
       <c r="W79">
-        <v>0.1996778848476927</v>
+        <v>0.1846778848476927</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3626630904268444</v>
+        <v>0.3897544567435908</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7820,13 +7820,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.1919671756462306</v>
+        <v>0.1801320863337237</v>
       </c>
       <c r="C80">
-        <v>-5780.656106154725</v>
+        <v>-5631.395209213721</v>
       </c>
       <c r="D80">
-        <v>1707.703893845276</v>
+        <v>1856.96479078628</v>
       </c>
       <c r="E80">
         <v>4665.960000000001</v>
@@ -7853,37 +7853,37 @@
         <v>592.8</v>
       </c>
       <c r="M80">
-        <v>1655.803188</v>
+        <v>1540.710288</v>
       </c>
       <c r="N80">
-        <v>-1063.003188</v>
+        <v>-947.9102880000003</v>
       </c>
       <c r="O80">
-        <v>-218.9786567280001</v>
+        <v>-195.2695193280001</v>
       </c>
       <c r="P80">
-        <v>-844.0245312720003</v>
+        <v>-752.6407686720001</v>
       </c>
       <c r="Q80">
-        <v>-390.4245312720002</v>
+        <v>-299.040768672</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.1638963832432142</v>
+        <v>0.1632823409136375</v>
       </c>
       <c r="T80">
-        <v>2.725645675953833</v>
+        <v>2.713218034956987</v>
       </c>
       <c r="U80">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V80">
-        <v>0.07375079410705904</v>
+        <v>0.07926006657521584</v>
       </c>
       <c r="W80">
-        <v>0.1998845786316967</v>
+        <v>0.1848845786316967</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3580135636265002</v>
+        <v>0.3847576047340575</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7902,13 +7902,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.1936671756462305</v>
+        <v>0.1816820863337237</v>
       </c>
       <c r="C81">
-        <v>-5898.659243846369</v>
+        <v>-5750.947511483128</v>
       </c>
       <c r="D81">
-        <v>1688.070756153632</v>
+        <v>1835.782488516872</v>
       </c>
       <c r="E81">
         <v>4764.33</v>
@@ -7935,37 +7935,37 @@
         <v>592.8</v>
       </c>
       <c r="M81">
-        <v>1677.031434</v>
+        <v>1560.462984</v>
       </c>
       <c r="N81">
-        <v>-1084.231434</v>
+        <v>-967.6629840000003</v>
       </c>
       <c r="O81">
-        <v>-223.3516754040001</v>
+        <v>-199.3385747040001</v>
       </c>
       <c r="P81">
-        <v>-860.8797585960002</v>
+        <v>-768.3244092960002</v>
       </c>
       <c r="Q81">
-        <v>-407.2797585960001</v>
+        <v>-314.7244092960001</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.1695200205405101</v>
+        <v>0.1688767381000013</v>
       </c>
       <c r="T81">
-        <v>2.855438327189729</v>
+        <v>2.842418893764464</v>
       </c>
       <c r="U81">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V81">
-        <v>0.07281723975127348</v>
+        <v>0.07825677459325109</v>
       </c>
       <c r="W81">
-        <v>0.2000860396616752</v>
+        <v>0.1850860396616752</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3534817463654053</v>
+        <v>0.3798872553070441</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7984,13 +7984,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.1953671756462305</v>
+        <v>0.1832320863337236</v>
       </c>
       <c r="C82">
-        <v>-6016.216075937447</v>
+        <v>-5870.022013125426</v>
       </c>
       <c r="D82">
-        <v>1668.883924062553</v>
+        <v>1815.077986874574</v>
       </c>
       <c r="E82">
         <v>4862.700000000001</v>
@@ -8017,37 +8017,37 @@
         <v>592.8</v>
       </c>
       <c r="M82">
-        <v>1698.25968</v>
+        <v>1580.21568</v>
       </c>
       <c r="N82">
-        <v>-1105.45968</v>
+        <v>-987.4156800000001</v>
       </c>
       <c r="O82">
-        <v>-227.7246940800001</v>
+        <v>-203.40763008</v>
       </c>
       <c r="P82">
-        <v>-877.7349859200003</v>
+        <v>-784.0080499200001</v>
       </c>
       <c r="Q82">
-        <v>-424.1349859200002</v>
+        <v>-330.4080499199999</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.1757060215675356</v>
+        <v>0.1750305750050013</v>
       </c>
       <c r="T82">
-        <v>2.998210243549216</v>
+        <v>2.984539838452687</v>
       </c>
       <c r="U82">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V82">
-        <v>0.07190702425438256</v>
+        <v>0.07727856491083547</v>
       </c>
       <c r="W82">
-        <v>0.2002824641659043</v>
+        <v>0.1852824641659042</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3490632245358377</v>
+        <v>0.3751386646157061</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8066,13 +8066,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1970671756462306</v>
+        <v>0.1847820863337236</v>
       </c>
       <c r="C83">
-        <v>-6133.341649701457</v>
+        <v>-5988.634700178634</v>
       </c>
       <c r="D83">
-        <v>1650.128350298543</v>
+        <v>1794.835299821365</v>
       </c>
       <c r="E83">
         <v>4961.07</v>
@@ -8099,37 +8099,37 @@
         <v>592.8</v>
       </c>
       <c r="M83">
-        <v>1719.487926</v>
+        <v>1599.968376</v>
       </c>
       <c r="N83">
-        <v>-1126.687926</v>
+        <v>-1007.168376</v>
       </c>
       <c r="O83">
-        <v>-232.0977127560001</v>
+        <v>-207.476685456</v>
       </c>
       <c r="P83">
-        <v>-894.5902132440002</v>
+        <v>-799.691690544</v>
       </c>
       <c r="Q83">
-        <v>-440.9902132440001</v>
+        <v>-346.0916905439999</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.1825431805974059</v>
+        <v>0.1818321842157909</v>
       </c>
       <c r="T83">
-        <v>3.156010782683386</v>
+        <v>3.141620882581776</v>
       </c>
       <c r="U83">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V83">
-        <v>0.071019283214205</v>
+        <v>0.07632450855391157</v>
       </c>
       <c r="W83">
-        <v>0.2004740386823746</v>
+        <v>0.1854740386823746</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3447538020107039</v>
+        <v>0.3705073230772405</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8148,13 +8148,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1987671756462305</v>
+        <v>0.1863320863337237</v>
       </c>
       <c r="C84">
-        <v>-6250.050343500676</v>
+        <v>-6106.800853408132</v>
       </c>
       <c r="D84">
-        <v>1631.789656499325</v>
+        <v>1775.039146591869</v>
       </c>
       <c r="E84">
         <v>5059.440000000001</v>
@@ -8181,37 +8181,37 @@
         <v>592.8</v>
       </c>
       <c r="M84">
-        <v>1740.716172</v>
+        <v>1619.721072</v>
       </c>
       <c r="N84">
-        <v>-1147.916172</v>
+        <v>-1026.921072</v>
       </c>
       <c r="O84">
-        <v>-236.4707314320001</v>
+        <v>-211.5457408320001</v>
       </c>
       <c r="P84">
-        <v>-911.4454405680003</v>
+        <v>-815.3753311680002</v>
       </c>
       <c r="Q84">
-        <v>-457.8454405680002</v>
+        <v>-361.7753311680001</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.1901400239639285</v>
+        <v>0.1893895277833348</v>
       </c>
       <c r="T84">
-        <v>3.331344715054685</v>
+        <v>3.316155376058541</v>
       </c>
       <c r="U84">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.07015319439451959</v>
+        <v>0.0753937218642297</v>
       </c>
       <c r="W84">
-        <v>0.2006609406496627</v>
+        <v>0.1856609406496627</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3405494873520367</v>
+        <v>0.3659889410884937</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8230,13 +8230,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2004671756462306</v>
+        <v>0.1878820863337236</v>
       </c>
       <c r="C85">
-        <v>-6366.355903547327</v>
+        <v>-6224.535086776405</v>
       </c>
       <c r="D85">
-        <v>1613.854096452674</v>
+        <v>1755.674913223596</v>
       </c>
       <c r="E85">
         <v>5157.810000000001</v>
@@ -8263,37 +8263,37 @@
         <v>592.8</v>
       </c>
       <c r="M85">
-        <v>1761.944418</v>
+        <v>1639.473768</v>
       </c>
       <c r="N85">
-        <v>-1169.144418</v>
+        <v>-1046.673768</v>
       </c>
       <c r="O85">
-        <v>-240.8437501080001</v>
+        <v>-215.6147962080001</v>
       </c>
       <c r="P85">
-        <v>-928.3006678920002</v>
+        <v>-831.0589717920002</v>
       </c>
       <c r="Q85">
-        <v>-474.7006678920001</v>
+        <v>-377.4589717920001</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.1986306136088655</v>
+        <v>0.1978359705941192</v>
       </c>
       <c r="T85">
-        <v>3.527306168881431</v>
+        <v>3.511223339356103</v>
       </c>
       <c r="U85">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V85">
-        <v>0.06930797518494705</v>
+        <v>0.07448536376947995</v>
       </c>
       <c r="W85">
-        <v>0.2008433389550885</v>
+        <v>0.1858433389550884</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3364464814803255</v>
+        <v>0.3615794357741745</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8312,13 +8312,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.2021671756462305</v>
+        <v>0.1894320863337236</v>
       </c>
       <c r="C86">
-        <v>-6482.271478266771</v>
+        <v>-6341.851383421945</v>
       </c>
       <c r="D86">
-        <v>1596.308521733229</v>
+        <v>1736.728616578056</v>
       </c>
       <c r="E86">
         <v>5256.18</v>
@@ -8345,37 +8345,37 @@
         <v>592.8</v>
       </c>
       <c r="M86">
-        <v>1783.172664</v>
+        <v>1659.226464</v>
       </c>
       <c r="N86">
-        <v>-1190.372664</v>
+        <v>-1066.426464</v>
       </c>
       <c r="O86">
-        <v>-245.2167687840001</v>
+        <v>-219.6838515840001</v>
       </c>
       <c r="P86">
-        <v>-945.1558952160001</v>
+        <v>-846.742612416</v>
       </c>
       <c r="Q86">
-        <v>-491.555895216</v>
+        <v>-393.1426124159999</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.2081825269594195</v>
+        <v>0.2073382187562516</v>
       </c>
       <c r="T86">
-        <v>3.747762804436519</v>
+        <v>3.730674798065857</v>
       </c>
       <c r="U86">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V86">
-        <v>0.06848288024226912</v>
+        <v>0.07359863324841473</v>
       </c>
       <c r="W86">
-        <v>0.2010213944437183</v>
+        <v>0.1860213944437183</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3324411662246074</v>
+        <v>0.3572749186816249</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8394,13 +8394,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.2038671756462305</v>
+        <v>0.1909820863337237</v>
       </c>
       <c r="C87">
-        <v>-6597.809650443263</v>
+        <v>-6458.763129333406</v>
       </c>
       <c r="D87">
-        <v>1579.140349556736</v>
+        <v>1718.186870666593</v>
       </c>
       <c r="E87">
         <v>5354.549999999999</v>
@@ -8427,37 +8427,37 @@
         <v>592.8</v>
       </c>
       <c r="M87">
-        <v>1804.40091</v>
+        <v>1678.97916</v>
       </c>
       <c r="N87">
-        <v>-1211.60091</v>
+        <v>-1086.17916</v>
       </c>
       <c r="O87">
-        <v>-249.58978746</v>
+        <v>-223.75290696</v>
       </c>
       <c r="P87">
-        <v>-962.0111225399999</v>
+        <v>-862.4262530399999</v>
       </c>
       <c r="Q87">
-        <v>-508.4111225399997</v>
+        <v>-408.8262530399998</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.2190080287567141</v>
+        <v>0.2181074333400017</v>
       </c>
       <c r="T87">
-        <v>3.99761365806562</v>
+        <v>3.979386451270249</v>
       </c>
       <c r="U87">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.06767719929824244</v>
+        <v>0.07273276697490397</v>
       </c>
       <c r="W87">
-        <v>0.2011952603914393</v>
+        <v>0.1861952603914393</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3285300936807884</v>
+        <v>0.353071684344194</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8476,13 +8476,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.2055671756462305</v>
+        <v>0.1925320863337237</v>
       </c>
       <c r="C88">
-        <v>-6712.982467313425</v>
+        <v>-6575.283144889488</v>
       </c>
       <c r="D88">
-        <v>1562.337532686574</v>
+        <v>1700.036855110512</v>
       </c>
       <c r="E88">
         <v>5452.92</v>
@@ -8509,37 +8509,37 @@
         <v>592.8</v>
       </c>
       <c r="M88">
-        <v>1825.629156</v>
+        <v>1698.731856</v>
       </c>
       <c r="N88">
-        <v>-1232.829156</v>
+        <v>-1105.931856</v>
       </c>
       <c r="O88">
-        <v>-253.9628061360001</v>
+        <v>-227.821962336</v>
       </c>
       <c r="P88">
-        <v>-978.8663498640002</v>
+        <v>-878.1098936640001</v>
       </c>
       <c r="Q88">
-        <v>-525.2663498640001</v>
+        <v>-424.5098936639999</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.2313800308107651</v>
+        <v>0.2304151071500018</v>
       </c>
       <c r="T88">
-        <v>4.283157490784594</v>
+        <v>4.263628340646694</v>
       </c>
       <c r="U88">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.06689025512035589</v>
+        <v>0.07188703712635856</v>
       </c>
       <c r="W88">
-        <v>0.2013650829450272</v>
+        <v>0.1863650829450272</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3247099763124072</v>
+        <v>0.3489661996425173</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8558,13 +8558,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.2072671756462305</v>
+        <v>0.1940820863337236</v>
       </c>
       <c r="C89">
-        <v>-6827.801468758688</v>
+        <v>-6691.423714420665</v>
       </c>
       <c r="D89">
-        <v>1545.888531241312</v>
+        <v>1682.266285579336</v>
       </c>
       <c r="E89">
         <v>5551.290000000001</v>
@@ -8591,37 +8591,37 @@
         <v>592.8</v>
       </c>
       <c r="M89">
-        <v>1846.857402</v>
+        <v>1718.484552</v>
       </c>
       <c r="N89">
-        <v>-1254.057402</v>
+        <v>-1125.684552</v>
       </c>
       <c r="O89">
-        <v>-258.3358248120001</v>
+        <v>-231.8910177120001</v>
       </c>
       <c r="P89">
-        <v>-995.7215771880003</v>
+        <v>-893.793534288</v>
       </c>
       <c r="Q89">
-        <v>-542.1215771880002</v>
+        <v>-440.1935342879999</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.2456554177962086</v>
+        <v>0.2446162692384635</v>
       </c>
       <c r="T89">
-        <v>4.612631143921869</v>
+        <v>4.591599751465671</v>
       </c>
       <c r="U89">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.06612140161322536</v>
+        <v>0.07106074934329698</v>
       </c>
       <c r="W89">
-        <v>0.201531001531866</v>
+        <v>0.186531001531866</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3209776777341036</v>
+        <v>0.3449550938994999</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8640,13 +8640,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.2089671756462305</v>
+        <v>0.1956320863337237</v>
       </c>
       <c r="C90">
-        <v>-6942.277713735361</v>
+        <v>-6807.196613936059</v>
       </c>
       <c r="D90">
-        <v>1529.782286264638</v>
+        <v>1664.86338606394</v>
       </c>
       <c r="E90">
         <v>5649.66</v>
@@ -8673,37 +8673,37 @@
         <v>592.8</v>
       </c>
       <c r="M90">
-        <v>1868.085648</v>
+        <v>1738.237248</v>
       </c>
       <c r="N90">
-        <v>-1275.285648</v>
+        <v>-1145.437248</v>
       </c>
       <c r="O90">
-        <v>-262.708843488</v>
+        <v>-235.960073088</v>
       </c>
       <c r="P90">
-        <v>-1012.576804512</v>
+        <v>-909.477174912</v>
       </c>
       <c r="Q90">
-        <v>-558.9768045119999</v>
+        <v>-455.8771749119999</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.2623100359458926</v>
+        <v>0.2611842916750021</v>
       </c>
       <c r="T90">
-        <v>4.997017072582026</v>
+        <v>4.974233064087811</v>
       </c>
       <c r="U90">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.0653700220494387</v>
+        <v>0.07025324082803223</v>
       </c>
       <c r="W90">
-        <v>0.2016931492417312</v>
+        <v>0.1866931492417311</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3173302041234889</v>
+        <v>0.341035149650642</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8722,13 +8722,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.2106671756462305</v>
+        <v>0.1971820863337237</v>
       </c>
       <c r="C91">
-        <v>-7056.42180506953</v>
+        <v>-6922.613137146939</v>
       </c>
       <c r="D91">
-        <v>1514.008194930471</v>
+        <v>1647.816862853061</v>
       </c>
       <c r="E91">
         <v>5748.030000000001</v>
@@ -8755,37 +8755,37 @@
         <v>592.8</v>
       </c>
       <c r="M91">
-        <v>1889.313894</v>
+        <v>1757.989944</v>
       </c>
       <c r="N91">
-        <v>-1296.513894</v>
+        <v>-1165.189944</v>
       </c>
       <c r="O91">
-        <v>-267.0818621640001</v>
+        <v>-240.0291284640001</v>
       </c>
       <c r="P91">
-        <v>-1029.432031836</v>
+        <v>-925.1608155360002</v>
       </c>
       <c r="Q91">
-        <v>-575.8320318360002</v>
+        <v>-471.5608155360001</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.2819927664864283</v>
+        <v>0.2807646818272752</v>
       </c>
       <c r="T91">
-        <v>5.451291351907665</v>
+        <v>5.426436069913977</v>
       </c>
       <c r="U91">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.06463552741966973</v>
+        <v>0.06946387857153749</v>
       </c>
       <c r="W91">
-        <v>0.2018516531828353</v>
+        <v>0.1868516531828353</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3137646962119889</v>
+        <v>0.3372032940365898</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8804,13 +8804,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.2123671756462305</v>
+        <v>0.1987320863337237</v>
       </c>
       <c r="C92">
-        <v>-7170.243912733577</v>
+        <v>-7037.684119907672</v>
       </c>
       <c r="D92">
-        <v>1498.556087266424</v>
+        <v>1631.115880092329</v>
       </c>
       <c r="E92">
         <v>5846.400000000001</v>
@@ -8837,37 +8837,37 @@
         <v>592.8</v>
       </c>
       <c r="M92">
-        <v>1910.54214</v>
+        <v>1777.74264</v>
       </c>
       <c r="N92">
-        <v>-1317.742140000001</v>
+        <v>-1184.94264</v>
       </c>
       <c r="O92">
-        <v>-271.4548808400001</v>
+        <v>-244.0981838400001</v>
       </c>
       <c r="P92">
-        <v>-1046.28725916</v>
+        <v>-940.8444561600002</v>
       </c>
       <c r="Q92">
-        <v>-592.6872591600002</v>
+        <v>-487.24445616</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.3056120431350712</v>
+        <v>0.3042611500100026</v>
       </c>
       <c r="T92">
-        <v>5.996420487098431</v>
+        <v>5.969079676905374</v>
       </c>
       <c r="U92">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.06391735489278451</v>
+        <v>0.06869205769852041</v>
       </c>
       <c r="W92">
-        <v>0.2020066348141371</v>
+        <v>0.1870066348141371</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3102784218096335</v>
+        <v>0.3334565907695165</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8886,13 +8886,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.2140671756462305</v>
+        <v>0.2002820863337237</v>
       </c>
       <c r="C93">
-        <v>-7283.753795711757</v>
+        <v>-7152.419963185328</v>
       </c>
       <c r="D93">
-        <v>1483.416204288244</v>
+        <v>1614.750036814673</v>
       </c>
       <c r="E93">
         <v>5944.77</v>
@@ -8919,37 +8919,37 @@
         <v>592.8</v>
       </c>
       <c r="M93">
-        <v>1931.770386</v>
+        <v>1797.495336</v>
       </c>
       <c r="N93">
-        <v>-1338.970386</v>
+        <v>-1204.695336</v>
       </c>
       <c r="O93">
-        <v>-275.8278995160001</v>
+        <v>-248.1672392160001</v>
       </c>
       <c r="P93">
-        <v>-1063.142486484</v>
+        <v>-956.5280967840001</v>
       </c>
       <c r="Q93">
-        <v>-609.5424864839999</v>
+        <v>-502.928096784</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.334480047927857</v>
+        <v>0.3329790555666696</v>
       </c>
       <c r="T93">
-        <v>6.66268943010937</v>
+        <v>6.632310752117082</v>
       </c>
       <c r="U93">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.06321496637747918</v>
+        <v>0.06793719992161359</v>
       </c>
       <c r="W93">
-        <v>0.20215821025574</v>
+        <v>0.18715821025574</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3068687688227145</v>
+        <v>0.3297922326291921</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8968,13 +8968,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.2157671756462305</v>
+        <v>0.2018320863337237</v>
       </c>
       <c r="C94">
-        <v>-7396.96082255357</v>
+        <v>-7266.830654660218</v>
       </c>
       <c r="D94">
-        <v>1468.579177446431</v>
+        <v>1598.709345339782</v>
       </c>
       <c r="E94">
         <v>6043.140000000001</v>
@@ -9001,37 +9001,37 @@
         <v>592.8</v>
       </c>
       <c r="M94">
-        <v>1952.998632</v>
+        <v>1817.248032</v>
       </c>
       <c r="N94">
-        <v>-1360.198632</v>
+        <v>-1224.448032</v>
       </c>
       <c r="O94">
-        <v>-280.2009181920001</v>
+        <v>-252.2362945920001</v>
       </c>
       <c r="P94">
-        <v>-1079.997713808</v>
+        <v>-972.2117374080002</v>
       </c>
       <c r="Q94">
-        <v>-626.3977138080002</v>
+        <v>-518.6117374080001</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>0.3705650539188391</v>
+        <v>0.3688764375125035</v>
       </c>
       <c r="T94">
-        <v>7.495525608873043</v>
+        <v>7.461349596131721</v>
       </c>
       <c r="U94">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.06252784717772397</v>
+        <v>0.06719875209637866</v>
       </c>
       <c r="W94">
-        <v>0.2023064905790472</v>
+        <v>0.1873064905790472</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3035332387268154</v>
+        <v>0.3262075344484401</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9050,13 +9050,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.2174671756462305</v>
+        <v>0.2033820863337236</v>
       </c>
       <c r="C95">
-        <v>-7509.8739907059</v>
+        <v>-7380.925789051628</v>
       </c>
       <c r="D95">
-        <v>1454.0360092941</v>
+        <v>1582.984210948371</v>
       </c>
       <c r="E95">
         <v>6141.51</v>
@@ -9083,37 +9083,37 @@
         <v>592.8</v>
       </c>
       <c r="M95">
-        <v>1974.226878</v>
+        <v>1837.000728</v>
       </c>
       <c r="N95">
-        <v>-1381.426878</v>
+        <v>-1244.200728</v>
       </c>
       <c r="O95">
-        <v>-284.5739368680001</v>
+        <v>-256.305349968</v>
       </c>
       <c r="P95">
-        <v>-1096.852941132</v>
+        <v>-987.8953780320001</v>
       </c>
       <c r="Q95">
-        <v>-643.2529411319999</v>
+        <v>-534.2953780319999</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>0.4169600616215305</v>
+        <v>0.4150302143000039</v>
       </c>
       <c r="T95">
-        <v>8.566314981569194</v>
+        <v>8.527256681293395</v>
       </c>
       <c r="U95">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.06185550473495276</v>
+        <v>0.06647618486953588</v>
       </c>
       <c r="W95">
-        <v>0.2024515820781972</v>
+        <v>0.1874515820781972</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3002694404609356</v>
+        <v>0.322699926551145</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9132,13 +9132,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2191671756462305</v>
+        <v>0.2049320863337237</v>
       </c>
       <c r="C96">
-        <v>-7622.501944707782</v>
+        <v>-7494.714587255685</v>
       </c>
       <c r="D96">
-        <v>1439.778055292219</v>
+        <v>1567.565412744316</v>
       </c>
       <c r="E96">
         <v>6239.880000000001</v>
@@ -9165,37 +9165,37 @@
         <v>592.8</v>
       </c>
       <c r="M96">
-        <v>1995.455124</v>
+        <v>1856.753424</v>
       </c>
       <c r="N96">
-        <v>-1402.655124</v>
+        <v>-1263.953424</v>
       </c>
       <c r="O96">
-        <v>-288.9469555440001</v>
+        <v>-260.3744053440001</v>
       </c>
       <c r="P96">
-        <v>-1113.708168456</v>
+        <v>-1003.579018656</v>
       </c>
       <c r="Q96">
-        <v>-660.1081684560002</v>
+        <v>-549.9790186560001</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>0.4788200718917857</v>
+        <v>0.4765685833500047</v>
       </c>
       <c r="T96">
-        <v>9.994034145164061</v>
+        <v>9.94846612817563</v>
       </c>
       <c r="U96">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.06119746745053836</v>
+        <v>0.06576899141347699</v>
       </c>
       <c r="W96">
-        <v>0.2025935865241738</v>
+        <v>0.1875935865241738</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2970750847113512</v>
+        <v>0.3192669486091115</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9214,13 +9214,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2208671756462305</v>
+        <v>0.2064820863337237</v>
       </c>
       <c r="C97">
-        <v>-7734.852993325045</v>
+        <v>-7608.205914375544</v>
       </c>
       <c r="D97">
-        <v>1425.797006674956</v>
+        <v>1552.444085624458</v>
       </c>
       <c r="E97">
         <v>6338.250000000002</v>
@@ -9247,37 +9247,37 @@
         <v>592.8</v>
       </c>
       <c r="M97">
-        <v>2016.68337</v>
+        <v>1876.50612</v>
       </c>
       <c r="N97">
-        <v>-1423.88337</v>
+        <v>-1283.70612</v>
       </c>
       <c r="O97">
-        <v>-293.3199742200001</v>
+        <v>-264.4434607200001</v>
       </c>
       <c r="P97">
-        <v>-1130.56339578</v>
+        <v>-1019.26265928</v>
       </c>
       <c r="Q97">
-        <v>-676.9633957800002</v>
+        <v>-565.6626592800001</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>0.5654240862701431</v>
+        <v>0.5627223000200058</v>
       </c>
       <c r="T97">
-        <v>11.99284097419688</v>
+        <v>11.93815935381076</v>
       </c>
       <c r="U97">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.06055328358263796</v>
+        <v>0.06507668624070354</v>
       </c>
       <c r="W97">
-        <v>0.2027326014028667</v>
+        <v>0.1877326014028667</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2939479785564949</v>
+        <v>0.3159062438869104</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9296,13 +9296,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.2225671756462305</v>
+        <v>0.2080320863337236</v>
       </c>
       <c r="C98">
-        <v>-7846.935125696262</v>
+        <v>-7721.40829671801</v>
       </c>
       <c r="D98">
-        <v>1412.084874303739</v>
+        <v>1537.61170328199</v>
       </c>
       <c r="E98">
         <v>6436.620000000001</v>
@@ -9329,37 +9329,37 @@
         <v>592.8</v>
       </c>
       <c r="M98">
-        <v>2037.911616</v>
+        <v>1896.258816</v>
       </c>
       <c r="N98">
-        <v>-1445.111616</v>
+        <v>-1303.458816</v>
       </c>
       <c r="O98">
-        <v>-297.6929928960001</v>
+        <v>-268.5125160960001</v>
       </c>
       <c r="P98">
-        <v>-1147.418623104</v>
+        <v>-1034.946299904</v>
       </c>
       <c r="Q98">
-        <v>-693.8186231040002</v>
+        <v>-581.346299904</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>0.6953301078376772</v>
+        <v>0.6919528750250059</v>
       </c>
       <c r="T98">
-        <v>14.99105121774606</v>
+        <v>14.92269919226342</v>
       </c>
       <c r="U98">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.05992252021198547</v>
+        <v>0.06439880409236287</v>
       </c>
       <c r="W98">
-        <v>0.2028687201382535</v>
+        <v>0.1878687201382535</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2908860204465314</v>
+        <v>0.3126155538464217</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9378,13 +9378,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.2242671756462305</v>
+        <v>0.2095820863337236</v>
       </c>
       <c r="C99">
-        <v>-7958.756026555894</v>
+        <v>-7834.329937825027</v>
       </c>
       <c r="D99">
-        <v>1398.633973444105</v>
+        <v>1523.060062174972</v>
       </c>
       <c r="E99">
         <v>6534.99</v>
@@ -9411,37 +9411,37 @@
         <v>592.8</v>
       </c>
       <c r="M99">
-        <v>2059.139862</v>
+        <v>1916.011512</v>
       </c>
       <c r="N99">
-        <v>-1466.339862</v>
+        <v>-1323.211512</v>
       </c>
       <c r="O99">
-        <v>-302.066011572</v>
+        <v>-272.5815714720001</v>
       </c>
       <c r="P99">
-        <v>-1164.273850428</v>
+        <v>-1050.629940528</v>
       </c>
       <c r="Q99">
-        <v>-710.6738504279999</v>
+        <v>-597.029940528</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>0.9118401437835698</v>
+        <v>0.9073371667000077</v>
       </c>
       <c r="T99">
-        <v>19.98806829032809</v>
+        <v>19.89693225635122</v>
       </c>
       <c r="U99">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.05930476227165574</v>
+        <v>0.06373489889553441</v>
       </c>
       <c r="W99">
-        <v>0.2030020323017767</v>
+        <v>0.1880020323017767</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2878871954934744</v>
+        <v>0.3093927130851184</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9460,13 +9460,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.2259671756462305</v>
+        <v>0.2111320863337237</v>
       </c>
       <c r="C100">
-        <v>-8070.323090595594</v>
+        <v>-7946.978733603399</v>
       </c>
       <c r="D100">
-        <v>1385.436909404406</v>
+        <v>1508.781266396601</v>
       </c>
       <c r="E100">
         <v>6633.360000000001</v>
@@ -9493,37 +9493,37 @@
         <v>592.8</v>
       </c>
       <c r="M100">
-        <v>2080.368108</v>
+        <v>1935.764208</v>
       </c>
       <c r="N100">
-        <v>-1487.568108</v>
+        <v>-1342.964208</v>
       </c>
       <c r="O100">
-        <v>-306.4390302480001</v>
+        <v>-276.6506268480001</v>
       </c>
       <c r="P100">
-        <v>-1181.129077752</v>
+        <v>-1066.313581152</v>
       </c>
       <c r="Q100">
-        <v>-727.5290777519999</v>
+        <v>-612.713581152</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>1.344860215675355</v>
+        <v>1.338105750050012</v>
       </c>
       <c r="T100">
-        <v>29.98210243549213</v>
+        <v>29.84539838452684</v>
       </c>
       <c r="U100">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.05869961163623068</v>
+        <v>0.06308454278435548</v>
       </c>
       <c r="W100">
-        <v>0.2031326238089014</v>
+        <v>0.1881326238089014</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2849495710496635</v>
+        <v>0.3062356445842499</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9542,13 +9542,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.2276671756462305</v>
+        <v>0.2126820863337237</v>
       </c>
       <c r="C101">
-        <v>-8181.643436020042</v>
+        <v>-8059.362286611346</v>
       </c>
       <c r="D101">
-        <v>1372.486563979957</v>
+        <v>1494.767713388653</v>
       </c>
       <c r="E101">
         <v>6731.73</v>
@@ -9575,37 +9575,37 @@
         <v>592.8</v>
       </c>
       <c r="M101">
-        <v>2101.596354</v>
+        <v>1955.516904</v>
       </c>
       <c r="N101">
-        <v>-1508.796354</v>
+        <v>-1362.716904</v>
       </c>
       <c r="O101">
-        <v>-310.812048924</v>
+        <v>-280.719682224</v>
       </c>
       <c r="P101">
-        <v>-1197.984305076</v>
+        <v>-1081.997221776</v>
       </c>
       <c r="Q101">
-        <v>-744.3843050759997</v>
+        <v>-628.3972217759997</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>2.643920431350709</v>
+        <v>2.630411500100024</v>
       </c>
       <c r="T101">
-        <v>59.96420487098425</v>
+        <v>59.69079676905368</v>
       </c>
       <c r="U101">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V101">
-        <v>0.05810668626616775</v>
+        <v>0.0624473251804731</v>
       </c>
       <c r="W101">
-        <v>0.203260577103761</v>
+        <v>0.188260577103761</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
@@ -9613,7 +9613,7 @@
         </is>
       </c>
       <c r="Y101">
-        <v>0.2820712925542124</v>
+        <v>0.3031423552450151</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/sweden/sweden_telecom_wireless.xlsx
+++ b/research/traditional_assets/database/data/sweden/sweden_telecom_wireless.xlsx
@@ -1157,7 +1157,7 @@
         <v>6830.1</v>
       </c>
       <c r="L2">
-        <v>6691.44071835918</v>
+        <v>6691.44071835919</v>
       </c>
       <c r="M2">
         <v>9652.5</v>
@@ -1284,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1421,22 +1421,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07334929072204935</v>
+        <v>0.07323392118316192</v>
       </c>
       <c r="C2">
-        <v>9239.177926605858</v>
+        <v>9178.886114925792</v>
       </c>
       <c r="D2">
-        <v>9054.677926605858</v>
+        <v>9092.756114925793</v>
       </c>
       <c r="E2">
-        <v>-3006.9</v>
+        <v>-2908.53</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>98.37</v>
       </c>
       <c r="G2">
         <v>184.5</v>
@@ -1457,28 +1457,28 @@
         <v>592.8</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>4.948011000000001</v>
       </c>
       <c r="N2">
-        <v>592.8</v>
+        <v>587.851989</v>
       </c>
       <c r="O2">
-        <v>122.1168</v>
+        <v>121.097509734</v>
       </c>
       <c r="P2">
-        <v>470.6831999999999</v>
+        <v>466.754479266</v>
       </c>
       <c r="Q2">
-        <v>924.2832000000001</v>
+        <v>920.3544792660001</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07334929072204935</v>
+        <v>0.07357024159915346</v>
       </c>
       <c r="T2">
-        <v>0.6362422799549505</v>
+        <v>0.6413450715739831</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>119.8057158724991</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1503,22 +1503,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07323392118316192</v>
+        <v>0.0731185516442745</v>
       </c>
       <c r="C3">
-        <v>9178.886114925792</v>
+        <v>9118.915920810621</v>
       </c>
       <c r="D3">
-        <v>9092.756114925793</v>
+        <v>9131.155920810621</v>
       </c>
       <c r="E3">
-        <v>-2908.53</v>
+        <v>-2810.16</v>
       </c>
       <c r="F3">
-        <v>98.37</v>
+        <v>196.74</v>
       </c>
       <c r="G3">
         <v>184.5</v>
@@ -1539,28 +1539,28 @@
         <v>592.8</v>
       </c>
       <c r="M3">
-        <v>4.948011000000001</v>
+        <v>9.896022000000002</v>
       </c>
       <c r="N3">
-        <v>587.851989</v>
+        <v>582.9039779999999</v>
       </c>
       <c r="O3">
-        <v>121.097509734</v>
+        <v>120.078219468</v>
       </c>
       <c r="P3">
-        <v>466.754479266</v>
+        <v>462.825758532</v>
       </c>
       <c r="Q3">
-        <v>920.3544792660001</v>
+        <v>916.4257585320001</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07357024159915346</v>
+        <v>0.07379570167783113</v>
       </c>
       <c r="T3">
-        <v>0.6413450715739831</v>
+        <v>0.6465520017974858</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>119.8057158724991</v>
+        <v>59.90285793624952</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1585,22 +1585,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.0731185516442745</v>
+        <v>0.07300318210538709</v>
       </c>
       <c r="C4">
-        <v>9118.915920810621</v>
+        <v>9059.271436230538</v>
       </c>
       <c r="D4">
-        <v>9131.155920810621</v>
+        <v>9169.881436230538</v>
       </c>
       <c r="E4">
-        <v>-2810.16</v>
+        <v>-2711.79</v>
       </c>
       <c r="F4">
-        <v>196.74</v>
+        <v>295.11</v>
       </c>
       <c r="G4">
         <v>184.5</v>
@@ -1621,28 +1621,28 @@
         <v>592.8</v>
       </c>
       <c r="M4">
-        <v>9.896022000000002</v>
+        <v>14.844033</v>
       </c>
       <c r="N4">
-        <v>582.9039779999999</v>
+        <v>577.955967</v>
       </c>
       <c r="O4">
-        <v>120.078219468</v>
+        <v>119.058929202</v>
       </c>
       <c r="P4">
-        <v>462.825758532</v>
+        <v>458.897037798</v>
       </c>
       <c r="Q4">
-        <v>916.4257585320001</v>
+        <v>912.4970377980001</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07379570167783113</v>
+        <v>0.07402581041792483</v>
       </c>
       <c r="T4">
-        <v>0.6465520017974858</v>
+        <v>0.6518662914070401</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>59.90285793624952</v>
+        <v>39.93523862416635</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1667,22 +1667,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07300318210538709</v>
+        <v>0.07288781256649966</v>
       </c>
       <c r="C5">
-        <v>9059.271436230538</v>
+        <v>8999.956822868093</v>
       </c>
       <c r="D5">
-        <v>9169.881436230538</v>
+        <v>9208.936822868092</v>
       </c>
       <c r="E5">
-        <v>-2711.79</v>
+        <v>-2613.42</v>
       </c>
       <c r="F5">
-        <v>295.11</v>
+        <v>393.48</v>
       </c>
       <c r="G5">
         <v>184.5</v>
@@ -1703,28 +1703,28 @@
         <v>592.8</v>
       </c>
       <c r="M5">
-        <v>14.844033</v>
+        <v>19.792044</v>
       </c>
       <c r="N5">
-        <v>577.955967</v>
+        <v>573.0079559999999</v>
       </c>
       <c r="O5">
-        <v>119.058929202</v>
+        <v>118.039638936</v>
       </c>
       <c r="P5">
-        <v>458.897037798</v>
+        <v>454.968317064</v>
       </c>
       <c r="Q5">
-        <v>912.4970377980001</v>
+        <v>908.5683170640001</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.07402581041792483</v>
+        <v>0.07426071309010382</v>
       </c>
       <c r="T5">
-        <v>0.6518662914070401</v>
+        <v>0.6572912953834602</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>39.93523862416635</v>
+        <v>29.95142896812476</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1749,22 +1749,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07288781256649966</v>
+        <v>0.07277244302761225</v>
       </c>
       <c r="C6">
-        <v>8999.956822868093</v>
+        <v>8940.976313609068</v>
       </c>
       <c r="D6">
-        <v>9208.936822868092</v>
+        <v>9248.326313609068</v>
       </c>
       <c r="E6">
-        <v>-2613.42</v>
+        <v>-2515.05</v>
       </c>
       <c r="F6">
-        <v>393.48</v>
+        <v>491.85</v>
       </c>
       <c r="G6">
         <v>184.5</v>
@@ -1785,28 +1785,28 @@
         <v>592.8</v>
       </c>
       <c r="M6">
-        <v>19.792044</v>
+        <v>24.740055</v>
       </c>
       <c r="N6">
-        <v>573.0079559999999</v>
+        <v>568.059945</v>
       </c>
       <c r="O6">
-        <v>118.039638936</v>
+        <v>117.02034867</v>
       </c>
       <c r="P6">
-        <v>454.968317064</v>
+        <v>451.03959633</v>
       </c>
       <c r="Q6">
-        <v>908.5683170640001</v>
+        <v>904.6395963300001</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.07426071309010382</v>
+        <v>0.0745005610816971</v>
       </c>
       <c r="T6">
-        <v>0.6572912953834602</v>
+        <v>0.6628305099699101</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>29.95142896812476</v>
+        <v>23.96114317449981</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1831,22 +1831,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07277244302761225</v>
+        <v>0.07265707348872481</v>
       </c>
       <c r="C7">
-        <v>8940.976313609068</v>
+        <v>8882.334214071849</v>
       </c>
       <c r="D7">
-        <v>9248.326313609068</v>
+        <v>9288.054214071848</v>
       </c>
       <c r="E7">
-        <v>-2515.05</v>
+        <v>-2416.68</v>
       </c>
       <c r="F7">
-        <v>491.85</v>
+        <v>590.22</v>
       </c>
       <c r="G7">
         <v>184.5</v>
@@ -1867,28 +1867,28 @@
         <v>592.8</v>
       </c>
       <c r="M7">
-        <v>24.740055</v>
+        <v>29.688066</v>
       </c>
       <c r="N7">
-        <v>568.059945</v>
+        <v>563.1119339999999</v>
       </c>
       <c r="O7">
-        <v>117.02034867</v>
+        <v>116.001058404</v>
       </c>
       <c r="P7">
-        <v>451.03959633</v>
+        <v>447.1108755959999</v>
       </c>
       <c r="Q7">
-        <v>904.6395963300001</v>
+        <v>900.7108755960001</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.0745005610816971</v>
+        <v>0.07474551222204769</v>
       </c>
       <c r="T7">
-        <v>0.6628305099699101</v>
+        <v>0.6684875801858589</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>23.96114317449981</v>
+        <v>19.96761931208317</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1913,22 +1913,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07265707348872481</v>
+        <v>0.0725417039498374</v>
       </c>
       <c r="C8">
-        <v>8882.334214071849</v>
+        <v>8824.034904176293</v>
       </c>
       <c r="D8">
-        <v>9288.054214071848</v>
+        <v>9328.124904176293</v>
       </c>
       <c r="E8">
-        <v>-2416.68</v>
+        <v>-2318.31</v>
       </c>
       <c r="F8">
-        <v>590.22</v>
+        <v>688.5899999999999</v>
       </c>
       <c r="G8">
         <v>184.5</v>
@@ -1949,28 +1949,28 @@
         <v>592.8</v>
       </c>
       <c r="M8">
-        <v>29.688066</v>
+        <v>34.636077</v>
       </c>
       <c r="N8">
-        <v>563.1119339999999</v>
+        <v>558.163923</v>
       </c>
       <c r="O8">
-        <v>116.001058404</v>
+        <v>114.981768138</v>
       </c>
       <c r="P8">
-        <v>447.1108755959999</v>
+        <v>443.1821548619999</v>
       </c>
       <c r="Q8">
-        <v>900.7108755960001</v>
+        <v>896.7821548620001</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07474551222204769</v>
+        <v>0.07499573112885742</v>
       </c>
       <c r="T8">
-        <v>0.6684875801858589</v>
+        <v>0.6742663078258065</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>19.96761931208317</v>
+        <v>17.11510226749986</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1995,22 +1995,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07254170394983739</v>
+        <v>0.07242633441094999</v>
       </c>
       <c r="C9">
-        <v>8824.034904176298</v>
+        <v>8766.082839753501</v>
       </c>
       <c r="D9">
-        <v>9328.124904176299</v>
+        <v>9368.542839753502</v>
       </c>
       <c r="E9">
-        <v>-2318.31</v>
+        <v>-2219.94</v>
       </c>
       <c r="F9">
-        <v>688.59</v>
+        <v>786.96</v>
       </c>
       <c r="G9">
         <v>184.5</v>
@@ -2031,28 +2031,28 @@
         <v>592.8</v>
       </c>
       <c r="M9">
-        <v>34.63607700000001</v>
+        <v>39.58408800000001</v>
       </c>
       <c r="N9">
-        <v>558.163923</v>
+        <v>553.2159119999999</v>
       </c>
       <c r="O9">
-        <v>114.981768138</v>
+        <v>113.962477872</v>
       </c>
       <c r="P9">
-        <v>443.1821548619999</v>
+        <v>439.2534341279999</v>
       </c>
       <c r="Q9">
-        <v>896.7821548620001</v>
+        <v>892.8534341280001</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.07499573112885742</v>
+        <v>0.07525138957711955</v>
       </c>
       <c r="T9">
-        <v>0.6742663078258065</v>
+        <v>0.6801706599796662</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>17.11510226749986</v>
+        <v>14.97571448406238</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2077,22 +2077,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07242633441094999</v>
+        <v>0.07231096487206257</v>
       </c>
       <c r="C10">
-        <v>8766.082839753501</v>
+        <v>8708.482554197522</v>
       </c>
       <c r="D10">
-        <v>9368.542839753502</v>
+        <v>9409.312554197522</v>
       </c>
       <c r="E10">
-        <v>-2219.94</v>
+        <v>-2121.57</v>
       </c>
       <c r="F10">
-        <v>786.96</v>
+        <v>885.3299999999999</v>
       </c>
       <c r="G10">
         <v>184.5</v>
@@ -2113,28 +2113,28 @@
         <v>592.8</v>
       </c>
       <c r="M10">
-        <v>39.58408800000001</v>
+        <v>44.532099</v>
       </c>
       <c r="N10">
-        <v>553.2159119999999</v>
+        <v>548.2679009999999</v>
       </c>
       <c r="O10">
-        <v>113.962477872</v>
+        <v>112.943187606</v>
       </c>
       <c r="P10">
-        <v>439.2534341279999</v>
+        <v>435.324713394</v>
       </c>
       <c r="Q10">
-        <v>892.8534341280001</v>
+        <v>888.924713394</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.07525138957711955</v>
+        <v>0.07551266689237644</v>
       </c>
       <c r="T10">
-        <v>0.6801706599796662</v>
+        <v>0.6862047781149294</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>14.97571448406238</v>
+        <v>13.31174620805545</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07231096487206257</v>
+        <v>0.07219559533317513</v>
       </c>
       <c r="C11">
-        <v>8708.482554197522</v>
+        <v>8651.238660160405</v>
       </c>
       <c r="D11">
-        <v>9409.312554197522</v>
+        <v>9450.438660160406</v>
       </c>
       <c r="E11">
-        <v>-2121.57</v>
+        <v>-2023.2</v>
       </c>
       <c r="F11">
-        <v>885.3299999999999</v>
+        <v>983.6999999999999</v>
       </c>
       <c r="G11">
         <v>184.5</v>
@@ -2195,28 +2195,28 @@
         <v>592.8</v>
       </c>
       <c r="M11">
-        <v>44.532099</v>
+        <v>49.48011</v>
       </c>
       <c r="N11">
-        <v>548.2679009999999</v>
+        <v>543.31989</v>
       </c>
       <c r="O11">
-        <v>112.943187606</v>
+        <v>111.92389734</v>
       </c>
       <c r="P11">
-        <v>435.324713394</v>
+        <v>431.39599266</v>
       </c>
       <c r="Q11">
-        <v>888.924713394</v>
+        <v>884.9959926600002</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.07551266689237644</v>
+        <v>0.07577975037019459</v>
       </c>
       <c r="T11">
-        <v>0.6862047781149294</v>
+        <v>0.6923729877643094</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>13.31174620805545</v>
+        <v>11.98057158724991</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2241,22 +2241,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07219559533317513</v>
+        <v>0.07208022579428772</v>
       </c>
       <c r="C12">
-        <v>8651.238660160405</v>
+        <v>8594.355851291901</v>
       </c>
       <c r="D12">
-        <v>9450.438660160406</v>
+        <v>9491.9258512919</v>
       </c>
       <c r="E12">
-        <v>-2023.2</v>
+        <v>-1924.83</v>
       </c>
       <c r="F12">
-        <v>983.7</v>
+        <v>1082.07</v>
       </c>
       <c r="G12">
         <v>184.5</v>
@@ -2277,28 +2277,28 @@
         <v>592.8</v>
       </c>
       <c r="M12">
-        <v>49.48011</v>
+        <v>54.428121</v>
       </c>
       <c r="N12">
-        <v>543.31989</v>
+        <v>538.3718789999999</v>
       </c>
       <c r="O12">
-        <v>111.92389734</v>
+        <v>110.904607074</v>
       </c>
       <c r="P12">
-        <v>431.39599266</v>
+        <v>427.4672719259999</v>
       </c>
       <c r="Q12">
-        <v>884.9959926600002</v>
+        <v>881.0672719260001</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.07577975037019459</v>
+        <v>0.07605283572391879</v>
       </c>
       <c r="T12">
-        <v>0.6923729877643094</v>
+        <v>0.6986798088664847</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>11.98057158724991</v>
+        <v>10.89142871568173</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2323,22 +2323,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07208022579428772</v>
+        <v>0.07196485625540029</v>
       </c>
       <c r="C13">
-        <v>8594.355851291901</v>
+        <v>8537.838904025228</v>
       </c>
       <c r="D13">
-        <v>9491.9258512919</v>
+        <v>9533.778904025228</v>
       </c>
       <c r="E13">
-        <v>-1924.83</v>
+        <v>-1826.46</v>
       </c>
       <c r="F13">
-        <v>1082.07</v>
+        <v>1180.44</v>
       </c>
       <c r="G13">
         <v>184.5</v>
@@ -2359,28 +2359,28 @@
         <v>592.8</v>
       </c>
       <c r="M13">
-        <v>54.428121</v>
+        <v>59.37613200000001</v>
       </c>
       <c r="N13">
-        <v>538.3718789999999</v>
+        <v>533.423868</v>
       </c>
       <c r="O13">
-        <v>110.904607074</v>
+        <v>109.885316808</v>
       </c>
       <c r="P13">
-        <v>427.4672719259999</v>
+        <v>423.538551192</v>
       </c>
       <c r="Q13">
-        <v>881.0672719260001</v>
+        <v>877.1385511920001</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.07605283572391879</v>
+        <v>0.07633212756295488</v>
       </c>
       <c r="T13">
-        <v>0.6986798088664847</v>
+        <v>0.7051299668118911</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>10.89142871568173</v>
+        <v>9.983809656041588</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2405,22 +2405,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07196485625540029</v>
+        <v>0.07184948671651288</v>
       </c>
       <c r="C14">
-        <v>8537.838904025228</v>
+        <v>8481.692679410202</v>
       </c>
       <c r="D14">
-        <v>9533.778904025228</v>
+        <v>9576.002679410201</v>
       </c>
       <c r="E14">
-        <v>-1826.46</v>
+        <v>-1728.09</v>
       </c>
       <c r="F14">
-        <v>1180.44</v>
+        <v>1278.81</v>
       </c>
       <c r="G14">
         <v>184.5</v>
@@ -2441,28 +2441,28 @@
         <v>592.8</v>
       </c>
       <c r="M14">
-        <v>59.37613200000001</v>
+        <v>64.32414300000001</v>
       </c>
       <c r="N14">
-        <v>533.423868</v>
+        <v>528.4758569999999</v>
       </c>
       <c r="O14">
-        <v>109.885316808</v>
+        <v>108.866026542</v>
       </c>
       <c r="P14">
-        <v>423.538551192</v>
+        <v>419.6098304579999</v>
       </c>
       <c r="Q14">
-        <v>877.1385511920001</v>
+        <v>873.2098304580001</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.07633212756295488</v>
+        <v>0.07661783990403778</v>
       </c>
       <c r="T14">
-        <v>0.7051299668118911</v>
+        <v>0.7117284042502953</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>9.983809656041588</v>
+        <v>9.215824297884541</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2487,22 +2487,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07184948671651288</v>
+        <v>0.07190085717762545</v>
       </c>
       <c r="C15">
-        <v>8481.692679410202</v>
+        <v>8364.475648069092</v>
       </c>
       <c r="D15">
-        <v>9576.002679410201</v>
+        <v>9557.155648069092</v>
       </c>
       <c r="E15">
-        <v>-1728.09</v>
+        <v>-1629.72</v>
       </c>
       <c r="F15">
-        <v>1278.81</v>
+        <v>1377.18</v>
       </c>
       <c r="G15">
         <v>184.5</v>
@@ -2523,45 +2523,45 @@
         <v>592.8</v>
       </c>
       <c r="M15">
-        <v>64.32414300000001</v>
+        <v>71.33792400000002</v>
       </c>
       <c r="N15">
-        <v>528.4758569999999</v>
+        <v>521.4620759999999</v>
       </c>
       <c r="O15">
-        <v>108.866026542</v>
+        <v>107.421187656</v>
       </c>
       <c r="P15">
-        <v>419.6098304579999</v>
+        <v>414.0408883439999</v>
       </c>
       <c r="Q15">
-        <v>873.2098304580001</v>
+        <v>867.6408883440001</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.07661783990403778</v>
+        <v>0.07691019671816912</v>
       </c>
       <c r="T15">
-        <v>0.7117284042502953</v>
+        <v>0.7184802937221508</v>
       </c>
       <c r="U15">
-        <v>0.0503</v>
+        <v>0.05180000000000001</v>
       </c>
       <c r="V15">
         <v>0.206</v>
       </c>
       <c r="W15">
-        <v>0.03993820000000001</v>
+        <v>0.0411292</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y15">
-        <v>9.215824297884541</v>
+        <v>8.309745598988833</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2569,22 +2569,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07190085717762545</v>
+        <v>0.07179739763873803</v>
       </c>
       <c r="C16">
-        <v>8364.475648069092</v>
+        <v>8304.139413223769</v>
       </c>
       <c r="D16">
-        <v>9557.155648069092</v>
+        <v>9595.18941322377</v>
       </c>
       <c r="E16">
-        <v>-1629.72</v>
+        <v>-1531.35</v>
       </c>
       <c r="F16">
-        <v>1377.18</v>
+        <v>1475.55</v>
       </c>
       <c r="G16">
         <v>184.5</v>
@@ -2605,28 +2605,28 @@
         <v>592.8</v>
       </c>
       <c r="M16">
-        <v>71.33792400000002</v>
+        <v>76.43349000000002</v>
       </c>
       <c r="N16">
-        <v>521.4620759999999</v>
+        <v>516.3665099999999</v>
       </c>
       <c r="O16">
-        <v>107.421187656</v>
+        <v>106.37150106</v>
       </c>
       <c r="P16">
-        <v>414.0408883439999</v>
+        <v>409.9950089399999</v>
       </c>
       <c r="Q16">
-        <v>867.6408883440001</v>
+        <v>863.5950089400001</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.07691019671816912</v>
+        <v>0.07720943251616239</v>
       </c>
       <c r="T16">
-        <v>0.7184802937221508</v>
+        <v>0.7253910511815794</v>
       </c>
       <c r="U16">
         <v>0.05180000000000001</v>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>8.309745598988833</v>
+        <v>7.755762559056244</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2651,22 +2651,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07179739763873803</v>
+        <v>0.0716939380998506</v>
       </c>
       <c r="C17">
-        <v>8304.139413223771</v>
+        <v>8244.107107104155</v>
       </c>
       <c r="D17">
-        <v>9595.18941322377</v>
+        <v>9633.527107104155</v>
       </c>
       <c r="E17">
-        <v>-1531.35</v>
+        <v>-1432.98</v>
       </c>
       <c r="F17">
-        <v>1475.55</v>
+        <v>1573.92</v>
       </c>
       <c r="G17">
         <v>184.5</v>
@@ -2687,28 +2687,28 @@
         <v>592.8</v>
       </c>
       <c r="M17">
-        <v>76.43349000000001</v>
+        <v>81.52905600000001</v>
       </c>
       <c r="N17">
-        <v>516.3665099999999</v>
+        <v>511.2709439999999</v>
       </c>
       <c r="O17">
-        <v>106.37150106</v>
+        <v>105.321814464</v>
       </c>
       <c r="P17">
-        <v>409.9950089399999</v>
+        <v>405.9491295359999</v>
       </c>
       <c r="Q17">
-        <v>863.5950089400001</v>
+        <v>859.549129536</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.07720943251616239</v>
+        <v>0.07751579297601263</v>
       </c>
       <c r="T17">
-        <v>0.7253910511815794</v>
+        <v>0.7324663504852802</v>
       </c>
       <c r="U17">
         <v>0.05180000000000001</v>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>7.755762559056245</v>
+        <v>7.271027399115229</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2733,22 +2733,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.0716939380998506</v>
+        <v>0.07159047856096318</v>
       </c>
       <c r="C18">
-        <v>8244.107107104155</v>
+        <v>8184.38238737705</v>
       </c>
       <c r="D18">
-        <v>9633.527107104155</v>
+        <v>9672.17238737705</v>
       </c>
       <c r="E18">
-        <v>-1432.98</v>
+        <v>-1334.61</v>
       </c>
       <c r="F18">
-        <v>1573.92</v>
+        <v>1672.29</v>
       </c>
       <c r="G18">
         <v>184.5</v>
@@ -2769,28 +2769,28 @@
         <v>592.8</v>
       </c>
       <c r="M18">
-        <v>81.52905600000001</v>
+        <v>86.62462200000002</v>
       </c>
       <c r="N18">
-        <v>511.2709439999999</v>
+        <v>506.1753779999999</v>
       </c>
       <c r="O18">
-        <v>105.321814464</v>
+        <v>104.272127868</v>
       </c>
       <c r="P18">
-        <v>405.9491295359999</v>
+        <v>401.9032501319999</v>
       </c>
       <c r="Q18">
-        <v>859.549129536</v>
+        <v>855.5032501320001</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.07751579297601263</v>
+        <v>0.07782953561561828</v>
       </c>
       <c r="T18">
-        <v>0.7324663504852802</v>
+        <v>0.739712138928829</v>
       </c>
       <c r="U18">
         <v>0.05180000000000001</v>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>7.271027399115229</v>
+        <v>6.843319905049627</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2815,22 +2815,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07159047856096318</v>
+        <v>0.07172998302207577</v>
       </c>
       <c r="C19">
-        <v>8184.38238737705</v>
+        <v>8033.975670054851</v>
       </c>
       <c r="D19">
-        <v>9672.17238737705</v>
+        <v>9620.135670054851</v>
       </c>
       <c r="E19">
-        <v>-1334.61</v>
+        <v>-1236.24</v>
       </c>
       <c r="F19">
-        <v>1672.29</v>
+        <v>1770.66</v>
       </c>
       <c r="G19">
         <v>184.5</v>
@@ -2851,45 +2851,45 @@
         <v>592.8</v>
       </c>
       <c r="M19">
-        <v>86.62462200000002</v>
+        <v>94.73031000000003</v>
       </c>
       <c r="N19">
-        <v>506.1753779999999</v>
+        <v>498.0696899999999</v>
       </c>
       <c r="O19">
-        <v>104.272127868</v>
+        <v>102.60235614</v>
       </c>
       <c r="P19">
-        <v>401.9032501319999</v>
+        <v>395.4673338599999</v>
       </c>
       <c r="Q19">
-        <v>855.5032501320001</v>
+        <v>849.0673338600001</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.07782953561561828</v>
+        <v>0.07815093051472655</v>
       </c>
       <c r="T19">
-        <v>0.739712138928829</v>
+        <v>0.7471346539197816</v>
       </c>
       <c r="U19">
-        <v>0.05180000000000001</v>
+        <v>0.05350000000000001</v>
       </c>
       <c r="V19">
         <v>0.206</v>
       </c>
       <c r="W19">
-        <v>0.0411292</v>
+        <v>0.04247900000000001</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y19">
-        <v>6.843319905049627</v>
+        <v>6.257764806216719</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2897,22 +2897,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07172998302207577</v>
+        <v>0.07164002148318835</v>
       </c>
       <c r="C20">
-        <v>8033.975670054851</v>
+        <v>7969.097987766235</v>
       </c>
       <c r="D20">
-        <v>9620.135670054851</v>
+        <v>9653.627987766235</v>
       </c>
       <c r="E20">
-        <v>-1236.24</v>
+        <v>-1137.87</v>
       </c>
       <c r="F20">
-        <v>1770.66</v>
+        <v>1869.03</v>
       </c>
       <c r="G20">
         <v>184.5</v>
@@ -2933,28 +2933,28 @@
         <v>592.8</v>
       </c>
       <c r="M20">
-        <v>94.73031</v>
+        <v>99.99310500000001</v>
       </c>
       <c r="N20">
-        <v>498.0696899999999</v>
+        <v>492.8068949999999</v>
       </c>
       <c r="O20">
-        <v>102.60235614</v>
+        <v>101.51822037</v>
       </c>
       <c r="P20">
-        <v>395.4673338599999</v>
+        <v>391.2886746299999</v>
       </c>
       <c r="Q20">
-        <v>849.0673338600001</v>
+        <v>844.8886746300001</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.07815093051472655</v>
+        <v>0.07848026109035597</v>
       </c>
       <c r="T20">
-        <v>0.7471346539197816</v>
+        <v>0.7547404408858195</v>
       </c>
       <c r="U20">
         <v>0.05350000000000001</v>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>6.257764806216721</v>
+        <v>5.928408763784262</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2979,22 +2979,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07164002148318835</v>
+        <v>0.07155005994430091</v>
       </c>
       <c r="C21">
-        <v>7969.097987766235</v>
+        <v>7904.454325938059</v>
       </c>
       <c r="D21">
-        <v>9653.627987766235</v>
+        <v>9687.354325938059</v>
       </c>
       <c r="E21">
-        <v>-1137.87</v>
+        <v>-1039.5</v>
       </c>
       <c r="F21">
-        <v>1869.03</v>
+        <v>1967.4</v>
       </c>
       <c r="G21">
         <v>184.5</v>
@@ -3015,28 +3015,28 @@
         <v>592.8</v>
       </c>
       <c r="M21">
-        <v>99.99310500000001</v>
+        <v>105.2559</v>
       </c>
       <c r="N21">
-        <v>492.8068949999999</v>
+        <v>487.5441</v>
       </c>
       <c r="O21">
-        <v>101.51822037</v>
+        <v>100.4340846</v>
       </c>
       <c r="P21">
-        <v>391.2886746299999</v>
+        <v>387.1100154</v>
       </c>
       <c r="Q21">
-        <v>844.8886746300001</v>
+        <v>840.7100154000001</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.07848026109035597</v>
+        <v>0.07881782493037615</v>
       </c>
       <c r="T21">
-        <v>0.7547404408858195</v>
+        <v>0.7625363725260083</v>
       </c>
       <c r="U21">
         <v>0.05350000000000001</v>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>5.928408763784262</v>
+        <v>5.631988325595048</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3061,22 +3061,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07155005994430091</v>
+        <v>0.0715934904054135</v>
       </c>
       <c r="C22">
-        <v>7904.454325938059</v>
+        <v>7789.772990840571</v>
       </c>
       <c r="D22">
-        <v>9687.354325938059</v>
+        <v>9671.042990840571</v>
       </c>
       <c r="E22">
-        <v>-1039.5</v>
+        <v>-941.1300000000001</v>
       </c>
       <c r="F22">
-        <v>1967.4</v>
+        <v>2065.77</v>
       </c>
       <c r="G22">
         <v>184.5</v>
@@ -3097,45 +3097,45 @@
         <v>592.8</v>
       </c>
       <c r="M22">
-        <v>105.2559</v>
+        <v>112.171311</v>
       </c>
       <c r="N22">
-        <v>487.5441</v>
+        <v>480.628689</v>
       </c>
       <c r="O22">
-        <v>100.4340846</v>
+        <v>99.00950993399999</v>
       </c>
       <c r="P22">
-        <v>387.1100154</v>
+        <v>381.619179066</v>
       </c>
       <c r="Q22">
-        <v>840.7100154000001</v>
+        <v>835.2191790660002</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.07881782493037615</v>
+        <v>0.07916393469039684</v>
       </c>
       <c r="T22">
-        <v>0.7625363725260083</v>
+        <v>0.7705296695241765</v>
       </c>
       <c r="U22">
-        <v>0.05350000000000001</v>
+        <v>0.05430000000000001</v>
       </c>
       <c r="V22">
         <v>0.206</v>
       </c>
       <c r="W22">
-        <v>0.04247900000000001</v>
+        <v>0.04311420000000001</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y22">
-        <v>5.631988325595048</v>
+        <v>5.284773751106465</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3143,22 +3143,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.0715934904054135</v>
+        <v>0.07150988086652607</v>
       </c>
       <c r="C23">
-        <v>7789.772990840571</v>
+        <v>7722.853601180721</v>
       </c>
       <c r="D23">
-        <v>9671.042990840571</v>
+        <v>9702.49360118072</v>
       </c>
       <c r="E23">
-        <v>-941.1300000000001</v>
+        <v>-842.7600000000002</v>
       </c>
       <c r="F23">
-        <v>2065.77</v>
+        <v>2164.14</v>
       </c>
       <c r="G23">
         <v>184.5</v>
@@ -3179,28 +3179,28 @@
         <v>592.8</v>
       </c>
       <c r="M23">
-        <v>112.171311</v>
+        <v>117.512802</v>
       </c>
       <c r="N23">
-        <v>480.628689</v>
+        <v>475.2871979999999</v>
       </c>
       <c r="O23">
-        <v>99.00950993399999</v>
+        <v>97.90916278799999</v>
       </c>
       <c r="P23">
-        <v>381.619179066</v>
+        <v>377.3780352119999</v>
       </c>
       <c r="Q23">
-        <v>835.2191790660002</v>
+        <v>830.9780352120001</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.07916393469039684</v>
+        <v>0.07951891905964881</v>
       </c>
       <c r="T23">
-        <v>0.7705296695241765</v>
+        <v>0.778727922855631</v>
       </c>
       <c r="U23">
         <v>0.05430000000000001</v>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>5.284773751106465</v>
+        <v>5.044556762419807</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.07150988086652607</v>
+        <v>0.07142627132763865</v>
       </c>
       <c r="C24">
-        <v>7722.853601180721</v>
+        <v>7656.139436151057</v>
       </c>
       <c r="D24">
-        <v>9702.49360118072</v>
+        <v>9734.149436151058</v>
       </c>
       <c r="E24">
-        <v>-842.7600000000002</v>
+        <v>-744.3899999999999</v>
       </c>
       <c r="F24">
-        <v>2164.14</v>
+        <v>2262.51</v>
       </c>
       <c r="G24">
         <v>184.5</v>
@@ -3261,28 +3261,28 @@
         <v>592.8</v>
       </c>
       <c r="M24">
-        <v>117.512802</v>
+        <v>122.854293</v>
       </c>
       <c r="N24">
-        <v>475.2871979999999</v>
+        <v>469.9457069999999</v>
       </c>
       <c r="O24">
-        <v>97.90916278799999</v>
+        <v>96.80881564199998</v>
       </c>
       <c r="P24">
-        <v>377.3780352119999</v>
+        <v>373.136891358</v>
       </c>
       <c r="Q24">
-        <v>830.9780352120001</v>
+        <v>826.7368913580001</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.07951891905964881</v>
+        <v>0.07988312380212811</v>
       </c>
       <c r="T24">
-        <v>0.778727922855631</v>
+        <v>0.7871391178320584</v>
       </c>
       <c r="U24">
         <v>0.05430000000000001</v>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>5.044556762419807</v>
+        <v>4.825228207531989</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3307,22 +3307,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.07142627132763865</v>
+        <v>0.07134266178875123</v>
       </c>
       <c r="C25">
-        <v>7656.139436151057</v>
+        <v>7589.632511054874</v>
       </c>
       <c r="D25">
-        <v>9734.149436151058</v>
+        <v>9766.012511054874</v>
       </c>
       <c r="E25">
-        <v>-744.3899999999999</v>
+        <v>-646.02</v>
       </c>
       <c r="F25">
-        <v>2262.51</v>
+        <v>2360.88</v>
       </c>
       <c r="G25">
         <v>184.5</v>
@@ -3343,28 +3343,28 @@
         <v>592.8</v>
       </c>
       <c r="M25">
-        <v>122.854293</v>
+        <v>128.195784</v>
       </c>
       <c r="N25">
-        <v>469.9457069999999</v>
+        <v>464.604216</v>
       </c>
       <c r="O25">
-        <v>96.80881564199998</v>
+        <v>95.70846849599999</v>
       </c>
       <c r="P25">
-        <v>373.136891358</v>
+        <v>368.8957475039999</v>
       </c>
       <c r="Q25">
-        <v>826.7368913580001</v>
+        <v>822.4957475040001</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.07988312380212811</v>
+        <v>0.08025691287993583</v>
       </c>
       <c r="T25">
-        <v>0.7871391178320584</v>
+        <v>0.7957716600447076</v>
       </c>
       <c r="U25">
         <v>0.05430000000000001</v>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>4.825228207531989</v>
+        <v>4.624177032218157</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3389,22 +3389,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.07134266178875123</v>
+        <v>0.07125905224986381</v>
       </c>
       <c r="C26">
-        <v>7589.632511054874</v>
+        <v>7523.334867669109</v>
       </c>
       <c r="D26">
-        <v>9766.012511054874</v>
+        <v>9798.084867669109</v>
       </c>
       <c r="E26">
-        <v>-646.02</v>
+        <v>-547.6500000000001</v>
       </c>
       <c r="F26">
-        <v>2360.88</v>
+        <v>2459.25</v>
       </c>
       <c r="G26">
         <v>184.5</v>
@@ -3425,28 +3425,28 @@
         <v>592.8</v>
       </c>
       <c r="M26">
-        <v>128.195784</v>
+        <v>133.537275</v>
       </c>
       <c r="N26">
-        <v>464.604216</v>
+        <v>459.2627249999999</v>
       </c>
       <c r="O26">
-        <v>95.70846849599999</v>
+        <v>94.60812134999999</v>
       </c>
       <c r="P26">
-        <v>368.8957475039999</v>
+        <v>364.65460365</v>
       </c>
       <c r="Q26">
-        <v>822.4957475040001</v>
+        <v>818.25460365</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.08025691287993583</v>
+        <v>0.08064066966648509</v>
       </c>
       <c r="T26">
-        <v>0.7957716600447076</v>
+        <v>0.8046344033830274</v>
       </c>
       <c r="U26">
         <v>0.05430000000000001</v>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>4.624177032218157</v>
+        <v>4.43920995092943</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3471,22 +3471,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.07125905224986381</v>
+        <v>0.07117544271097639</v>
       </c>
       <c r="C27">
-        <v>7523.334867669109</v>
+        <v>7457.248574680504</v>
       </c>
       <c r="D27">
-        <v>9798.084867669109</v>
+        <v>9830.368574680504</v>
       </c>
       <c r="E27">
-        <v>-547.6500000000001</v>
+        <v>-449.2800000000002</v>
       </c>
       <c r="F27">
-        <v>2459.25</v>
+        <v>2557.62</v>
       </c>
       <c r="G27">
         <v>184.5</v>
@@ -3507,28 +3507,28 @@
         <v>592.8</v>
       </c>
       <c r="M27">
-        <v>133.537275</v>
+        <v>138.878766</v>
       </c>
       <c r="N27">
-        <v>459.2627249999999</v>
+        <v>453.9212339999999</v>
       </c>
       <c r="O27">
-        <v>94.60812134999999</v>
+        <v>93.50777420399999</v>
       </c>
       <c r="P27">
-        <v>364.65460365</v>
+        <v>360.4134597959999</v>
       </c>
       <c r="Q27">
-        <v>818.25460365</v>
+        <v>814.013459796</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.08064066966648509</v>
+        <v>0.0810347982580762</v>
       </c>
       <c r="T27">
-        <v>0.8046344033830274</v>
+        <v>0.8137366803250857</v>
       </c>
       <c r="U27">
         <v>0.05430000000000001</v>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>4.43920995092943</v>
+        <v>4.268471106662914</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3553,22 +3553,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07117544271097639</v>
+        <v>0.07130621317208896</v>
       </c>
       <c r="C28">
-        <v>7457.248574680504</v>
+        <v>7308.478234075488</v>
       </c>
       <c r="D28">
-        <v>9830.368574680504</v>
+        <v>9779.968234075488</v>
       </c>
       <c r="E28">
-        <v>-449.2800000000002</v>
+        <v>-350.9099999999999</v>
       </c>
       <c r="F28">
-        <v>2557.62</v>
+        <v>2655.99</v>
       </c>
       <c r="G28">
         <v>184.5</v>
@@ -3589,45 +3589,45 @@
         <v>592.8</v>
       </c>
       <c r="M28">
-        <v>138.878766</v>
+        <v>146.876247</v>
       </c>
       <c r="N28">
-        <v>453.9212339999999</v>
+        <v>445.9237529999999</v>
       </c>
       <c r="O28">
-        <v>93.50777420399999</v>
+        <v>91.86029311799999</v>
       </c>
       <c r="P28">
-        <v>360.4134597959999</v>
+        <v>354.063459882</v>
       </c>
       <c r="Q28">
-        <v>814.013459796</v>
+        <v>807.6634598820001</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.0810347982580762</v>
+        <v>0.08143972489327256</v>
       </c>
       <c r="T28">
-        <v>0.8137366803250857</v>
+        <v>0.8230883347176112</v>
       </c>
       <c r="U28">
-        <v>0.05430000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V28">
         <v>0.206</v>
       </c>
       <c r="W28">
-        <v>0.04311420000000001</v>
+        <v>0.04390820000000001</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y28">
-        <v>4.268471106662914</v>
+        <v>4.036050839452616</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3635,22 +3635,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07130621317208896</v>
+        <v>0.07123054363320155</v>
       </c>
       <c r="C29">
-        <v>7308.478234075488</v>
+        <v>7239.208897328308</v>
       </c>
       <c r="D29">
-        <v>9779.968234075488</v>
+        <v>9809.068897328309</v>
       </c>
       <c r="E29">
-        <v>-350.9099999999999</v>
+        <v>-252.54</v>
       </c>
       <c r="F29">
-        <v>2655.99</v>
+        <v>2754.36</v>
       </c>
       <c r="G29">
         <v>184.5</v>
@@ -3671,28 +3671,28 @@
         <v>592.8</v>
       </c>
       <c r="M29">
-        <v>146.876247</v>
+        <v>152.316108</v>
       </c>
       <c r="N29">
-        <v>445.9237529999999</v>
+        <v>440.4838919999999</v>
       </c>
       <c r="O29">
-        <v>91.86029311799999</v>
+        <v>90.739681752</v>
       </c>
       <c r="P29">
-        <v>354.063459882</v>
+        <v>349.7442102479999</v>
       </c>
       <c r="Q29">
-        <v>807.6634598820001</v>
+        <v>803.3442102480001</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.08143972489327256</v>
+        <v>0.0818558994905577</v>
       </c>
       <c r="T29">
-        <v>0.8230883347176112</v>
+        <v>0.832699757287707</v>
       </c>
       <c r="U29">
         <v>0.05530000000000001</v>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>4.036050839452616</v>
+        <v>3.891906166615023</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3717,22 +3717,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07123054363320155</v>
+        <v>0.07115487409431412</v>
       </c>
       <c r="C30">
-        <v>7239.208897328308</v>
+        <v>7170.113257658987</v>
       </c>
       <c r="D30">
-        <v>9809.068897328309</v>
+        <v>9838.343257658988</v>
       </c>
       <c r="E30">
-        <v>-252.54</v>
+        <v>-154.1699999999996</v>
       </c>
       <c r="F30">
-        <v>2754.36</v>
+        <v>2852.73</v>
       </c>
       <c r="G30">
         <v>184.5</v>
@@ -3753,28 +3753,28 @@
         <v>592.8</v>
       </c>
       <c r="M30">
-        <v>152.316108</v>
+        <v>157.7559690000001</v>
       </c>
       <c r="N30">
-        <v>440.4838919999999</v>
+        <v>435.0440309999999</v>
       </c>
       <c r="O30">
-        <v>90.739681752</v>
+        <v>89.61907038599999</v>
       </c>
       <c r="P30">
-        <v>349.7442102479999</v>
+        <v>345.4249606139999</v>
       </c>
       <c r="Q30">
-        <v>803.3442102480001</v>
+        <v>799.0249606140001</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.0818558994905577</v>
+        <v>0.08228379731593538</v>
       </c>
       <c r="T30">
-        <v>0.832699757287707</v>
+        <v>0.8425819241555518</v>
       </c>
       <c r="U30">
         <v>0.05530000000000001</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>3.891906166615023</v>
+        <v>3.757702505697263</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3799,22 +3799,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07115487409431412</v>
+        <v>0.0710792045554267</v>
       </c>
       <c r="C31">
-        <v>7170.113257658988</v>
+        <v>7101.192874876606</v>
       </c>
       <c r="D31">
-        <v>9838.343257658988</v>
+        <v>9867.792874876606</v>
       </c>
       <c r="E31">
-        <v>-154.1700000000001</v>
+        <v>-55.80000000000018</v>
       </c>
       <c r="F31">
-        <v>2852.73</v>
+        <v>2951.1</v>
       </c>
       <c r="G31">
         <v>184.5</v>
@@ -3835,28 +3835,28 @@
         <v>592.8</v>
       </c>
       <c r="M31">
-        <v>157.755969</v>
+        <v>163.19583</v>
       </c>
       <c r="N31">
-        <v>435.0440309999999</v>
+        <v>429.60417</v>
       </c>
       <c r="O31">
-        <v>89.61907038599999</v>
+        <v>88.49845902</v>
       </c>
       <c r="P31">
-        <v>345.4249606139999</v>
+        <v>341.10571098</v>
       </c>
       <c r="Q31">
-        <v>799.0249606140001</v>
+        <v>794.70571098</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.08228379731593538</v>
+        <v>0.08272392079346672</v>
       </c>
       <c r="T31">
-        <v>0.8425819241555518</v>
+        <v>0.8527464386481923</v>
       </c>
       <c r="U31">
         <v>0.05530000000000001</v>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>3.757702505697264</v>
+        <v>3.632445755507355</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3881,22 +3881,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.0710792045554267</v>
+        <v>0.07100353501653928</v>
       </c>
       <c r="C32">
-        <v>7101.192874876606</v>
+        <v>7032.449327522576</v>
       </c>
       <c r="D32">
-        <v>9867.792874876606</v>
+        <v>9897.419327522575</v>
       </c>
       <c r="E32">
-        <v>-55.80000000000018</v>
+        <v>42.56999999999971</v>
       </c>
       <c r="F32">
-        <v>2951.1</v>
+        <v>3049.47</v>
       </c>
       <c r="G32">
         <v>184.5</v>
@@ -3917,28 +3917,28 @@
         <v>592.8</v>
       </c>
       <c r="M32">
-        <v>163.19583</v>
+        <v>168.635691</v>
       </c>
       <c r="N32">
-        <v>429.60417</v>
+        <v>424.1643089999999</v>
       </c>
       <c r="O32">
-        <v>88.49845902</v>
+        <v>87.37784765399999</v>
       </c>
       <c r="P32">
-        <v>341.10571098</v>
+        <v>336.786461346</v>
       </c>
       <c r="Q32">
-        <v>794.70571098</v>
+        <v>790.386461346</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.08272392079346672</v>
+        <v>0.08317680147324533</v>
       </c>
       <c r="T32">
-        <v>0.8527464386481923</v>
+        <v>0.8632055767493151</v>
       </c>
       <c r="U32">
         <v>0.05530000000000001</v>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>3.632445755507355</v>
+        <v>3.51527008597486</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3963,22 +3963,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.07100353501653928</v>
+        <v>0.07092786547765186</v>
       </c>
       <c r="C33">
-        <v>7032.449327522576</v>
+        <v>6963.88421315264</v>
       </c>
       <c r="D33">
-        <v>9897.419327522575</v>
+        <v>9927.22421315264</v>
       </c>
       <c r="E33">
-        <v>42.56999999999971</v>
+        <v>140.9400000000001</v>
       </c>
       <c r="F33">
-        <v>3049.47</v>
+        <v>3147.84</v>
       </c>
       <c r="G33">
         <v>184.5</v>
@@ -3999,28 +3999,28 @@
         <v>592.8</v>
       </c>
       <c r="M33">
-        <v>168.635691</v>
+        <v>174.075552</v>
       </c>
       <c r="N33">
-        <v>424.1643089999999</v>
+        <v>418.7244479999999</v>
       </c>
       <c r="O33">
-        <v>87.37784765399999</v>
+        <v>86.25723628799999</v>
       </c>
       <c r="P33">
-        <v>336.786461346</v>
+        <v>332.4672117119999</v>
       </c>
       <c r="Q33">
-        <v>790.386461346</v>
+        <v>786.067211712</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.08317680147324533</v>
+        <v>0.08364300217301744</v>
       </c>
       <c r="T33">
-        <v>0.8632055767493151</v>
+        <v>0.8739723365592944</v>
       </c>
       <c r="U33">
         <v>0.05530000000000001</v>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>3.51527008597486</v>
+        <v>3.405417895788145</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4045,22 +4045,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.07092786547765186</v>
+        <v>0.07085219593876443</v>
       </c>
       <c r="C34">
-        <v>6963.88421315264</v>
+        <v>6895.499148624062</v>
       </c>
       <c r="D34">
-        <v>9927.22421315264</v>
+        <v>9957.209148624062</v>
       </c>
       <c r="E34">
-        <v>140.9400000000001</v>
+        <v>239.3099999999999</v>
       </c>
       <c r="F34">
-        <v>3147.84</v>
+        <v>3246.21</v>
       </c>
       <c r="G34">
         <v>184.5</v>
@@ -4081,28 +4081,28 @@
         <v>592.8</v>
       </c>
       <c r="M34">
-        <v>174.075552</v>
+        <v>179.515413</v>
       </c>
       <c r="N34">
-        <v>418.7244479999999</v>
+        <v>413.2845869999999</v>
       </c>
       <c r="O34">
-        <v>86.25723628799999</v>
+        <v>85.136624922</v>
       </c>
       <c r="P34">
-        <v>332.4672117119999</v>
+        <v>328.1479620779999</v>
       </c>
       <c r="Q34">
-        <v>786.067211712</v>
+        <v>781.747962078</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.08364300217301744</v>
+        <v>0.08412311931158872</v>
       </c>
       <c r="T34">
-        <v>0.8739723365592944</v>
+        <v>0.8850604921844971</v>
       </c>
       <c r="U34">
         <v>0.05530000000000001</v>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>3.405417895788145</v>
+        <v>3.302223414097595</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4127,22 +4127,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.07085219593876443</v>
+        <v>0.070776526399877</v>
       </c>
       <c r="C35">
-        <v>6895.499148624062</v>
+        <v>6827.295770388002</v>
       </c>
       <c r="D35">
-        <v>9957.209148624062</v>
+        <v>9987.375770388002</v>
       </c>
       <c r="E35">
-        <v>239.3099999999999</v>
+        <v>337.6800000000003</v>
       </c>
       <c r="F35">
-        <v>3246.21</v>
+        <v>3344.58</v>
       </c>
       <c r="G35">
         <v>184.5</v>
@@ -4163,28 +4163,28 @@
         <v>592.8</v>
       </c>
       <c r="M35">
-        <v>179.515413</v>
+        <v>184.9552740000001</v>
       </c>
       <c r="N35">
-        <v>413.2845869999999</v>
+        <v>407.8447259999999</v>
       </c>
       <c r="O35">
-        <v>85.136624922</v>
+        <v>84.01601355599999</v>
       </c>
       <c r="P35">
-        <v>328.1479620779999</v>
+        <v>323.828712444</v>
       </c>
       <c r="Q35">
-        <v>781.747962078</v>
+        <v>777.4287124440001</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.08412311931158872</v>
+        <v>0.08461778545435911</v>
       </c>
       <c r="T35">
-        <v>0.8850604921844971</v>
+        <v>0.8964846525256148</v>
       </c>
       <c r="U35">
         <v>0.05530000000000001</v>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.302223414097595</v>
+        <v>3.205099196035901</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4209,22 +4209,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.070776526399877</v>
+        <v>0.07070085686098959</v>
       </c>
       <c r="C36">
-        <v>6827.295770388002</v>
+        <v>6759.275734787198</v>
       </c>
       <c r="D36">
-        <v>9987.375770388002</v>
+        <v>10017.7257347872</v>
       </c>
       <c r="E36">
-        <v>337.6800000000003</v>
+        <v>436.0500000000002</v>
       </c>
       <c r="F36">
-        <v>3344.58</v>
+        <v>3442.95</v>
       </c>
       <c r="G36">
         <v>184.5</v>
@@ -4245,28 +4245,28 @@
         <v>592.8</v>
       </c>
       <c r="M36">
-        <v>184.9552740000001</v>
+        <v>190.395135</v>
       </c>
       <c r="N36">
-        <v>407.8447259999999</v>
+        <v>402.4048649999999</v>
       </c>
       <c r="O36">
-        <v>84.01601355599999</v>
+        <v>82.89540218999998</v>
       </c>
       <c r="P36">
-        <v>323.828712444</v>
+        <v>319.5094628099999</v>
       </c>
       <c r="Q36">
-        <v>777.4287124440001</v>
+        <v>773.1094628100001</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.08461778545435911</v>
+        <v>0.08512767209383015</v>
       </c>
       <c r="T36">
-        <v>0.8964846525256148</v>
+        <v>0.9082603254926133</v>
       </c>
       <c r="U36">
         <v>0.05530000000000001</v>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>3.205099196035901</v>
+        <v>3.113524933292018</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.07070085686098959</v>
+        <v>0.07062518732210217</v>
       </c>
       <c r="C37">
-        <v>6759.275734787198</v>
+        <v>6691.440718359189</v>
       </c>
       <c r="D37">
-        <v>10017.7257347872</v>
+        <v>10048.26071835919</v>
       </c>
       <c r="E37">
-        <v>436.0500000000002</v>
+        <v>534.4200000000005</v>
       </c>
       <c r="F37">
-        <v>3442.95</v>
+        <v>3541.320000000001</v>
       </c>
       <c r="G37">
         <v>184.5</v>
@@ -4327,28 +4327,28 @@
         <v>592.8</v>
       </c>
       <c r="M37">
-        <v>190.395135</v>
+        <v>195.8349960000001</v>
       </c>
       <c r="N37">
-        <v>402.4048649999999</v>
+        <v>396.9650039999999</v>
       </c>
       <c r="O37">
-        <v>82.89540218999998</v>
+        <v>81.77479082399999</v>
       </c>
       <c r="P37">
-        <v>319.5094628099999</v>
+        <v>315.1902131759999</v>
       </c>
       <c r="Q37">
-        <v>773.1094628100001</v>
+        <v>768.7902131760001</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.08512767209383015</v>
+        <v>0.08565349269078465</v>
       </c>
       <c r="T37">
-        <v>0.9082603254926133</v>
+        <v>0.9204039882398304</v>
       </c>
       <c r="U37">
         <v>0.05530000000000001</v>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>3.113524933292018</v>
+        <v>3.027038129589462</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4373,22 +4373,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.07062518732210218</v>
+        <v>0.07128396778321475</v>
       </c>
       <c r="C38">
-        <v>6691.440718359185</v>
+        <v>6333.31533467125</v>
       </c>
       <c r="D38">
-        <v>10048.26071835918</v>
+        <v>9788.50533467125</v>
       </c>
       <c r="E38">
-        <v>534.4199999999996</v>
+        <v>632.79</v>
       </c>
       <c r="F38">
-        <v>3541.32</v>
+        <v>3639.69</v>
       </c>
       <c r="G38">
         <v>184.5</v>
@@ -4409,45 +4409,45 @@
         <v>592.8</v>
       </c>
       <c r="M38">
-        <v>195.834996</v>
+        <v>210.374082</v>
       </c>
       <c r="N38">
-        <v>396.9650039999999</v>
+        <v>382.4259179999999</v>
       </c>
       <c r="O38">
-        <v>81.77479082399999</v>
+        <v>78.77973910799999</v>
       </c>
       <c r="P38">
-        <v>315.1902131759999</v>
+        <v>303.6461788919999</v>
       </c>
       <c r="Q38">
-        <v>768.7902131760001</v>
+        <v>757.246178892</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.08565349269078465</v>
+        <v>0.08619600600510277</v>
       </c>
       <c r="T38">
-        <v>0.9204039882398304</v>
+        <v>0.9329331640901336</v>
       </c>
       <c r="U38">
-        <v>0.05530000000000001</v>
+        <v>0.0578</v>
       </c>
       <c r="V38">
         <v>0.206</v>
       </c>
       <c r="W38">
-        <v>0.04390820000000001</v>
+        <v>0.04589320000000001</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y38">
-        <v>3.027038129589462</v>
+        <v>2.817837607961612</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4455,22 +4455,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.07128396778321475</v>
+        <v>0.07122814824432734</v>
       </c>
       <c r="C39">
-        <v>6333.31533467125</v>
+        <v>6256.432933725979</v>
       </c>
       <c r="D39">
-        <v>9788.50533467125</v>
+        <v>9809.992933725978</v>
       </c>
       <c r="E39">
-        <v>632.79</v>
+        <v>731.1599999999999</v>
       </c>
       <c r="F39">
-        <v>3639.69</v>
+        <v>3738.06</v>
       </c>
       <c r="G39">
         <v>184.5</v>
@@ -4491,28 +4491,28 @@
         <v>592.8</v>
       </c>
       <c r="M39">
-        <v>210.374082</v>
+        <v>216.059868</v>
       </c>
       <c r="N39">
-        <v>382.4259179999999</v>
+        <v>376.7401319999999</v>
       </c>
       <c r="O39">
-        <v>78.77973910799999</v>
+        <v>77.60846719199999</v>
       </c>
       <c r="P39">
-        <v>303.6461788919999</v>
+        <v>299.1316648079999</v>
       </c>
       <c r="Q39">
-        <v>757.246178892</v>
+        <v>752.731664808</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.08619600600510277</v>
+        <v>0.08675601974891506</v>
       </c>
       <c r="T39">
-        <v>0.9329331640901336</v>
+        <v>0.9458665069033501</v>
       </c>
       <c r="U39">
         <v>0.0578</v>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>2.817837607961612</v>
+        <v>2.743683986699463</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4537,22 +4537,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.07122814824432734</v>
+        <v>0.07117232870543992</v>
       </c>
       <c r="C40">
-        <v>6256.432933725979</v>
+        <v>6179.645078920716</v>
       </c>
       <c r="D40">
-        <v>9809.992933725978</v>
+        <v>9831.575078920716</v>
       </c>
       <c r="E40">
-        <v>731.1599999999999</v>
+        <v>829.5300000000002</v>
       </c>
       <c r="F40">
-        <v>3738.06</v>
+        <v>3836.43</v>
       </c>
       <c r="G40">
         <v>184.5</v>
@@ -4573,28 +4573,28 @@
         <v>592.8</v>
       </c>
       <c r="M40">
-        <v>216.059868</v>
+        <v>221.745654</v>
       </c>
       <c r="N40">
-        <v>376.7401319999999</v>
+        <v>371.0543459999999</v>
       </c>
       <c r="O40">
-        <v>77.60846719199999</v>
+        <v>76.43719527599998</v>
       </c>
       <c r="P40">
-        <v>299.1316648079999</v>
+        <v>294.6171507239999</v>
       </c>
       <c r="Q40">
-        <v>752.731664808</v>
+        <v>748.217150724</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.08675601974891506</v>
+        <v>0.08733439459908182</v>
       </c>
       <c r="T40">
-        <v>0.9458665069033501</v>
+        <v>0.9592238937432294</v>
       </c>
       <c r="U40">
         <v>0.0578</v>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>2.743683986699463</v>
+        <v>2.673333115245631</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4619,22 +4619,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.07117232870543992</v>
+        <v>0.07111650916655249</v>
       </c>
       <c r="C41">
-        <v>6179.645078920716</v>
+        <v>6102.952395640493</v>
       </c>
       <c r="D41">
-        <v>9831.575078920716</v>
+        <v>9853.252395640493</v>
       </c>
       <c r="E41">
-        <v>829.5300000000002</v>
+        <v>927.9000000000001</v>
       </c>
       <c r="F41">
-        <v>3836.43</v>
+        <v>3934.8</v>
       </c>
       <c r="G41">
         <v>184.5</v>
@@ -4655,28 +4655,28 @@
         <v>592.8</v>
       </c>
       <c r="M41">
-        <v>221.745654</v>
+        <v>227.43144</v>
       </c>
       <c r="N41">
-        <v>371.0543459999999</v>
+        <v>365.3685599999999</v>
       </c>
       <c r="O41">
-        <v>76.43719527599998</v>
+        <v>75.26592335999999</v>
       </c>
       <c r="P41">
-        <v>294.6171507239999</v>
+        <v>290.1026366399999</v>
       </c>
       <c r="Q41">
-        <v>748.217150724</v>
+        <v>743.70263664</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.08733439459908182</v>
+        <v>0.08793204861092081</v>
       </c>
       <c r="T41">
-        <v>0.9592238937432294</v>
+        <v>0.9730265268111044</v>
       </c>
       <c r="U41">
         <v>0.0578</v>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>2.673333115245631</v>
+        <v>2.60649978736449</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4701,22 +4701,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.07111650916655249</v>
+        <v>0.07106068962766507</v>
       </c>
       <c r="C42">
-        <v>6102.952395640493</v>
+        <v>6026.355514798081</v>
       </c>
       <c r="D42">
-        <v>9853.252395640493</v>
+        <v>9875.025514798081</v>
       </c>
       <c r="E42">
-        <v>927.9000000000001</v>
+        <v>1026.27</v>
       </c>
       <c r="F42">
-        <v>3934.8</v>
+        <v>4033.170000000001</v>
       </c>
       <c r="G42">
         <v>184.5</v>
@@ -4737,28 +4737,28 @@
         <v>592.8</v>
       </c>
       <c r="M42">
-        <v>227.43144</v>
+        <v>233.117226</v>
       </c>
       <c r="N42">
-        <v>365.3685599999999</v>
+        <v>359.6827739999999</v>
       </c>
       <c r="O42">
-        <v>75.26592335999999</v>
+        <v>74.09465144399998</v>
       </c>
       <c r="P42">
-        <v>290.1026366399999</v>
+        <v>285.5881225559999</v>
       </c>
       <c r="Q42">
-        <v>743.70263664</v>
+        <v>739.1881225560001</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.08793204861092081</v>
+        <v>0.08854996208078825</v>
       </c>
       <c r="T42">
-        <v>0.9730265268111044</v>
+        <v>0.9872970457456872</v>
       </c>
       <c r="U42">
         <v>0.0578</v>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>2.60649978736449</v>
+        <v>2.542926621819015</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4783,22 +4783,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.07106068962766507</v>
+        <v>0.07217205008877764</v>
       </c>
       <c r="C43">
-        <v>6026.355514798081</v>
+        <v>5511.836111445683</v>
       </c>
       <c r="D43">
-        <v>9875.025514798081</v>
+        <v>9458.876111445683</v>
       </c>
       <c r="E43">
-        <v>1026.27</v>
+        <v>1124.64</v>
       </c>
       <c r="F43">
-        <v>4033.170000000001</v>
+        <v>4131.54</v>
       </c>
       <c r="G43">
         <v>184.5</v>
@@ -4819,45 +4819,45 @@
         <v>592.8</v>
       </c>
       <c r="M43">
-        <v>233.117226</v>
+        <v>253.263402</v>
       </c>
       <c r="N43">
-        <v>359.6827739999999</v>
+        <v>339.5365979999999</v>
       </c>
       <c r="O43">
-        <v>74.09465144399998</v>
+        <v>69.94453918799999</v>
       </c>
       <c r="P43">
-        <v>285.5881225559999</v>
+        <v>269.5920588119999</v>
       </c>
       <c r="Q43">
-        <v>739.1881225560001</v>
+        <v>723.192058812</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.08854996208078825</v>
+        <v>0.08918918291168559</v>
       </c>
       <c r="T43">
-        <v>0.9872970457456872</v>
+        <v>1.002059651540083</v>
       </c>
       <c r="U43">
-        <v>0.0578</v>
+        <v>0.06130000000000001</v>
       </c>
       <c r="V43">
         <v>0.206</v>
       </c>
       <c r="W43">
-        <v>0.04589320000000001</v>
+        <v>0.04867220000000001</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y43">
-        <v>2.542926621819015</v>
+        <v>2.340646123043075</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4865,22 +4865,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.07217205008877765</v>
+        <v>0.07214402054989022</v>
       </c>
       <c r="C44">
-        <v>5511.836111445677</v>
+        <v>5423.530176469279</v>
       </c>
       <c r="D44">
-        <v>9458.876111445677</v>
+        <v>9468.940176469279</v>
       </c>
       <c r="E44">
-        <v>1124.64</v>
+        <v>1223.01</v>
       </c>
       <c r="F44">
-        <v>4131.54</v>
+        <v>4229.91</v>
       </c>
       <c r="G44">
         <v>184.5</v>
@@ -4901,28 +4901,28 @@
         <v>592.8</v>
       </c>
       <c r="M44">
-        <v>253.263402</v>
+        <v>259.293483</v>
       </c>
       <c r="N44">
-        <v>339.5365979999999</v>
+        <v>333.5065169999999</v>
       </c>
       <c r="O44">
-        <v>69.94453918799999</v>
+        <v>68.70234250199999</v>
       </c>
       <c r="P44">
-        <v>269.5920588119999</v>
+        <v>264.804174498</v>
       </c>
       <c r="Q44">
-        <v>723.192058812</v>
+        <v>718.4041744980001</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.08918918291168559</v>
+        <v>0.08985083254366705</v>
       </c>
       <c r="T44">
-        <v>1.002059651540083</v>
+        <v>1.017340243502703</v>
       </c>
       <c r="U44">
         <v>0.06130000000000001</v>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>2.340646123043075</v>
+        <v>2.286212492274632</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4947,22 +4947,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.07214402054989022</v>
+        <v>0.07309419901100281</v>
       </c>
       <c r="C45">
-        <v>5423.530176469279</v>
+        <v>4995.522988669124</v>
       </c>
       <c r="D45">
-        <v>9468.940176469279</v>
+        <v>9139.302988669124</v>
       </c>
       <c r="E45">
-        <v>1223.01</v>
+        <v>1321.38</v>
       </c>
       <c r="F45">
-        <v>4229.91</v>
+        <v>4328.28</v>
       </c>
       <c r="G45">
         <v>184.5</v>
@@ -4983,45 +4983,45 @@
         <v>592.8</v>
       </c>
       <c r="M45">
-        <v>259.293483</v>
+        <v>277.442748</v>
       </c>
       <c r="N45">
-        <v>333.5065169999999</v>
+        <v>315.357252</v>
       </c>
       <c r="O45">
-        <v>68.70234250199999</v>
+        <v>64.96359391199999</v>
       </c>
       <c r="P45">
-        <v>264.804174498</v>
+        <v>250.393658088</v>
       </c>
       <c r="Q45">
-        <v>718.4041744980001</v>
+        <v>703.9936580880001</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.08985083254366705</v>
+        <v>0.09053611251964785</v>
       </c>
       <c r="T45">
-        <v>1.017340243502703</v>
+        <v>1.03316657089256</v>
       </c>
       <c r="U45">
-        <v>0.06130000000000001</v>
+        <v>0.0641</v>
       </c>
       <c r="V45">
         <v>0.206</v>
       </c>
       <c r="W45">
-        <v>0.04867220000000001</v>
+        <v>0.05089540000000001</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y45">
-        <v>2.286212492274632</v>
+        <v>2.136657037436783</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5029,22 +5029,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.07309419901100281</v>
+        <v>0.07308840147211539</v>
       </c>
       <c r="C46">
-        <v>4995.522988669124</v>
+        <v>4899.094673107286</v>
       </c>
       <c r="D46">
-        <v>9139.302988669124</v>
+        <v>9141.244673107287</v>
       </c>
       <c r="E46">
-        <v>1321.38</v>
+        <v>1419.75</v>
       </c>
       <c r="F46">
-        <v>4328.28</v>
+        <v>4426.650000000001</v>
       </c>
       <c r="G46">
         <v>184.5</v>
@@ -5065,28 +5065,28 @@
         <v>592.8</v>
       </c>
       <c r="M46">
-        <v>277.442748</v>
+        <v>283.7482650000001</v>
       </c>
       <c r="N46">
-        <v>315.357252</v>
+        <v>309.0517349999999</v>
       </c>
       <c r="O46">
-        <v>64.96359391199999</v>
+        <v>63.66465740999998</v>
       </c>
       <c r="P46">
-        <v>250.393658088</v>
+        <v>245.3870775899999</v>
       </c>
       <c r="Q46">
-        <v>703.9936580880001</v>
+        <v>698.98707759</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.09053611251964785</v>
+        <v>0.0912463117674825</v>
       </c>
       <c r="T46">
-        <v>1.03316657089256</v>
+        <v>1.049568401096594</v>
       </c>
       <c r="U46">
         <v>0.0641</v>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.136657037436783</v>
+        <v>2.089175769938187</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5111,22 +5111,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.07308840147211539</v>
+        <v>0.07308260393322796</v>
       </c>
       <c r="C47">
-        <v>4899.094673107286</v>
+        <v>4802.667182759278</v>
       </c>
       <c r="D47">
-        <v>9141.244673107287</v>
+        <v>9143.187182759279</v>
       </c>
       <c r="E47">
-        <v>1419.75</v>
+        <v>1518.12</v>
       </c>
       <c r="F47">
-        <v>4426.650000000001</v>
+        <v>4525.02</v>
       </c>
       <c r="G47">
         <v>184.5</v>
@@ -5147,28 +5147,28 @@
         <v>592.8</v>
       </c>
       <c r="M47">
-        <v>283.7482650000001</v>
+        <v>290.0537820000001</v>
       </c>
       <c r="N47">
-        <v>309.0517349999999</v>
+        <v>302.7462179999999</v>
       </c>
       <c r="O47">
-        <v>63.66465740999998</v>
+        <v>62.36572090799998</v>
       </c>
       <c r="P47">
-        <v>245.3870775899999</v>
+        <v>240.3804970919999</v>
       </c>
       <c r="Q47">
-        <v>698.98707759</v>
+        <v>693.9804970920001</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.0912463117674825</v>
+        <v>0.09198281469116287</v>
       </c>
       <c r="T47">
-        <v>1.049568401096594</v>
+        <v>1.066577706493369</v>
       </c>
       <c r="U47">
         <v>0.0641</v>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.089175769938187</v>
+        <v>2.043758905374314</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5193,22 +5193,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.07308260393322796</v>
+        <v>0.07307680639434054</v>
       </c>
       <c r="C48">
-        <v>4802.667182759278</v>
+        <v>4706.240518151285</v>
       </c>
       <c r="D48">
-        <v>9143.187182759279</v>
+        <v>9145.130518151285</v>
       </c>
       <c r="E48">
-        <v>1518.12</v>
+        <v>1616.49</v>
       </c>
       <c r="F48">
-        <v>4525.02</v>
+        <v>4623.39</v>
       </c>
       <c r="G48">
         <v>184.5</v>
@@ -5229,28 +5229,28 @@
         <v>592.8</v>
       </c>
       <c r="M48">
-        <v>290.0537820000001</v>
+        <v>296.359299</v>
       </c>
       <c r="N48">
-        <v>302.7462179999999</v>
+        <v>296.4407009999999</v>
       </c>
       <c r="O48">
-        <v>62.36572090799998</v>
+        <v>61.06678440599999</v>
       </c>
       <c r="P48">
-        <v>240.3804970919999</v>
+        <v>235.373916594</v>
       </c>
       <c r="Q48">
-        <v>693.9804970920001</v>
+        <v>688.9739165940001</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.09198281469116287</v>
+        <v>0.092747110178001</v>
       </c>
       <c r="T48">
-        <v>1.066577706493369</v>
+        <v>1.084228872471155</v>
       </c>
       <c r="U48">
         <v>0.0641</v>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.043758905374314</v>
+        <v>2.000274673345073</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5275,22 +5275,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.07307680639434054</v>
+        <v>0.07753011285545312</v>
       </c>
       <c r="C49">
-        <v>4706.240518151285</v>
+        <v>3324.35573805173</v>
       </c>
       <c r="D49">
-        <v>9145.130518151285</v>
+        <v>7861.615738051731</v>
       </c>
       <c r="E49">
-        <v>1616.49</v>
+        <v>1714.86</v>
       </c>
       <c r="F49">
-        <v>4623.39</v>
+        <v>4721.76</v>
       </c>
       <c r="G49">
         <v>184.5</v>
@@ -5311,45 +5311,45 @@
         <v>592.8</v>
       </c>
       <c r="M49">
-        <v>296.359299</v>
+        <v>357.909408</v>
       </c>
       <c r="N49">
-        <v>296.4407009999999</v>
+        <v>234.8905919999999</v>
       </c>
       <c r="O49">
-        <v>61.06678440599999</v>
+        <v>48.38746195199999</v>
       </c>
       <c r="P49">
-        <v>235.373916594</v>
+        <v>186.5031300479999</v>
       </c>
       <c r="Q49">
-        <v>688.9739165940001</v>
+        <v>640.103130048</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.092747110178001</v>
+        <v>0.09354080164510215</v>
       </c>
       <c r="T49">
-        <v>1.084228872471155</v>
+        <v>1.102558929448087</v>
       </c>
       <c r="U49">
-        <v>0.0641</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V49">
         <v>0.206</v>
       </c>
       <c r="W49">
-        <v>0.05089540000000001</v>
+        <v>0.06018520000000001</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y49">
-        <v>2.000274673345073</v>
+        <v>1.656285045181042</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.07753011285545311</v>
+        <v>0.07761721331656571</v>
       </c>
       <c r="C50">
-        <v>3324.355738051734</v>
+        <v>3204.464357500225</v>
       </c>
       <c r="D50">
-        <v>7861.615738051734</v>
+        <v>7840.094357500225</v>
       </c>
       <c r="E50">
-        <v>1714.86</v>
+        <v>1813.23</v>
       </c>
       <c r="F50">
-        <v>4721.76</v>
+        <v>4820.13</v>
       </c>
       <c r="G50">
         <v>184.5</v>
@@ -5393,28 +5393,28 @@
         <v>592.8</v>
       </c>
       <c r="M50">
-        <v>357.909408</v>
+        <v>365.365854</v>
       </c>
       <c r="N50">
-        <v>234.8905919999999</v>
+        <v>227.4341459999999</v>
       </c>
       <c r="O50">
-        <v>48.38746195199999</v>
+        <v>46.85143407599999</v>
       </c>
       <c r="P50">
-        <v>186.5031300479999</v>
+        <v>180.582711924</v>
       </c>
       <c r="Q50">
-        <v>640.103130048</v>
+        <v>634.1827119240002</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.09354080164510213</v>
+        <v>0.09436561826777587</v>
       </c>
       <c r="T50">
-        <v>1.102558929448086</v>
+        <v>1.121607812188819</v>
       </c>
       <c r="U50">
         <v>0.07580000000000001</v>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>1.656285045181042</v>
+        <v>1.622483309565102</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5439,22 +5439,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.07761721331656571</v>
+        <v>0.07770431377767828</v>
       </c>
       <c r="C51">
-        <v>3204.464357500225</v>
+        <v>3084.690485959125</v>
       </c>
       <c r="D51">
-        <v>7840.094357500225</v>
+        <v>7818.690485959125</v>
       </c>
       <c r="E51">
-        <v>1813.23</v>
+        <v>1911.6</v>
       </c>
       <c r="F51">
-        <v>4820.13</v>
+        <v>4918.5</v>
       </c>
       <c r="G51">
         <v>184.5</v>
@@ -5475,28 +5475,28 @@
         <v>592.8</v>
       </c>
       <c r="M51">
-        <v>365.365854</v>
+        <v>372.8223</v>
       </c>
       <c r="N51">
-        <v>227.4341459999999</v>
+        <v>219.9776999999999</v>
       </c>
       <c r="O51">
-        <v>46.85143407599999</v>
+        <v>45.31540619999998</v>
       </c>
       <c r="P51">
-        <v>180.582711924</v>
+        <v>174.6622937999999</v>
       </c>
       <c r="Q51">
-        <v>634.1827119240002</v>
+        <v>628.2622938000001</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.09436561826777587</v>
+        <v>0.09522342755535654</v>
       </c>
       <c r="T51">
-        <v>1.121607812188819</v>
+        <v>1.141418650239181</v>
       </c>
       <c r="U51">
         <v>0.07580000000000001</v>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>1.622483309565102</v>
+        <v>1.5900336433738</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5521,22 +5521,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.07770431377767828</v>
+        <v>0.07779141423879085</v>
       </c>
       <c r="C52">
-        <v>3084.690485959125</v>
+        <v>2965.033163631319</v>
       </c>
       <c r="D52">
-        <v>7818.690485959125</v>
+        <v>7797.403163631319</v>
       </c>
       <c r="E52">
-        <v>1911.6</v>
+        <v>2009.97</v>
       </c>
       <c r="F52">
-        <v>4918.5</v>
+        <v>5016.87</v>
       </c>
       <c r="G52">
         <v>184.5</v>
@@ -5557,28 +5557,28 @@
         <v>592.8</v>
       </c>
       <c r="M52">
-        <v>372.8223</v>
+        <v>380.278746</v>
       </c>
       <c r="N52">
-        <v>219.9776999999999</v>
+        <v>212.5212539999999</v>
       </c>
       <c r="O52">
-        <v>45.31540619999998</v>
+        <v>43.77937832399999</v>
       </c>
       <c r="P52">
-        <v>174.6622937999999</v>
+        <v>168.7418756759999</v>
       </c>
       <c r="Q52">
-        <v>628.2622938000001</v>
+        <v>622.3418756760001</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.09522342755535654</v>
+        <v>0.0961162494669201</v>
       </c>
       <c r="T52">
-        <v>1.141418650239181</v>
+        <v>1.162038093924252</v>
       </c>
       <c r="U52">
         <v>0.07580000000000001</v>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>1.5900336433738</v>
+        <v>1.558856513111569</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5603,22 +5603,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.07779141423879085</v>
+        <v>0.07787851469990342</v>
       </c>
       <c r="C53">
-        <v>2965.033163631319</v>
+        <v>2845.491441143964</v>
       </c>
       <c r="D53">
-        <v>7797.403163631319</v>
+        <v>7776.231441143964</v>
       </c>
       <c r="E53">
-        <v>2009.97</v>
+        <v>2108.34</v>
       </c>
       <c r="F53">
-        <v>5016.87</v>
+        <v>5115.24</v>
       </c>
       <c r="G53">
         <v>184.5</v>
@@ -5639,28 +5639,28 @@
         <v>592.8</v>
       </c>
       <c r="M53">
-        <v>380.278746</v>
+        <v>387.735192</v>
       </c>
       <c r="N53">
-        <v>212.5212539999999</v>
+        <v>205.0648079999999</v>
       </c>
       <c r="O53">
-        <v>43.77937832399999</v>
+        <v>42.24335044799999</v>
       </c>
       <c r="P53">
-        <v>168.7418756759999</v>
+        <v>162.8214575519999</v>
       </c>
       <c r="Q53">
-        <v>622.3418756760001</v>
+        <v>616.421457552</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.0961162494669201</v>
+        <v>0.09704627229146548</v>
       </c>
       <c r="T53">
-        <v>1.162038093924252</v>
+        <v>1.183516681096201</v>
       </c>
       <c r="U53">
         <v>0.07580000000000001</v>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>1.558856513111569</v>
+        <v>1.528878503244039</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5685,22 +5685,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.07787851469990342</v>
+        <v>0.07796561516101601</v>
       </c>
       <c r="C54">
-        <v>2845.491441143964</v>
+        <v>2726.064379407345</v>
       </c>
       <c r="D54">
-        <v>7776.231441143964</v>
+        <v>7755.174379407345</v>
       </c>
       <c r="E54">
-        <v>2108.34</v>
+        <v>2206.71</v>
       </c>
       <c r="F54">
-        <v>5115.24</v>
+        <v>5213.610000000001</v>
       </c>
       <c r="G54">
         <v>184.5</v>
@@ -5721,28 +5721,28 @@
         <v>592.8</v>
       </c>
       <c r="M54">
-        <v>387.735192</v>
+        <v>395.1916380000001</v>
       </c>
       <c r="N54">
-        <v>205.0648079999999</v>
+        <v>197.6083619999999</v>
       </c>
       <c r="O54">
-        <v>42.24335044799999</v>
+        <v>40.70732257199998</v>
       </c>
       <c r="P54">
-        <v>162.8214575519999</v>
+        <v>156.9010394279999</v>
       </c>
       <c r="Q54">
-        <v>616.421457552</v>
+        <v>610.501039428</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.09704627229146548</v>
+        <v>0.09801587055535321</v>
       </c>
       <c r="T54">
-        <v>1.183516681096201</v>
+        <v>1.205909250700998</v>
       </c>
       <c r="U54">
         <v>0.07580000000000001</v>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>1.528878503244039</v>
+        <v>1.500031739031887</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5767,22 +5767,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.07796561516101601</v>
+        <v>0.09736363908018036</v>
       </c>
       <c r="C55">
-        <v>2726.064379407345</v>
+        <v>-289.7695698517628</v>
       </c>
       <c r="D55">
-        <v>7755.174379407345</v>
+        <v>4837.710430148238</v>
       </c>
       <c r="E55">
-        <v>2206.71</v>
+        <v>2305.08</v>
       </c>
       <c r="F55">
-        <v>5213.610000000001</v>
+        <v>5311.98</v>
       </c>
       <c r="G55">
         <v>184.5</v>
@@ -5803,45 +5803,45 @@
         <v>592.8</v>
       </c>
       <c r="M55">
-        <v>395.1916380000001</v>
+        <v>630.0008280000001</v>
       </c>
       <c r="N55">
-        <v>197.6083619999999</v>
+        <v>-37.20082800000012</v>
       </c>
       <c r="O55">
-        <v>40.70732257199998</v>
+        <v>-7.663370568000024</v>
       </c>
       <c r="P55">
-        <v>156.9010394279999</v>
+        <v>-29.53745743200009</v>
       </c>
       <c r="Q55">
-        <v>610.501039428</v>
+        <v>424.062542568</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.09801587055535321</v>
+        <v>0.09942101684229773</v>
       </c>
       <c r="T55">
-        <v>1.205909250700998</v>
+        <v>1.238360666103874</v>
       </c>
       <c r="U55">
-        <v>0.07580000000000001</v>
+        <v>0.1186</v>
       </c>
       <c r="V55">
-        <v>0.206</v>
+        <v>0.1938359357203892</v>
       </c>
       <c r="W55">
-        <v>0.06018520000000001</v>
+        <v>0.09561105802356185</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y55">
-        <v>1.500031739031887</v>
+        <v>0.9409511442737341</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5849,22 +5849,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.09736363908018036</v>
+        <v>0.09809163908018036</v>
       </c>
       <c r="C56">
-        <v>-289.7695698517628</v>
+        <v>-455.489785968487</v>
       </c>
       <c r="D56">
-        <v>4837.710430148238</v>
+        <v>4770.360214031513</v>
       </c>
       <c r="E56">
-        <v>2305.08</v>
+        <v>2403.45</v>
       </c>
       <c r="F56">
-        <v>5311.98</v>
+        <v>5410.35</v>
       </c>
       <c r="G56">
         <v>184.5</v>
@@ -5885,37 +5885,37 @@
         <v>592.8</v>
       </c>
       <c r="M56">
-        <v>630.0008280000001</v>
+        <v>641.6675100000001</v>
       </c>
       <c r="N56">
-        <v>-37.20082800000012</v>
+        <v>-48.86751000000015</v>
       </c>
       <c r="O56">
-        <v>-7.663370568000024</v>
+        <v>-10.06670706000003</v>
       </c>
       <c r="P56">
-        <v>-29.53745743200009</v>
+        <v>-38.80080294000012</v>
       </c>
       <c r="Q56">
-        <v>424.062542568</v>
+        <v>414.79919706</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.09942101684229773</v>
+        <v>0.1006125949943488</v>
       </c>
       <c r="T56">
-        <v>1.238360666103874</v>
+        <v>1.265879792017294</v>
       </c>
       <c r="U56">
         <v>0.1186</v>
       </c>
       <c r="V56">
-        <v>0.1938359357203892</v>
+        <v>0.1903116459800185</v>
       </c>
       <c r="W56">
-        <v>0.09561105802356185</v>
+        <v>0.09602903878676981</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.9409511442737341</v>
+        <v>0.9238429416505751</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5931,22 +5931,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.09809163908018036</v>
+        <v>0.09881963908018035</v>
       </c>
       <c r="C57">
-        <v>-455.489785968487</v>
+        <v>-619.3604626246033</v>
       </c>
       <c r="D57">
-        <v>4770.360214031513</v>
+        <v>4704.859537375397</v>
       </c>
       <c r="E57">
-        <v>2403.45</v>
+        <v>2501.82</v>
       </c>
       <c r="F57">
-        <v>5410.35</v>
+        <v>5508.72</v>
       </c>
       <c r="G57">
         <v>184.5</v>
@@ -5967,37 +5967,37 @@
         <v>592.8</v>
       </c>
       <c r="M57">
-        <v>641.6675100000001</v>
+        <v>653.3341920000001</v>
       </c>
       <c r="N57">
-        <v>-48.86751000000015</v>
+        <v>-60.53419200000019</v>
       </c>
       <c r="O57">
-        <v>-10.06670706000003</v>
+        <v>-12.47004355200004</v>
       </c>
       <c r="P57">
-        <v>-38.80080294000012</v>
+        <v>-48.06414844800015</v>
       </c>
       <c r="Q57">
-        <v>414.79919706</v>
+        <v>405.535851552</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1006125949943488</v>
+        <v>0.1018583357896749</v>
       </c>
       <c r="T57">
-        <v>1.265879792017294</v>
+        <v>1.294649787290414</v>
       </c>
       <c r="U57">
         <v>0.1186</v>
       </c>
       <c r="V57">
-        <v>0.1903116459800185</v>
+        <v>0.1869132237303753</v>
       </c>
       <c r="W57">
-        <v>0.09602903878676981</v>
+        <v>0.09643209166557749</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.9238429416505751</v>
+        <v>0.9073457462639577</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6013,22 +6013,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.09881963908018035</v>
+        <v>0.09954763908018036</v>
       </c>
       <c r="C58">
-        <v>-619.3604626246033</v>
+        <v>-781.4567546408871</v>
       </c>
       <c r="D58">
-        <v>4704.859537375397</v>
+        <v>4641.133245359114</v>
       </c>
       <c r="E58">
-        <v>2501.82</v>
+        <v>2600.190000000001</v>
       </c>
       <c r="F58">
-        <v>5508.72</v>
+        <v>5607.090000000001</v>
       </c>
       <c r="G58">
         <v>184.5</v>
@@ -6049,37 +6049,37 @@
         <v>592.8</v>
       </c>
       <c r="M58">
-        <v>653.3341920000001</v>
+        <v>665.0008740000002</v>
       </c>
       <c r="N58">
-        <v>-60.53419200000019</v>
+        <v>-72.20087400000023</v>
       </c>
       <c r="O58">
-        <v>-12.47004355200004</v>
+        <v>-14.87338004400005</v>
       </c>
       <c r="P58">
-        <v>-48.06414844800015</v>
+        <v>-57.32749395600018</v>
       </c>
       <c r="Q58">
-        <v>405.535851552</v>
+        <v>396.272506044</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1018583357896749</v>
+        <v>0.1031620180173418</v>
       </c>
       <c r="T58">
-        <v>1.294649787290414</v>
+        <v>1.324757921878563</v>
       </c>
       <c r="U58">
         <v>0.1186</v>
       </c>
       <c r="V58">
-        <v>0.1869132237303753</v>
+        <v>0.1836340443666845</v>
       </c>
       <c r="W58">
-        <v>0.09643209166557749</v>
+        <v>0.09682100233811122</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.9073457462639577</v>
+        <v>0.8914273998382742</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6095,22 +6095,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.09954763908018036</v>
+        <v>0.1002756390801804</v>
       </c>
       <c r="C59">
-        <v>-781.4567546408871</v>
+        <v>-941.849799430659</v>
       </c>
       <c r="D59">
-        <v>4641.133245359114</v>
+        <v>4579.110200569342</v>
       </c>
       <c r="E59">
-        <v>2600.190000000001</v>
+        <v>2698.560000000001</v>
       </c>
       <c r="F59">
-        <v>5607.090000000001</v>
+        <v>5705.460000000001</v>
       </c>
       <c r="G59">
         <v>184.5</v>
@@ -6131,37 +6131,37 @@
         <v>592.8</v>
       </c>
       <c r="M59">
-        <v>665.0008740000002</v>
+        <v>676.6675560000002</v>
       </c>
       <c r="N59">
-        <v>-72.20087400000023</v>
+        <v>-83.86755600000026</v>
       </c>
       <c r="O59">
-        <v>-14.87338004400005</v>
+        <v>-17.27671653600006</v>
       </c>
       <c r="P59">
-        <v>-57.32749395600018</v>
+        <v>-66.59083946400021</v>
       </c>
       <c r="Q59">
-        <v>396.272506044</v>
+        <v>387.0091605359999</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1031620180173418</v>
+        <v>0.104527780351088</v>
       </c>
       <c r="T59">
-        <v>1.324757921878563</v>
+        <v>1.356299777161386</v>
       </c>
       <c r="U59">
         <v>0.1186</v>
       </c>
       <c r="V59">
-        <v>0.1836340443666845</v>
+        <v>0.1804679401534658</v>
       </c>
       <c r="W59">
-        <v>0.09682100233811122</v>
+        <v>0.09719650229779897</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.8914273998382742</v>
+        <v>0.876057961910028</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6177,22 +6177,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1002756390801804</v>
+        <v>0.1010036390801803</v>
       </c>
       <c r="C60">
-        <v>-941.8497994306581</v>
+        <v>-1100.606981898331</v>
       </c>
       <c r="D60">
-        <v>4579.110200569342</v>
+        <v>4518.723018101669</v>
       </c>
       <c r="E60">
-        <v>2698.56</v>
+        <v>2796.93</v>
       </c>
       <c r="F60">
-        <v>5705.46</v>
+        <v>5803.83</v>
       </c>
       <c r="G60">
         <v>184.5</v>
@@ -6213,37 +6213,37 @@
         <v>592.8</v>
       </c>
       <c r="M60">
-        <v>676.6675560000001</v>
+        <v>688.334238</v>
       </c>
       <c r="N60">
-        <v>-83.86755600000015</v>
+        <v>-95.53423800000007</v>
       </c>
       <c r="O60">
-        <v>-17.27671653600003</v>
+        <v>-19.68005302800002</v>
       </c>
       <c r="P60">
-        <v>-66.59083946400011</v>
+        <v>-75.85418497200006</v>
       </c>
       <c r="Q60">
-        <v>387.009160536</v>
+        <v>377.7458150280001</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.104527780351088</v>
+        <v>0.1059601652376999</v>
       </c>
       <c r="T60">
-        <v>1.356299777161386</v>
+        <v>1.389380259531175</v>
       </c>
       <c r="U60">
         <v>0.1186</v>
       </c>
       <c r="V60">
-        <v>0.1804679401534658</v>
+        <v>0.1774091615067969</v>
       </c>
       <c r="W60">
-        <v>0.09719650229779897</v>
+        <v>0.09755927344529389</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.8760579619100282</v>
+        <v>0.861209521877655</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6259,22 +6259,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1010036390801803</v>
+        <v>0.1017316390801803</v>
       </c>
       <c r="C61">
-        <v>-1100.606981898331</v>
+        <v>-1257.792178650605</v>
       </c>
       <c r="D61">
-        <v>4518.723018101669</v>
+        <v>4459.907821349395</v>
       </c>
       <c r="E61">
-        <v>2796.93</v>
+        <v>2895.3</v>
       </c>
       <c r="F61">
-        <v>5803.83</v>
+        <v>5902.2</v>
       </c>
       <c r="G61">
         <v>184.5</v>
@@ -6295,37 +6295,37 @@
         <v>592.8</v>
       </c>
       <c r="M61">
-        <v>688.334238</v>
+        <v>700.0009200000001</v>
       </c>
       <c r="N61">
-        <v>-95.53423800000007</v>
+        <v>-107.2009200000001</v>
       </c>
       <c r="O61">
-        <v>-19.68005302800002</v>
+        <v>-22.08338952000003</v>
       </c>
       <c r="P61">
-        <v>-75.85418497200006</v>
+        <v>-85.11753048000008</v>
       </c>
       <c r="Q61">
-        <v>377.7458150280001</v>
+        <v>368.4824695200001</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1059601652376999</v>
+        <v>0.1074641693686424</v>
       </c>
       <c r="T61">
-        <v>1.389380259531175</v>
+        <v>1.424114766019455</v>
       </c>
       <c r="U61">
         <v>0.1186</v>
       </c>
       <c r="V61">
-        <v>0.1774091615067969</v>
+        <v>0.1744523421483503</v>
       </c>
       <c r="W61">
-        <v>0.09755927344529389</v>
+        <v>0.09790995222120566</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.861209521877655</v>
+        <v>0.8468560298463607</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6341,22 +6341,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1017316390801803</v>
+        <v>0.1024596390801804</v>
       </c>
       <c r="C62">
-        <v>-1257.792178650605</v>
+        <v>-1413.465983380948</v>
       </c>
       <c r="D62">
-        <v>4459.907821349395</v>
+        <v>4402.604016619051</v>
       </c>
       <c r="E62">
-        <v>2895.3</v>
+        <v>2993.67</v>
       </c>
       <c r="F62">
-        <v>5902.2</v>
+        <v>6000.57</v>
       </c>
       <c r="G62">
         <v>184.5</v>
@@ -6377,37 +6377,37 @@
         <v>592.8</v>
       </c>
       <c r="M62">
-        <v>700.0009200000001</v>
+        <v>711.667602</v>
       </c>
       <c r="N62">
-        <v>-107.2009200000001</v>
+        <v>-118.867602</v>
       </c>
       <c r="O62">
-        <v>-22.08338952000003</v>
+        <v>-24.48672601200001</v>
       </c>
       <c r="P62">
-        <v>-85.11753048000008</v>
+        <v>-94.38087598800003</v>
       </c>
       <c r="Q62">
-        <v>368.4824695200001</v>
+        <v>359.2191240120001</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1074641693686424</v>
+        <v>0.1090453019165563</v>
       </c>
       <c r="T62">
-        <v>1.424114766019455</v>
+        <v>1.460630529250723</v>
       </c>
       <c r="U62">
         <v>0.1186</v>
       </c>
       <c r="V62">
-        <v>0.1744523421483503</v>
+        <v>0.171592467686902</v>
       </c>
       <c r="W62">
-        <v>0.09790995222120566</v>
+        <v>0.09824913333233344</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.8468560298463607</v>
+        <v>0.8329731441111745</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1024596390801804</v>
+        <v>0.1031876390801804</v>
       </c>
       <c r="C63">
-        <v>-1413.465983380948</v>
+        <v>-1567.685915099181</v>
       </c>
       <c r="D63">
-        <v>4402.604016619051</v>
+        <v>4346.754084900818</v>
       </c>
       <c r="E63">
-        <v>2993.67</v>
+        <v>3092.04</v>
       </c>
       <c r="F63">
-        <v>6000.57</v>
+        <v>6098.94</v>
       </c>
       <c r="G63">
         <v>184.5</v>
@@ -6459,37 +6459,37 @@
         <v>592.8</v>
       </c>
       <c r="M63">
-        <v>711.667602</v>
+        <v>723.334284</v>
       </c>
       <c r="N63">
-        <v>-118.867602</v>
+        <v>-130.5342840000001</v>
       </c>
       <c r="O63">
-        <v>-24.48672601200001</v>
+        <v>-26.89006250400002</v>
       </c>
       <c r="P63">
-        <v>-94.38087598800003</v>
+        <v>-103.6442214960001</v>
       </c>
       <c r="Q63">
-        <v>359.2191240120001</v>
+        <v>349.9557785040001</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1090453019165563</v>
+        <v>0.110709651966992</v>
       </c>
       <c r="T63">
-        <v>1.460630529250723</v>
+        <v>1.499068174757321</v>
       </c>
       <c r="U63">
         <v>0.1186</v>
       </c>
       <c r="V63">
-        <v>0.171592467686902</v>
+        <v>0.168824847240339</v>
       </c>
       <c r="W63">
-        <v>0.09824913333233344</v>
+        <v>0.09857737311729581</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.8329731441111745</v>
+        <v>0.8195380933997038</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6505,22 +6505,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1031876390801804</v>
+        <v>0.1039156390801804</v>
       </c>
       <c r="C64">
-        <v>-1567.685915099181</v>
+        <v>-1720.506610710426</v>
       </c>
       <c r="D64">
-        <v>4346.754084900818</v>
+        <v>4292.303389289575</v>
       </c>
       <c r="E64">
-        <v>3092.04</v>
+        <v>3190.41</v>
       </c>
       <c r="F64">
-        <v>6098.94</v>
+        <v>6197.31</v>
       </c>
       <c r="G64">
         <v>184.5</v>
@@ -6541,37 +6541,37 @@
         <v>592.8</v>
       </c>
       <c r="M64">
-        <v>723.334284</v>
+        <v>735.0009660000001</v>
       </c>
       <c r="N64">
-        <v>-130.5342840000001</v>
+        <v>-142.2009660000001</v>
       </c>
       <c r="O64">
-        <v>-26.89006250400002</v>
+        <v>-29.29339899600003</v>
       </c>
       <c r="P64">
-        <v>-103.6442214960001</v>
+        <v>-112.9075670040001</v>
       </c>
       <c r="Q64">
-        <v>349.9557785040001</v>
+        <v>340.692432996</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.110709651966992</v>
+        <v>0.1124639668850188</v>
       </c>
       <c r="T64">
-        <v>1.499068174757321</v>
+        <v>1.539583530831843</v>
       </c>
       <c r="U64">
         <v>0.1186</v>
       </c>
       <c r="V64">
-        <v>0.168824847240339</v>
+        <v>0.1661450877603336</v>
       </c>
       <c r="W64">
-        <v>0.09857737311729581</v>
+        <v>0.09889519259162444</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.8195380933997038</v>
+        <v>0.8065295522346292</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6587,22 +6587,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1039156390801804</v>
+        <v>0.1584320863337237</v>
       </c>
       <c r="C65">
-        <v>-1720.506610710426</v>
+        <v>-3896.447389476574</v>
       </c>
       <c r="D65">
-        <v>4292.303389289575</v>
+        <v>2214.732610523427</v>
       </c>
       <c r="E65">
-        <v>3190.41</v>
+        <v>3288.78</v>
       </c>
       <c r="F65">
-        <v>6197.31</v>
+        <v>6295.68</v>
       </c>
       <c r="G65">
         <v>184.5</v>
@@ -6623,45 +6623,45 @@
         <v>592.8</v>
       </c>
       <c r="M65">
-        <v>735.0009660000001</v>
+        <v>1264.172544</v>
       </c>
       <c r="N65">
-        <v>-142.2009660000001</v>
+        <v>-671.3725440000001</v>
       </c>
       <c r="O65">
-        <v>-29.29339899600003</v>
+        <v>-138.302744064</v>
       </c>
       <c r="P65">
-        <v>-112.9075670040001</v>
+        <v>-533.069799936</v>
       </c>
       <c r="Q65">
-        <v>340.692432996</v>
+        <v>-79.46979993599984</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1124639668850188</v>
+        <v>0.1175947638916674</v>
       </c>
       <c r="T65">
-        <v>1.539583530831843</v>
+        <v>1.65807768802927</v>
       </c>
       <c r="U65">
-        <v>0.1186</v>
+        <v>0.2008</v>
       </c>
       <c r="V65">
-        <v>0.1661450877603336</v>
+        <v>0.09659820613854432</v>
       </c>
       <c r="W65">
-        <v>0.09889519259162444</v>
+        <v>0.1814030802073803</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y65">
-        <v>0.8065295522346292</v>
+        <v>0.4689233307696327</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6669,22 +6669,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1584320863337237</v>
+        <v>0.1599820863337237</v>
       </c>
       <c r="C66">
-        <v>-3896.447389476574</v>
+        <v>-4024.881961394432</v>
       </c>
       <c r="D66">
-        <v>2214.732610523427</v>
+        <v>2184.668038605568</v>
       </c>
       <c r="E66">
-        <v>3288.78</v>
+        <v>3387.15</v>
       </c>
       <c r="F66">
-        <v>6295.68</v>
+        <v>6394.05</v>
       </c>
       <c r="G66">
         <v>184.5</v>
@@ -6705,37 +6705,37 @@
         <v>592.8</v>
       </c>
       <c r="M66">
-        <v>1264.172544</v>
+        <v>1283.92524</v>
       </c>
       <c r="N66">
-        <v>-671.3725440000001</v>
+        <v>-691.1252400000001</v>
       </c>
       <c r="O66">
-        <v>-138.302744064</v>
+        <v>-142.37179944</v>
       </c>
       <c r="P66">
-        <v>-533.069799936</v>
+        <v>-548.7534405600001</v>
       </c>
       <c r="Q66">
-        <v>-79.46979993599984</v>
+        <v>-95.15344055999992</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1175947638916674</v>
+        <v>0.1196460428600007</v>
       </c>
       <c r="T66">
-        <v>1.65807768802927</v>
+        <v>1.705451336258678</v>
       </c>
       <c r="U66">
         <v>0.2008</v>
       </c>
       <c r="V66">
-        <v>0.09659820613854432</v>
+        <v>0.09511207989025902</v>
       </c>
       <c r="W66">
-        <v>0.1814030802073803</v>
+        <v>0.181701494358036</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.4689233307696327</v>
+        <v>0.4617091256808691</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6751,22 +6751,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1599820863337237</v>
+        <v>0.1615320863337237</v>
       </c>
       <c r="C67">
-        <v>-4024.881961394432</v>
+        <v>-4152.511223601751</v>
       </c>
       <c r="D67">
-        <v>2184.668038605568</v>
+        <v>2155.408776398249</v>
       </c>
       <c r="E67">
-        <v>3387.15</v>
+        <v>3485.52</v>
       </c>
       <c r="F67">
-        <v>6394.05</v>
+        <v>6492.42</v>
       </c>
       <c r="G67">
         <v>184.5</v>
@@ -6787,37 +6787,37 @@
         <v>592.8</v>
       </c>
       <c r="M67">
-        <v>1283.92524</v>
+        <v>1303.677936</v>
       </c>
       <c r="N67">
-        <v>-691.1252400000001</v>
+        <v>-710.8779360000001</v>
       </c>
       <c r="O67">
-        <v>-142.37179944</v>
+        <v>-146.440854816</v>
       </c>
       <c r="P67">
-        <v>-548.7534405600001</v>
+        <v>-564.437081184</v>
       </c>
       <c r="Q67">
-        <v>-95.15344055999992</v>
+        <v>-110.8370811839999</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1196460428600007</v>
+        <v>0.1218179852970596</v>
       </c>
       <c r="T67">
-        <v>1.705451336258678</v>
+        <v>1.755611669678051</v>
       </c>
       <c r="U67">
         <v>0.2008</v>
       </c>
       <c r="V67">
-        <v>0.09511207989025902</v>
+        <v>0.09367098777070965</v>
       </c>
       <c r="W67">
-        <v>0.181701494358036</v>
+        <v>0.1819908656556415</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.4617091256808691</v>
+        <v>0.4547135328675226</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6833,22 +6833,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1615320863337237</v>
+        <v>0.1630820863337237</v>
       </c>
       <c r="C68">
-        <v>-4152.511223601751</v>
+        <v>-4279.367105016845</v>
       </c>
       <c r="D68">
-        <v>2155.408776398249</v>
+        <v>2126.922894983154</v>
       </c>
       <c r="E68">
-        <v>3485.52</v>
+        <v>3583.89</v>
       </c>
       <c r="F68">
-        <v>6492.42</v>
+        <v>6590.79</v>
       </c>
       <c r="G68">
         <v>184.5</v>
@@ -6869,37 +6869,37 @@
         <v>592.8</v>
       </c>
       <c r="M68">
-        <v>1303.677936</v>
+        <v>1323.430632</v>
       </c>
       <c r="N68">
-        <v>-710.8779360000001</v>
+        <v>-730.6306320000001</v>
       </c>
       <c r="O68">
-        <v>-146.440854816</v>
+        <v>-150.509910192</v>
       </c>
       <c r="P68">
-        <v>-564.437081184</v>
+        <v>-580.1207218080001</v>
       </c>
       <c r="Q68">
-        <v>-110.8370811839999</v>
+        <v>-126.520721808</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1218179852970596</v>
+        <v>0.1241215606090917</v>
       </c>
       <c r="T68">
-        <v>1.755611669678051</v>
+        <v>1.808812023304659</v>
       </c>
       <c r="U68">
         <v>0.2008</v>
       </c>
       <c r="V68">
-        <v>0.09367098777070965</v>
+        <v>0.09227291332637071</v>
       </c>
       <c r="W68">
-        <v>0.1819908656556415</v>
+        <v>0.1822715990040648</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.4547135328675226</v>
+        <v>0.4479267637202461</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6915,22 +6915,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1630820863337237</v>
+        <v>0.1646320863337237</v>
       </c>
       <c r="C69">
-        <v>-4279.367105016845</v>
+        <v>-4405.479868683939</v>
       </c>
       <c r="D69">
-        <v>2126.922894983154</v>
+        <v>2099.180131316063</v>
       </c>
       <c r="E69">
-        <v>3583.89</v>
+        <v>3682.260000000001</v>
       </c>
       <c r="F69">
-        <v>6590.79</v>
+        <v>6689.160000000001</v>
       </c>
       <c r="G69">
         <v>184.5</v>
@@ -6951,37 +6951,37 @@
         <v>592.8</v>
       </c>
       <c r="M69">
-        <v>1323.430632</v>
+        <v>1343.183328</v>
       </c>
       <c r="N69">
-        <v>-730.6306320000001</v>
+        <v>-750.3833280000003</v>
       </c>
       <c r="O69">
-        <v>-150.509910192</v>
+        <v>-154.5789655680001</v>
       </c>
       <c r="P69">
-        <v>-580.1207218080001</v>
+        <v>-595.8043624320003</v>
       </c>
       <c r="Q69">
-        <v>-126.520721808</v>
+        <v>-142.2043624320002</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1241215606090917</v>
+        <v>0.1265691093781258</v>
       </c>
       <c r="T69">
-        <v>1.808812023304659</v>
+        <v>1.865337399032929</v>
       </c>
       <c r="U69">
         <v>0.2008</v>
       </c>
       <c r="V69">
-        <v>0.09227291332637071</v>
+        <v>0.09091595871862994</v>
       </c>
       <c r="W69">
-        <v>0.1822715990040648</v>
+        <v>0.1825440754892991</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.4479267637202461</v>
+        <v>0.4413396054302424</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6997,22 +6997,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1646320863337237</v>
+        <v>0.1661820863337237</v>
       </c>
       <c r="C70">
-        <v>-4405.479868683939</v>
+        <v>-4530.878219019384</v>
       </c>
       <c r="D70">
-        <v>2099.180131316063</v>
+        <v>2072.151780980616</v>
       </c>
       <c r="E70">
-        <v>3682.260000000001</v>
+        <v>3780.630000000001</v>
       </c>
       <c r="F70">
-        <v>6689.160000000001</v>
+        <v>6787.530000000001</v>
       </c>
       <c r="G70">
         <v>184.5</v>
@@ -7033,37 +7033,37 @@
         <v>592.8</v>
       </c>
       <c r="M70">
-        <v>1343.183328</v>
+        <v>1362.936024</v>
       </c>
       <c r="N70">
-        <v>-750.3833280000003</v>
+        <v>-770.1360240000001</v>
       </c>
       <c r="O70">
-        <v>-154.5789655680001</v>
+        <v>-158.6480209440001</v>
       </c>
       <c r="P70">
-        <v>-595.8043624320003</v>
+        <v>-611.488003056</v>
       </c>
       <c r="Q70">
-        <v>-142.2043624320002</v>
+        <v>-157.8880030559999</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1265691093781258</v>
+        <v>0.1291745645193557</v>
       </c>
       <c r="T70">
-        <v>1.865337399032929</v>
+        <v>1.925509573195282</v>
       </c>
       <c r="U70">
         <v>0.2008</v>
       </c>
       <c r="V70">
-        <v>0.09091595871862994</v>
+        <v>0.08959833612850487</v>
       </c>
       <c r="W70">
-        <v>0.1825440754892991</v>
+        <v>0.1828086541053962</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.4413396054302424</v>
+        <v>0.4349433792645867</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7079,22 +7079,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1661820863337237</v>
+        <v>0.1677320863337237</v>
       </c>
       <c r="C71">
-        <v>-4530.878219019384</v>
+        <v>-4655.589400878024</v>
       </c>
       <c r="D71">
-        <v>2072.151780980616</v>
+        <v>2045.810599121976</v>
       </c>
       <c r="E71">
-        <v>3780.630000000001</v>
+        <v>3879</v>
       </c>
       <c r="F71">
-        <v>6787.530000000001</v>
+        <v>6885.900000000001</v>
       </c>
       <c r="G71">
         <v>184.5</v>
@@ -7115,37 +7115,37 @@
         <v>592.8</v>
       </c>
       <c r="M71">
-        <v>1362.936024</v>
+        <v>1382.68872</v>
       </c>
       <c r="N71">
-        <v>-770.1360240000001</v>
+        <v>-789.8887200000001</v>
       </c>
       <c r="O71">
-        <v>-158.6480209440001</v>
+        <v>-162.71707632</v>
       </c>
       <c r="P71">
-        <v>-611.488003056</v>
+        <v>-627.1716436800001</v>
       </c>
       <c r="Q71">
-        <v>-157.8880030559999</v>
+        <v>-173.57164368</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1291745645193557</v>
+        <v>0.1319537166700009</v>
       </c>
       <c r="T71">
-        <v>1.925509573195282</v>
+        <v>1.989693225635125</v>
       </c>
       <c r="U71">
         <v>0.2008</v>
       </c>
       <c r="V71">
-        <v>0.08959833612850487</v>
+        <v>0.08831835989809766</v>
       </c>
       <c r="W71">
-        <v>0.1828086541053962</v>
+        <v>0.183065673332462</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.4349433792645867</v>
+        <v>0.4287299024179498</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7161,22 +7161,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1677320863337237</v>
+        <v>0.1692820863337237</v>
       </c>
       <c r="C72">
-        <v>-4655.589400878024</v>
+        <v>-4779.639291158377</v>
       </c>
       <c r="D72">
-        <v>2045.810599121976</v>
+        <v>2020.130708841624</v>
       </c>
       <c r="E72">
-        <v>3879</v>
+        <v>3977.37</v>
       </c>
       <c r="F72">
-        <v>6885.900000000001</v>
+        <v>6984.27</v>
       </c>
       <c r="G72">
         <v>184.5</v>
@@ -7197,37 +7197,37 @@
         <v>592.8</v>
       </c>
       <c r="M72">
-        <v>1382.68872</v>
+        <v>1402.441416</v>
       </c>
       <c r="N72">
-        <v>-789.8887200000001</v>
+        <v>-809.6414160000002</v>
       </c>
       <c r="O72">
-        <v>-162.71707632</v>
+        <v>-166.786131696</v>
       </c>
       <c r="P72">
-        <v>-627.1716436800001</v>
+        <v>-642.8552843040002</v>
       </c>
       <c r="Q72">
-        <v>-173.57164368</v>
+        <v>-189.255284304</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1319537166700009</v>
+        <v>0.1349245344862078</v>
       </c>
       <c r="T72">
-        <v>1.989693225635125</v>
+        <v>2.058303336863922</v>
       </c>
       <c r="U72">
         <v>0.2008</v>
       </c>
       <c r="V72">
-        <v>0.08831835989809766</v>
+        <v>0.08707443933615262</v>
       </c>
       <c r="W72">
-        <v>0.183065673332462</v>
+        <v>0.1833154525813006</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.4287299024179498</v>
+        <v>0.4226914530881195</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7243,22 +7243,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1692820863337237</v>
+        <v>0.1708320863337237</v>
       </c>
       <c r="C73">
-        <v>-4779.639291158375</v>
+        <v>-4903.052483594171</v>
       </c>
       <c r="D73">
-        <v>2020.130708841624</v>
+        <v>1995.087516405828</v>
       </c>
       <c r="E73">
-        <v>3977.369999999999</v>
+        <v>4075.739999999999</v>
       </c>
       <c r="F73">
-        <v>6984.27</v>
+        <v>7082.639999999999</v>
       </c>
       <c r="G73">
         <v>184.5</v>
@@ -7279,37 +7279,37 @@
         <v>592.8</v>
       </c>
       <c r="M73">
-        <v>1402.441416</v>
+        <v>1422.194112</v>
       </c>
       <c r="N73">
-        <v>-809.6414159999999</v>
+        <v>-829.394112</v>
       </c>
       <c r="O73">
-        <v>-166.786131696</v>
+        <v>-170.855187072</v>
       </c>
       <c r="P73">
-        <v>-642.855284304</v>
+        <v>-658.5389249279999</v>
       </c>
       <c r="Q73">
-        <v>-189.2552843039998</v>
+        <v>-204.9389249279998</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1349245344862078</v>
+        <v>0.1381075535750009</v>
       </c>
       <c r="T73">
-        <v>2.058303336863921</v>
+        <v>2.131814170323347</v>
       </c>
       <c r="U73">
         <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.08707443933615264</v>
+        <v>0.08586507212315052</v>
       </c>
       <c r="W73">
-        <v>0.1833154525813006</v>
+        <v>0.1835582935176714</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.4226914530881196</v>
+        <v>0.4168207384618957</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7325,22 +7325,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1708320863337237</v>
+        <v>0.1723820863337236</v>
       </c>
       <c r="C74">
-        <v>-4903.052483594171</v>
+        <v>-5025.852367316236</v>
       </c>
       <c r="D74">
-        <v>1995.087516405828</v>
+        <v>1970.657632683764</v>
       </c>
       <c r="E74">
-        <v>4075.739999999999</v>
+        <v>4174.110000000001</v>
       </c>
       <c r="F74">
-        <v>7082.639999999999</v>
+        <v>7181.01</v>
       </c>
       <c r="G74">
         <v>184.5</v>
@@ -7361,37 +7361,37 @@
         <v>592.8</v>
       </c>
       <c r="M74">
-        <v>1422.194112</v>
+        <v>1441.946808</v>
       </c>
       <c r="N74">
-        <v>-829.394112</v>
+        <v>-849.1468080000002</v>
       </c>
       <c r="O74">
-        <v>-170.855187072</v>
+        <v>-174.9242424480001</v>
       </c>
       <c r="P74">
-        <v>-658.5389249279999</v>
+        <v>-674.2225655520001</v>
       </c>
       <c r="Q74">
-        <v>-204.9389249279998</v>
+        <v>-220.622565552</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1381075535750009</v>
+        <v>0.1415263518555565</v>
       </c>
       <c r="T74">
-        <v>2.131814170323347</v>
+        <v>2.210770250705693</v>
       </c>
       <c r="U74">
         <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.08586507212315052</v>
+        <v>0.08468883825844982</v>
       </c>
       <c r="W74">
-        <v>0.1835582935176714</v>
+        <v>0.1837944812777033</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.4168207384618957</v>
+        <v>0.4111108653322806</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7407,22 +7407,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1723820863337236</v>
+        <v>0.1739320863337236</v>
       </c>
       <c r="C75">
-        <v>-5025.852367316236</v>
+        <v>-5148.061199712239</v>
       </c>
       <c r="D75">
-        <v>1970.657632683764</v>
+        <v>1946.818800287761</v>
       </c>
       <c r="E75">
-        <v>4174.110000000001</v>
+        <v>4272.48</v>
       </c>
       <c r="F75">
-        <v>7181.01</v>
+        <v>7279.38</v>
       </c>
       <c r="G75">
         <v>184.5</v>
@@ -7443,37 +7443,37 @@
         <v>592.8</v>
       </c>
       <c r="M75">
-        <v>1441.946808</v>
+        <v>1461.699504</v>
       </c>
       <c r="N75">
-        <v>-849.1468080000002</v>
+        <v>-868.8995040000002</v>
       </c>
       <c r="O75">
-        <v>-174.9242424480001</v>
+        <v>-178.9932978240001</v>
       </c>
       <c r="P75">
-        <v>-674.2225655520001</v>
+        <v>-689.9062061760002</v>
       </c>
       <c r="Q75">
-        <v>-220.622565552</v>
+        <v>-236.306206176</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1415263518555565</v>
+        <v>0.1452081346192317</v>
       </c>
       <c r="T75">
-        <v>2.210770250705693</v>
+        <v>2.295799875732835</v>
       </c>
       <c r="U75">
         <v>0.2008</v>
       </c>
       <c r="V75">
-        <v>0.08468883825844982</v>
+        <v>0.08354439449820049</v>
       </c>
       <c r="W75">
-        <v>0.1837944812777033</v>
+        <v>0.1840242855847613</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.4111108653322806</v>
+        <v>0.4055553130980606</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7489,22 +7489,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1739320863337236</v>
+        <v>0.1754820863337236</v>
       </c>
       <c r="C76">
-        <v>-5148.061199712239</v>
+        <v>-5269.700174061407</v>
       </c>
       <c r="D76">
-        <v>1946.818800287761</v>
+        <v>1923.549825938593</v>
       </c>
       <c r="E76">
-        <v>4272.48</v>
+        <v>4370.85</v>
       </c>
       <c r="F76">
-        <v>7279.38</v>
+        <v>7377.75</v>
       </c>
       <c r="G76">
         <v>184.5</v>
@@ -7525,37 +7525,37 @@
         <v>592.8</v>
       </c>
       <c r="M76">
-        <v>1461.699504</v>
+        <v>1481.4522</v>
       </c>
       <c r="N76">
-        <v>-868.8995040000002</v>
+        <v>-888.6522</v>
       </c>
       <c r="O76">
-        <v>-178.9932978240001</v>
+        <v>-183.0623532</v>
       </c>
       <c r="P76">
-        <v>-689.9062061760002</v>
+        <v>-705.5898468</v>
       </c>
       <c r="Q76">
-        <v>-236.306206176</v>
+        <v>-251.9898467999999</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1452081346192317</v>
+        <v>0.149184460004001</v>
       </c>
       <c r="T76">
-        <v>2.295799875732835</v>
+        <v>2.387631870762149</v>
       </c>
       <c r="U76">
         <v>0.2008</v>
       </c>
       <c r="V76">
-        <v>0.08354439449820049</v>
+        <v>0.08243046923822449</v>
       </c>
       <c r="W76">
-        <v>0.1840242855847613</v>
+        <v>0.1842479617769645</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.4055553130980606</v>
+        <v>0.4001479089234199</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7571,22 +7571,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1754820863337236</v>
+        <v>0.1770320863337236</v>
       </c>
       <c r="C77">
-        <v>-5269.700174061407</v>
+        <v>-5390.789482376164</v>
       </c>
       <c r="D77">
-        <v>1923.549825938593</v>
+        <v>1900.830517623836</v>
       </c>
       <c r="E77">
-        <v>4370.85</v>
+        <v>4469.219999999999</v>
       </c>
       <c r="F77">
-        <v>7377.75</v>
+        <v>7476.12</v>
       </c>
       <c r="G77">
         <v>184.5</v>
@@ -7607,37 +7607,37 @@
         <v>592.8</v>
       </c>
       <c r="M77">
-        <v>1481.4522</v>
+        <v>1501.204896</v>
       </c>
       <c r="N77">
-        <v>-888.6522</v>
+        <v>-908.404896</v>
       </c>
       <c r="O77">
-        <v>-183.0623532</v>
+        <v>-187.131408576</v>
       </c>
       <c r="P77">
-        <v>-705.5898468</v>
+        <v>-721.273487424</v>
       </c>
       <c r="Q77">
-        <v>-251.9898467999999</v>
+        <v>-267.6734874239999</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.149184460004001</v>
+        <v>0.1534921458375011</v>
       </c>
       <c r="T77">
-        <v>2.387631870762149</v>
+        <v>2.487116532043905</v>
       </c>
       <c r="U77">
         <v>0.2008</v>
       </c>
       <c r="V77">
-        <v>0.08243046923822449</v>
+        <v>0.08134585780087944</v>
       </c>
       <c r="W77">
-        <v>0.1842479617769645</v>
+        <v>0.1844657517535834</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.4001479089234199</v>
+        <v>0.394882804858638</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7653,22 +7653,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1770320863337236</v>
+        <v>0.1785820863337237</v>
       </c>
       <c r="C78">
-        <v>-5390.789482376164</v>
+        <v>-5511.348373842383</v>
       </c>
       <c r="D78">
-        <v>1900.830517623836</v>
+        <v>1878.641626157617</v>
       </c>
       <c r="E78">
-        <v>4469.219999999999</v>
+        <v>4567.59</v>
       </c>
       <c r="F78">
-        <v>7476.12</v>
+        <v>7574.49</v>
       </c>
       <c r="G78">
         <v>184.5</v>
@@ -7689,37 +7689,37 @@
         <v>592.8</v>
       </c>
       <c r="M78">
-        <v>1501.204896</v>
+        <v>1520.957592</v>
       </c>
       <c r="N78">
-        <v>-908.404896</v>
+        <v>-928.157592</v>
       </c>
       <c r="O78">
-        <v>-187.131408576</v>
+        <v>-191.200463952</v>
       </c>
       <c r="P78">
-        <v>-721.273487424</v>
+        <v>-736.957128048</v>
       </c>
       <c r="Q78">
-        <v>-267.6734874239999</v>
+        <v>-283.3571280479998</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1534921458375011</v>
+        <v>0.1581744130478272</v>
       </c>
       <c r="T78">
-        <v>2.487116532043905</v>
+        <v>2.595252033437119</v>
       </c>
       <c r="U78">
         <v>0.2008</v>
       </c>
       <c r="V78">
-        <v>0.08134585780087944</v>
+        <v>0.08028941808917971</v>
       </c>
       <c r="W78">
-        <v>0.1844657517535834</v>
+        <v>0.1846778848476927</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.394882804858638</v>
+        <v>0.3897544567435908</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7735,22 +7735,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1785820863337237</v>
+        <v>0.1801320863337237</v>
       </c>
       <c r="C79">
-        <v>-5511.348373842383</v>
+        <v>-5631.395209213721</v>
       </c>
       <c r="D79">
-        <v>1878.641626157617</v>
+        <v>1856.96479078628</v>
       </c>
       <c r="E79">
-        <v>4567.59</v>
+        <v>4665.960000000001</v>
       </c>
       <c r="F79">
-        <v>7574.49</v>
+        <v>7672.860000000001</v>
       </c>
       <c r="G79">
         <v>184.5</v>
@@ -7771,37 +7771,37 @@
         <v>592.8</v>
       </c>
       <c r="M79">
-        <v>1520.957592</v>
+        <v>1540.710288</v>
       </c>
       <c r="N79">
-        <v>-928.157592</v>
+        <v>-947.9102880000003</v>
       </c>
       <c r="O79">
-        <v>-191.200463952</v>
+        <v>-195.2695193280001</v>
       </c>
       <c r="P79">
-        <v>-736.957128048</v>
+        <v>-752.6407686720001</v>
       </c>
       <c r="Q79">
-        <v>-283.3571280479998</v>
+        <v>-299.040768672</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1581744130478272</v>
+        <v>0.1632823409136375</v>
       </c>
       <c r="T79">
-        <v>2.595252033437119</v>
+        <v>2.713218034956987</v>
       </c>
       <c r="U79">
         <v>0.2008</v>
       </c>
       <c r="V79">
-        <v>0.08028941808917971</v>
+        <v>0.07926006657521584</v>
       </c>
       <c r="W79">
-        <v>0.1846778848476927</v>
+        <v>0.1848845786316967</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3897544567435908</v>
+        <v>0.3847576047340575</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7817,22 +7817,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1801320863337237</v>
+        <v>0.1816820863337237</v>
       </c>
       <c r="C80">
-        <v>-5631.395209213721</v>
+        <v>-5750.947511483128</v>
       </c>
       <c r="D80">
-        <v>1856.96479078628</v>
+        <v>1835.782488516872</v>
       </c>
       <c r="E80">
-        <v>4665.960000000001</v>
+        <v>4764.33</v>
       </c>
       <c r="F80">
-        <v>7672.860000000001</v>
+        <v>7771.23</v>
       </c>
       <c r="G80">
         <v>184.5</v>
@@ -7853,37 +7853,37 @@
         <v>592.8</v>
       </c>
       <c r="M80">
-        <v>1540.710288</v>
+        <v>1560.462984</v>
       </c>
       <c r="N80">
-        <v>-947.9102880000003</v>
+        <v>-967.6629840000003</v>
       </c>
       <c r="O80">
-        <v>-195.2695193280001</v>
+        <v>-199.3385747040001</v>
       </c>
       <c r="P80">
-        <v>-752.6407686720001</v>
+        <v>-768.3244092960002</v>
       </c>
       <c r="Q80">
-        <v>-299.040768672</v>
+        <v>-314.7244092960001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1632823409136375</v>
+        <v>0.1688767381000013</v>
       </c>
       <c r="T80">
-        <v>2.713218034956987</v>
+        <v>2.842418893764464</v>
       </c>
       <c r="U80">
         <v>0.2008</v>
       </c>
       <c r="V80">
-        <v>0.07926006657521584</v>
+        <v>0.07825677459325109</v>
       </c>
       <c r="W80">
-        <v>0.1848845786316967</v>
+        <v>0.1850860396616752</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3847576047340575</v>
+        <v>0.3798872553070441</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7899,22 +7899,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1816820863337237</v>
+        <v>0.1832320863337236</v>
       </c>
       <c r="C81">
-        <v>-5750.947511483128</v>
+        <v>-5870.022013125426</v>
       </c>
       <c r="D81">
-        <v>1835.782488516872</v>
+        <v>1815.077986874574</v>
       </c>
       <c r="E81">
-        <v>4764.33</v>
+        <v>4862.700000000001</v>
       </c>
       <c r="F81">
-        <v>7771.23</v>
+        <v>7869.6</v>
       </c>
       <c r="G81">
         <v>184.5</v>
@@ -7935,37 +7935,37 @@
         <v>592.8</v>
       </c>
       <c r="M81">
-        <v>1560.462984</v>
+        <v>1580.21568</v>
       </c>
       <c r="N81">
-        <v>-967.6629840000003</v>
+        <v>-987.4156800000001</v>
       </c>
       <c r="O81">
-        <v>-199.3385747040001</v>
+        <v>-203.40763008</v>
       </c>
       <c r="P81">
-        <v>-768.3244092960002</v>
+        <v>-784.0080499200001</v>
       </c>
       <c r="Q81">
-        <v>-314.7244092960001</v>
+        <v>-330.4080499199999</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1688767381000013</v>
+        <v>0.1750305750050013</v>
       </c>
       <c r="T81">
-        <v>2.842418893764464</v>
+        <v>2.984539838452687</v>
       </c>
       <c r="U81">
         <v>0.2008</v>
       </c>
       <c r="V81">
-        <v>0.07825677459325109</v>
+        <v>0.07727856491083547</v>
       </c>
       <c r="W81">
-        <v>0.1850860396616752</v>
+        <v>0.1852824641659042</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3798872553070441</v>
+        <v>0.3751386646157061</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7981,22 +7981,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1832320863337236</v>
+        <v>0.1847820863337236</v>
       </c>
       <c r="C82">
-        <v>-5870.022013125426</v>
+        <v>-5988.634700178634</v>
       </c>
       <c r="D82">
-        <v>1815.077986874574</v>
+        <v>1794.835299821365</v>
       </c>
       <c r="E82">
-        <v>4862.700000000001</v>
+        <v>4961.07</v>
       </c>
       <c r="F82">
-        <v>7869.6</v>
+        <v>7967.97</v>
       </c>
       <c r="G82">
         <v>184.5</v>
@@ -8017,37 +8017,37 @@
         <v>592.8</v>
       </c>
       <c r="M82">
-        <v>1580.21568</v>
+        <v>1599.968376</v>
       </c>
       <c r="N82">
-        <v>-987.4156800000001</v>
+        <v>-1007.168376</v>
       </c>
       <c r="O82">
-        <v>-203.40763008</v>
+        <v>-207.476685456</v>
       </c>
       <c r="P82">
-        <v>-784.0080499200001</v>
+        <v>-799.691690544</v>
       </c>
       <c r="Q82">
-        <v>-330.4080499199999</v>
+        <v>-346.0916905439999</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1750305750050013</v>
+        <v>0.1818321842157909</v>
       </c>
       <c r="T82">
-        <v>2.984539838452687</v>
+        <v>3.141620882581776</v>
       </c>
       <c r="U82">
         <v>0.2008</v>
       </c>
       <c r="V82">
-        <v>0.07727856491083547</v>
+        <v>0.07632450855391157</v>
       </c>
       <c r="W82">
-        <v>0.1852824641659042</v>
+        <v>0.1854740386823746</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3751386646157061</v>
+        <v>0.3705073230772405</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8063,22 +8063,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1847820863337236</v>
+        <v>0.1863320863337237</v>
       </c>
       <c r="C83">
-        <v>-5988.634700178634</v>
+        <v>-6106.800853408132</v>
       </c>
       <c r="D83">
-        <v>1794.835299821365</v>
+        <v>1775.039146591869</v>
       </c>
       <c r="E83">
-        <v>4961.07</v>
+        <v>5059.440000000001</v>
       </c>
       <c r="F83">
-        <v>7967.97</v>
+        <v>8066.340000000001</v>
       </c>
       <c r="G83">
         <v>184.5</v>
@@ -8099,37 +8099,37 @@
         <v>592.8</v>
       </c>
       <c r="M83">
-        <v>1599.968376</v>
+        <v>1619.721072</v>
       </c>
       <c r="N83">
-        <v>-1007.168376</v>
+        <v>-1026.921072</v>
       </c>
       <c r="O83">
-        <v>-207.476685456</v>
+        <v>-211.5457408320001</v>
       </c>
       <c r="P83">
-        <v>-799.691690544</v>
+        <v>-815.3753311680002</v>
       </c>
       <c r="Q83">
-        <v>-346.0916905439999</v>
+        <v>-361.7753311680001</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1818321842157909</v>
+        <v>0.1893895277833348</v>
       </c>
       <c r="T83">
-        <v>3.141620882581776</v>
+        <v>3.316155376058541</v>
       </c>
       <c r="U83">
         <v>0.2008</v>
       </c>
       <c r="V83">
-        <v>0.07632450855391157</v>
+        <v>0.0753937218642297</v>
       </c>
       <c r="W83">
-        <v>0.1854740386823746</v>
+        <v>0.1856609406496627</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3705073230772405</v>
+        <v>0.3659889410884937</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8145,22 +8145,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1863320863337237</v>
+        <v>0.1878820863337236</v>
       </c>
       <c r="C84">
-        <v>-6106.800853408132</v>
+        <v>-6224.535086776405</v>
       </c>
       <c r="D84">
-        <v>1775.039146591869</v>
+        <v>1755.674913223596</v>
       </c>
       <c r="E84">
-        <v>5059.440000000001</v>
+        <v>5157.810000000001</v>
       </c>
       <c r="F84">
-        <v>8066.340000000001</v>
+        <v>8164.710000000001</v>
       </c>
       <c r="G84">
         <v>184.5</v>
@@ -8181,37 +8181,37 @@
         <v>592.8</v>
       </c>
       <c r="M84">
-        <v>1619.721072</v>
+        <v>1639.473768</v>
       </c>
       <c r="N84">
-        <v>-1026.921072</v>
+        <v>-1046.673768</v>
       </c>
       <c r="O84">
-        <v>-211.5457408320001</v>
+        <v>-215.6147962080001</v>
       </c>
       <c r="P84">
-        <v>-815.3753311680002</v>
+        <v>-831.0589717920002</v>
       </c>
       <c r="Q84">
-        <v>-361.7753311680001</v>
+        <v>-377.4589717920001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.1893895277833348</v>
+        <v>0.1978359705941192</v>
       </c>
       <c r="T84">
-        <v>3.316155376058541</v>
+        <v>3.511223339356103</v>
       </c>
       <c r="U84">
         <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.0753937218642297</v>
+        <v>0.07448536376947995</v>
       </c>
       <c r="W84">
-        <v>0.1856609406496627</v>
+        <v>0.1858433389550884</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3659889410884937</v>
+        <v>0.3615794357741745</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8227,22 +8227,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1878820863337236</v>
+        <v>0.1894320863337237</v>
       </c>
       <c r="C85">
-        <v>-6224.535086776405</v>
+        <v>-6341.851383421945</v>
       </c>
       <c r="D85">
-        <v>1755.674913223596</v>
+        <v>1736.728616578056</v>
       </c>
       <c r="E85">
-        <v>5157.810000000001</v>
+        <v>5256.18</v>
       </c>
       <c r="F85">
-        <v>8164.710000000001</v>
+        <v>8263.08</v>
       </c>
       <c r="G85">
         <v>184.5</v>
@@ -8263,37 +8263,37 @@
         <v>592.8</v>
       </c>
       <c r="M85">
-        <v>1639.473768</v>
+        <v>1659.226464</v>
       </c>
       <c r="N85">
-        <v>-1046.673768</v>
+        <v>-1066.426464</v>
       </c>
       <c r="O85">
-        <v>-215.6147962080001</v>
+        <v>-219.6838515840001</v>
       </c>
       <c r="P85">
-        <v>-831.0589717920002</v>
+        <v>-846.742612416</v>
       </c>
       <c r="Q85">
-        <v>-377.4589717920001</v>
+        <v>-393.1426124159999</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.1978359705941192</v>
+        <v>0.2073382187562517</v>
       </c>
       <c r="T85">
-        <v>3.511223339356103</v>
+        <v>3.73067479806586</v>
       </c>
       <c r="U85">
         <v>0.2008</v>
       </c>
       <c r="V85">
-        <v>0.07448536376947995</v>
+        <v>0.07359863324841473</v>
       </c>
       <c r="W85">
-        <v>0.1858433389550884</v>
+        <v>0.1860213944437183</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3615794357741745</v>
+        <v>0.3572749186816249</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8309,22 +8309,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1894320863337236</v>
+        <v>0.1909820863337237</v>
       </c>
       <c r="C86">
-        <v>-6341.851383421945</v>
+        <v>-6458.763129333406</v>
       </c>
       <c r="D86">
-        <v>1736.728616578056</v>
+        <v>1718.186870666593</v>
       </c>
       <c r="E86">
-        <v>5256.18</v>
+        <v>5354.549999999999</v>
       </c>
       <c r="F86">
-        <v>8263.08</v>
+        <v>8361.449999999999</v>
       </c>
       <c r="G86">
         <v>184.5</v>
@@ -8345,37 +8345,37 @@
         <v>592.8</v>
       </c>
       <c r="M86">
-        <v>1659.226464</v>
+        <v>1678.97916</v>
       </c>
       <c r="N86">
-        <v>-1066.426464</v>
+        <v>-1086.17916</v>
       </c>
       <c r="O86">
-        <v>-219.6838515840001</v>
+        <v>-223.75290696</v>
       </c>
       <c r="P86">
-        <v>-846.742612416</v>
+        <v>-862.4262530399999</v>
       </c>
       <c r="Q86">
-        <v>-393.1426124159999</v>
+        <v>-408.8262530399998</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2073382187562516</v>
+        <v>0.2181074333400017</v>
       </c>
       <c r="T86">
-        <v>3.730674798065857</v>
+        <v>3.979386451270249</v>
       </c>
       <c r="U86">
         <v>0.2008</v>
       </c>
       <c r="V86">
-        <v>0.07359863324841473</v>
+        <v>0.07273276697490397</v>
       </c>
       <c r="W86">
-        <v>0.1860213944437183</v>
+        <v>0.1861952603914393</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3572749186816249</v>
+        <v>0.353071684344194</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8391,22 +8391,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1909820863337237</v>
+        <v>0.1925320863337237</v>
       </c>
       <c r="C87">
-        <v>-6458.763129333406</v>
+        <v>-6575.283144889488</v>
       </c>
       <c r="D87">
-        <v>1718.186870666593</v>
+        <v>1700.036855110512</v>
       </c>
       <c r="E87">
-        <v>5354.549999999999</v>
+        <v>5452.92</v>
       </c>
       <c r="F87">
-        <v>8361.449999999999</v>
+        <v>8459.82</v>
       </c>
       <c r="G87">
         <v>184.5</v>
@@ -8427,37 +8427,37 @@
         <v>592.8</v>
       </c>
       <c r="M87">
-        <v>1678.97916</v>
+        <v>1698.731856</v>
       </c>
       <c r="N87">
-        <v>-1086.17916</v>
+        <v>-1105.931856</v>
       </c>
       <c r="O87">
-        <v>-223.75290696</v>
+        <v>-227.821962336</v>
       </c>
       <c r="P87">
-        <v>-862.4262530399999</v>
+        <v>-878.1098936640001</v>
       </c>
       <c r="Q87">
-        <v>-408.8262530399998</v>
+        <v>-424.5098936639999</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2181074333400017</v>
+        <v>0.2304151071500018</v>
       </c>
       <c r="T87">
-        <v>3.979386451270249</v>
+        <v>4.263628340646694</v>
       </c>
       <c r="U87">
         <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.07273276697490397</v>
+        <v>0.07188703712635856</v>
       </c>
       <c r="W87">
-        <v>0.1861952603914393</v>
+        <v>0.1863650829450272</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.353071684344194</v>
+        <v>0.3489661996425173</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8473,22 +8473,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1925320863337237</v>
+        <v>0.1940820863337236</v>
       </c>
       <c r="C88">
-        <v>-6575.283144889488</v>
+        <v>-6691.423714420665</v>
       </c>
       <c r="D88">
-        <v>1700.036855110512</v>
+        <v>1682.266285579336</v>
       </c>
       <c r="E88">
-        <v>5452.92</v>
+        <v>5551.290000000001</v>
       </c>
       <c r="F88">
-        <v>8459.82</v>
+        <v>8558.190000000001</v>
       </c>
       <c r="G88">
         <v>184.5</v>
@@ -8509,37 +8509,37 @@
         <v>592.8</v>
       </c>
       <c r="M88">
-        <v>1698.731856</v>
+        <v>1718.484552</v>
       </c>
       <c r="N88">
-        <v>-1105.931856</v>
+        <v>-1125.684552</v>
       </c>
       <c r="O88">
-        <v>-227.821962336</v>
+        <v>-231.8910177120001</v>
       </c>
       <c r="P88">
-        <v>-878.1098936640001</v>
+        <v>-893.793534288</v>
       </c>
       <c r="Q88">
-        <v>-424.5098936639999</v>
+        <v>-440.1935342879999</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2304151071500018</v>
+        <v>0.2446162692384635</v>
       </c>
       <c r="T88">
-        <v>4.263628340646694</v>
+        <v>4.591599751465671</v>
       </c>
       <c r="U88">
         <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.07188703712635856</v>
+        <v>0.07106074934329698</v>
       </c>
       <c r="W88">
-        <v>0.1863650829450272</v>
+        <v>0.186531001531866</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3489661996425173</v>
+        <v>0.3449550938994999</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8555,22 +8555,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1940820863337236</v>
+        <v>0.1956320863337237</v>
       </c>
       <c r="C89">
-        <v>-6691.423714420665</v>
+        <v>-6807.196613936059</v>
       </c>
       <c r="D89">
-        <v>1682.266285579336</v>
+        <v>1664.86338606394</v>
       </c>
       <c r="E89">
-        <v>5551.290000000001</v>
+        <v>5649.66</v>
       </c>
       <c r="F89">
-        <v>8558.190000000001</v>
+        <v>8656.559999999999</v>
       </c>
       <c r="G89">
         <v>184.5</v>
@@ -8591,37 +8591,37 @@
         <v>592.8</v>
       </c>
       <c r="M89">
-        <v>1718.484552</v>
+        <v>1738.237248</v>
       </c>
       <c r="N89">
-        <v>-1125.684552</v>
+        <v>-1145.437248</v>
       </c>
       <c r="O89">
-        <v>-231.8910177120001</v>
+        <v>-235.960073088</v>
       </c>
       <c r="P89">
-        <v>-893.793534288</v>
+        <v>-909.477174912</v>
       </c>
       <c r="Q89">
-        <v>-440.1935342879999</v>
+        <v>-455.8771749119999</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2446162692384635</v>
+        <v>0.2611842916750021</v>
       </c>
       <c r="T89">
-        <v>4.591599751465671</v>
+        <v>4.974233064087811</v>
       </c>
       <c r="U89">
         <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.07106074934329698</v>
+        <v>0.07025324082803223</v>
       </c>
       <c r="W89">
-        <v>0.186531001531866</v>
+        <v>0.1866931492417311</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3449550938994999</v>
+        <v>0.341035149650642</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8637,22 +8637,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1956320863337237</v>
+        <v>0.1971820863337237</v>
       </c>
       <c r="C90">
-        <v>-6807.196613936059</v>
+        <v>-6922.613137146939</v>
       </c>
       <c r="D90">
-        <v>1664.86338606394</v>
+        <v>1647.816862853061</v>
       </c>
       <c r="E90">
-        <v>5649.66</v>
+        <v>5748.030000000001</v>
       </c>
       <c r="F90">
-        <v>8656.559999999999</v>
+        <v>8754.93</v>
       </c>
       <c r="G90">
         <v>184.5</v>
@@ -8673,37 +8673,37 @@
         <v>592.8</v>
       </c>
       <c r="M90">
-        <v>1738.237248</v>
+        <v>1757.989944</v>
       </c>
       <c r="N90">
-        <v>-1145.437248</v>
+        <v>-1165.189944</v>
       </c>
       <c r="O90">
-        <v>-235.960073088</v>
+        <v>-240.0291284640001</v>
       </c>
       <c r="P90">
-        <v>-909.477174912</v>
+        <v>-925.1608155360002</v>
       </c>
       <c r="Q90">
-        <v>-455.8771749119999</v>
+        <v>-471.5608155360001</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2611842916750021</v>
+        <v>0.2807646818272752</v>
       </c>
       <c r="T90">
-        <v>4.974233064087811</v>
+        <v>5.426436069913977</v>
       </c>
       <c r="U90">
         <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.07025324082803223</v>
+        <v>0.06946387857153749</v>
       </c>
       <c r="W90">
-        <v>0.1866931492417311</v>
+        <v>0.1868516531828353</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.341035149650642</v>
+        <v>0.3372032940365898</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8719,22 +8719,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1971820863337237</v>
+        <v>0.1987320863337237</v>
       </c>
       <c r="C91">
-        <v>-6922.613137146939</v>
+        <v>-7037.684119907672</v>
       </c>
       <c r="D91">
-        <v>1647.816862853061</v>
+        <v>1631.115880092329</v>
       </c>
       <c r="E91">
-        <v>5748.030000000001</v>
+        <v>5846.400000000001</v>
       </c>
       <c r="F91">
-        <v>8754.93</v>
+        <v>8853.300000000001</v>
       </c>
       <c r="G91">
         <v>184.5</v>
@@ -8755,37 +8755,37 @@
         <v>592.8</v>
       </c>
       <c r="M91">
-        <v>1757.989944</v>
+        <v>1777.74264</v>
       </c>
       <c r="N91">
-        <v>-1165.189944</v>
+        <v>-1184.94264</v>
       </c>
       <c r="O91">
-        <v>-240.0291284640001</v>
+        <v>-244.0981838400001</v>
       </c>
       <c r="P91">
-        <v>-925.1608155360002</v>
+        <v>-940.8444561600002</v>
       </c>
       <c r="Q91">
-        <v>-471.5608155360001</v>
+        <v>-487.24445616</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.2807646818272752</v>
+        <v>0.3042611500100026</v>
       </c>
       <c r="T91">
-        <v>5.426436069913977</v>
+        <v>5.969079676905374</v>
       </c>
       <c r="U91">
         <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.06946387857153749</v>
+        <v>0.06869205769852041</v>
       </c>
       <c r="W91">
-        <v>0.1868516531828353</v>
+        <v>0.1870066348141371</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3372032940365898</v>
+        <v>0.3334565907695165</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8801,22 +8801,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1987320863337237</v>
+        <v>0.2002820863337237</v>
       </c>
       <c r="C92">
-        <v>-7037.684119907672</v>
+        <v>-7152.419963185328</v>
       </c>
       <c r="D92">
-        <v>1631.115880092329</v>
+        <v>1614.750036814673</v>
       </c>
       <c r="E92">
-        <v>5846.400000000001</v>
+        <v>5944.77</v>
       </c>
       <c r="F92">
-        <v>8853.300000000001</v>
+        <v>8951.67</v>
       </c>
       <c r="G92">
         <v>184.5</v>
@@ -8837,37 +8837,37 @@
         <v>592.8</v>
       </c>
       <c r="M92">
-        <v>1777.74264</v>
+        <v>1797.495336</v>
       </c>
       <c r="N92">
-        <v>-1184.94264</v>
+        <v>-1204.695336</v>
       </c>
       <c r="O92">
-        <v>-244.0981838400001</v>
+        <v>-248.1672392160001</v>
       </c>
       <c r="P92">
-        <v>-940.8444561600002</v>
+        <v>-956.5280967840001</v>
       </c>
       <c r="Q92">
-        <v>-487.24445616</v>
+        <v>-502.928096784</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3042611500100026</v>
+        <v>0.3329790555666696</v>
       </c>
       <c r="T92">
-        <v>5.969079676905374</v>
+        <v>6.632310752117082</v>
       </c>
       <c r="U92">
         <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.06869205769852041</v>
+        <v>0.06793719992161359</v>
       </c>
       <c r="W92">
-        <v>0.1870066348141371</v>
+        <v>0.18715821025574</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3334565907695165</v>
+        <v>0.3297922326291921</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8883,22 +8883,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2002820863337237</v>
+        <v>0.2018320863337237</v>
       </c>
       <c r="C93">
-        <v>-7152.419963185328</v>
+        <v>-7266.830654660218</v>
       </c>
       <c r="D93">
-        <v>1614.750036814673</v>
+        <v>1598.709345339782</v>
       </c>
       <c r="E93">
-        <v>5944.77</v>
+        <v>6043.140000000001</v>
       </c>
       <c r="F93">
-        <v>8951.67</v>
+        <v>9050.040000000001</v>
       </c>
       <c r="G93">
         <v>184.5</v>
@@ -8919,37 +8919,37 @@
         <v>592.8</v>
       </c>
       <c r="M93">
-        <v>1797.495336</v>
+        <v>1817.248032</v>
       </c>
       <c r="N93">
-        <v>-1204.695336</v>
+        <v>-1224.448032</v>
       </c>
       <c r="O93">
-        <v>-248.1672392160001</v>
+        <v>-252.2362945920001</v>
       </c>
       <c r="P93">
-        <v>-956.5280967840001</v>
+        <v>-972.2117374080002</v>
       </c>
       <c r="Q93">
-        <v>-502.928096784</v>
+        <v>-518.6117374080001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3329790555666696</v>
+        <v>0.3688764375125035</v>
       </c>
       <c r="T93">
-        <v>6.632310752117082</v>
+        <v>7.461349596131721</v>
       </c>
       <c r="U93">
         <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.06793719992161359</v>
+        <v>0.06719875209637866</v>
       </c>
       <c r="W93">
-        <v>0.18715821025574</v>
+        <v>0.1873064905790472</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3297922326291921</v>
+        <v>0.3262075344484401</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8965,22 +8965,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2018320863337237</v>
+        <v>0.2033820863337236</v>
       </c>
       <c r="C94">
-        <v>-7266.830654660218</v>
+        <v>-7380.925789051628</v>
       </c>
       <c r="D94">
-        <v>1598.709345339782</v>
+        <v>1582.984210948371</v>
       </c>
       <c r="E94">
-        <v>6043.140000000001</v>
+        <v>6141.51</v>
       </c>
       <c r="F94">
-        <v>9050.040000000001</v>
+        <v>9148.41</v>
       </c>
       <c r="G94">
         <v>184.5</v>
@@ -9001,37 +9001,37 @@
         <v>592.8</v>
       </c>
       <c r="M94">
-        <v>1817.248032</v>
+        <v>1837.000728</v>
       </c>
       <c r="N94">
-        <v>-1224.448032</v>
+        <v>-1244.200728</v>
       </c>
       <c r="O94">
-        <v>-252.2362945920001</v>
+        <v>-256.305349968</v>
       </c>
       <c r="P94">
-        <v>-972.2117374080002</v>
+        <v>-987.8953780320001</v>
       </c>
       <c r="Q94">
-        <v>-518.6117374080001</v>
+        <v>-534.2953780319999</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.3688764375125035</v>
+        <v>0.4150302143000039</v>
       </c>
       <c r="T94">
-        <v>7.461349596131721</v>
+        <v>8.527256681293395</v>
       </c>
       <c r="U94">
         <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.06719875209637866</v>
+        <v>0.06647618486953588</v>
       </c>
       <c r="W94">
-        <v>0.1873064905790472</v>
+        <v>0.1874515820781972</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3262075344484401</v>
+        <v>0.322699926551145</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9047,22 +9047,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2033820863337236</v>
+        <v>0.2049320863337237</v>
       </c>
       <c r="C95">
-        <v>-7380.925789051628</v>
+        <v>-7494.714587255685</v>
       </c>
       <c r="D95">
-        <v>1582.984210948371</v>
+        <v>1567.565412744316</v>
       </c>
       <c r="E95">
-        <v>6141.51</v>
+        <v>6239.880000000001</v>
       </c>
       <c r="F95">
-        <v>9148.41</v>
+        <v>9246.780000000001</v>
       </c>
       <c r="G95">
         <v>184.5</v>
@@ -9083,37 +9083,37 @@
         <v>592.8</v>
       </c>
       <c r="M95">
-        <v>1837.000728</v>
+        <v>1856.753424</v>
       </c>
       <c r="N95">
-        <v>-1244.200728</v>
+        <v>-1263.953424</v>
       </c>
       <c r="O95">
-        <v>-256.305349968</v>
+        <v>-260.3744053440001</v>
       </c>
       <c r="P95">
-        <v>-987.8953780320001</v>
+        <v>-1003.579018656</v>
       </c>
       <c r="Q95">
-        <v>-534.2953780319999</v>
+        <v>-549.9790186560001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.4150302143000039</v>
+        <v>0.4765685833500047</v>
       </c>
       <c r="T95">
-        <v>8.527256681293395</v>
+        <v>9.94846612817563</v>
       </c>
       <c r="U95">
         <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.06647618486953588</v>
+        <v>0.06576899141347699</v>
       </c>
       <c r="W95">
-        <v>0.1874515820781972</v>
+        <v>0.1875935865241738</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.322699926551145</v>
+        <v>0.3192669486091115</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9129,22 +9129,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2049320863337237</v>
+        <v>0.2064820863337237</v>
       </c>
       <c r="C96">
-        <v>-7494.714587255685</v>
+        <v>-7608.205914375544</v>
       </c>
       <c r="D96">
-        <v>1567.565412744316</v>
+        <v>1552.444085624458</v>
       </c>
       <c r="E96">
-        <v>6239.880000000001</v>
+        <v>6338.250000000002</v>
       </c>
       <c r="F96">
-        <v>9246.780000000001</v>
+        <v>9345.150000000001</v>
       </c>
       <c r="G96">
         <v>184.5</v>
@@ -9165,37 +9165,37 @@
         <v>592.8</v>
       </c>
       <c r="M96">
-        <v>1856.753424</v>
+        <v>1876.50612</v>
       </c>
       <c r="N96">
-        <v>-1263.953424</v>
+        <v>-1283.70612</v>
       </c>
       <c r="O96">
-        <v>-260.3744053440001</v>
+        <v>-264.4434607200001</v>
       </c>
       <c r="P96">
-        <v>-1003.579018656</v>
+        <v>-1019.26265928</v>
       </c>
       <c r="Q96">
-        <v>-549.9790186560001</v>
+        <v>-565.6626592800001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.4765685833500047</v>
+        <v>0.5627223000200058</v>
       </c>
       <c r="T96">
-        <v>9.94846612817563</v>
+        <v>11.93815935381076</v>
       </c>
       <c r="U96">
         <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.06576899141347699</v>
+        <v>0.06507668624070354</v>
       </c>
       <c r="W96">
-        <v>0.1875935865241738</v>
+        <v>0.1877326014028667</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3192669486091115</v>
+        <v>0.3159062438869104</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9211,22 +9211,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2064820863337237</v>
+        <v>0.2080320863337237</v>
       </c>
       <c r="C97">
-        <v>-7608.205914375544</v>
+        <v>-7721.40829671801</v>
       </c>
       <c r="D97">
-        <v>1552.444085624458</v>
+        <v>1537.61170328199</v>
       </c>
       <c r="E97">
-        <v>6338.250000000002</v>
+        <v>6436.620000000001</v>
       </c>
       <c r="F97">
-        <v>9345.150000000001</v>
+        <v>9443.52</v>
       </c>
       <c r="G97">
         <v>184.5</v>
@@ -9247,37 +9247,37 @@
         <v>592.8</v>
       </c>
       <c r="M97">
-        <v>1876.50612</v>
+        <v>1896.258816</v>
       </c>
       <c r="N97">
-        <v>-1283.70612</v>
+        <v>-1303.458816</v>
       </c>
       <c r="O97">
-        <v>-264.4434607200001</v>
+        <v>-268.5125160960001</v>
       </c>
       <c r="P97">
-        <v>-1019.26265928</v>
+        <v>-1034.946299904</v>
       </c>
       <c r="Q97">
-        <v>-565.6626592800001</v>
+        <v>-581.346299904</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.5627223000200058</v>
+        <v>0.6919528750250077</v>
       </c>
       <c r="T97">
-        <v>11.93815935381076</v>
+        <v>14.92269919226346</v>
       </c>
       <c r="U97">
         <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.06507668624070354</v>
+        <v>0.06439880409236287</v>
       </c>
       <c r="W97">
-        <v>0.1877326014028667</v>
+        <v>0.1878687201382535</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3159062438869104</v>
+        <v>0.3126155538464217</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9293,22 +9293,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2080320863337236</v>
+        <v>0.2095820863337236</v>
       </c>
       <c r="C98">
-        <v>-7721.40829671801</v>
+        <v>-7834.329937825027</v>
       </c>
       <c r="D98">
-        <v>1537.61170328199</v>
+        <v>1523.060062174972</v>
       </c>
       <c r="E98">
-        <v>6436.620000000001</v>
+        <v>6534.99</v>
       </c>
       <c r="F98">
-        <v>9443.52</v>
+        <v>9541.889999999999</v>
       </c>
       <c r="G98">
         <v>184.5</v>
@@ -9329,37 +9329,37 @@
         <v>592.8</v>
       </c>
       <c r="M98">
-        <v>1896.258816</v>
+        <v>1916.011512</v>
       </c>
       <c r="N98">
-        <v>-1303.458816</v>
+        <v>-1323.211512</v>
       </c>
       <c r="O98">
-        <v>-268.5125160960001</v>
+        <v>-272.5815714720001</v>
       </c>
       <c r="P98">
-        <v>-1034.946299904</v>
+        <v>-1050.629940528</v>
       </c>
       <c r="Q98">
-        <v>-581.346299904</v>
+        <v>-597.029940528</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.6919528750250059</v>
+        <v>0.9073371667000077</v>
       </c>
       <c r="T98">
-        <v>14.92269919226342</v>
+        <v>19.89693225635122</v>
       </c>
       <c r="U98">
         <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.06439880409236287</v>
+        <v>0.06373489889553441</v>
       </c>
       <c r="W98">
-        <v>0.1878687201382535</v>
+        <v>0.1880020323017767</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3126155538464217</v>
+        <v>0.3093927130851184</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2095820863337236</v>
+        <v>0.2111320863337237</v>
       </c>
       <c r="C99">
-        <v>-7834.329937825027</v>
+        <v>-7946.978733603399</v>
       </c>
       <c r="D99">
-        <v>1523.060062174972</v>
+        <v>1508.781266396601</v>
       </c>
       <c r="E99">
-        <v>6534.99</v>
+        <v>6633.360000000001</v>
       </c>
       <c r="F99">
-        <v>9541.889999999999</v>
+        <v>9640.26</v>
       </c>
       <c r="G99">
         <v>184.5</v>
@@ -9411,37 +9411,37 @@
         <v>592.8</v>
       </c>
       <c r="M99">
-        <v>1916.011512</v>
+        <v>1935.764208</v>
       </c>
       <c r="N99">
-        <v>-1323.211512</v>
+        <v>-1342.964208</v>
       </c>
       <c r="O99">
-        <v>-272.5815714720001</v>
+        <v>-276.6506268480001</v>
       </c>
       <c r="P99">
-        <v>-1050.629940528</v>
+        <v>-1066.313581152</v>
       </c>
       <c r="Q99">
-        <v>-597.029940528</v>
+        <v>-612.713581152</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.9073371667000077</v>
+        <v>1.338105750050012</v>
       </c>
       <c r="T99">
-        <v>19.89693225635122</v>
+        <v>29.84539838452684</v>
       </c>
       <c r="U99">
         <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.06373489889553441</v>
+        <v>0.06308454278435548</v>
       </c>
       <c r="W99">
-        <v>0.1880020323017767</v>
+        <v>0.1881326238089014</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3093927130851184</v>
+        <v>0.3062356445842499</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9457,22 +9457,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2111320863337237</v>
+        <v>0.2126820863337237</v>
       </c>
       <c r="C100">
-        <v>-7946.978733603399</v>
+        <v>-8059.362286611346</v>
       </c>
       <c r="D100">
-        <v>1508.781266396601</v>
+        <v>1494.767713388653</v>
       </c>
       <c r="E100">
-        <v>6633.360000000001</v>
+        <v>6731.73</v>
       </c>
       <c r="F100">
-        <v>9640.26</v>
+        <v>9738.629999999999</v>
       </c>
       <c r="G100">
         <v>184.5</v>
@@ -9493,37 +9493,37 @@
         <v>592.8</v>
       </c>
       <c r="M100">
-        <v>1935.764208</v>
+        <v>1955.516904</v>
       </c>
       <c r="N100">
-        <v>-1342.964208</v>
+        <v>-1362.716904</v>
       </c>
       <c r="O100">
-        <v>-276.6506268480001</v>
+        <v>-280.719682224</v>
       </c>
       <c r="P100">
-        <v>-1066.313581152</v>
+        <v>-1081.997221776</v>
       </c>
       <c r="Q100">
-        <v>-612.713581152</v>
+        <v>-628.3972217759997</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.338105750050012</v>
+        <v>2.630411500100024</v>
       </c>
       <c r="T100">
-        <v>29.84539838452684</v>
+        <v>59.69079676905368</v>
       </c>
       <c r="U100">
         <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.06308454278435548</v>
+        <v>0.0624473251804731</v>
       </c>
       <c r="W100">
-        <v>0.1881326238089014</v>
+        <v>0.188260577103761</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,91 +9531,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3062356445842499</v>
+        <v>0.3031423552450151</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2126820863337237</v>
-      </c>
-      <c r="C101">
-        <v>-8059.362286611346</v>
-      </c>
-      <c r="D101">
-        <v>1494.767713388653</v>
-      </c>
-      <c r="E101">
-        <v>6731.73</v>
-      </c>
-      <c r="F101">
-        <v>9738.629999999999</v>
-      </c>
-      <c r="G101">
-        <v>184.5</v>
-      </c>
-      <c r="H101">
-        <v>6830.1</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>1046.4</v>
-      </c>
-      <c r="K101">
-        <v>453.6000000000001</v>
-      </c>
-      <c r="L101">
-        <v>592.8</v>
-      </c>
-      <c r="M101">
-        <v>1955.516904</v>
-      </c>
-      <c r="N101">
-        <v>-1362.716904</v>
-      </c>
-      <c r="O101">
-        <v>-280.719682224</v>
-      </c>
-      <c r="P101">
-        <v>-1081.997221776</v>
-      </c>
-      <c r="Q101">
-        <v>-628.3972217759997</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.630411500100024</v>
-      </c>
-      <c r="T101">
-        <v>59.69079676905368</v>
-      </c>
-      <c r="U101">
-        <v>0.2008</v>
-      </c>
-      <c r="V101">
-        <v>0.0624473251804731</v>
-      </c>
-      <c r="W101">
-        <v>0.188260577103761</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3031423552450151</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
